--- a/data/dataset.xlsx
+++ b/data/dataset.xlsx
@@ -543,7 +543,7 @@
       </c>
       <c r="Y1" t="inlineStr">
         <is>
-          <t>ret_12m</t>
+          <t>ret_12m.1</t>
         </is>
       </c>
     </row>
@@ -563,7 +563,7 @@
         <v>24.39999961853027</v>
       </c>
       <c r="E2" t="n">
-        <v>0.02736840499074835</v>
+        <v>0.2842105062384352</v>
       </c>
       <c r="F2" t="n">
         <v>0</v>
@@ -613,7 +613,7 @@
         </is>
       </c>
       <c r="S2" s="1" t="n">
-        <v>43573</v>
+        <v>25569.0421709838</v>
       </c>
       <c r="T2" t="n">
         <v>19</v>
@@ -654,7 +654,7 @@
         <v>28.89999961853027</v>
       </c>
       <c r="E3" t="n">
-        <v>0.03214284351893833</v>
+        <v>0.4449999809265135</v>
       </c>
       <c r="F3" t="n">
         <v>-0.3813148997655281</v>
@@ -704,7 +704,7 @@
         </is>
       </c>
       <c r="S3" s="1" t="n">
-        <v>43644</v>
+        <v>25569.04217180555</v>
       </c>
       <c r="T3" t="n">
         <v>20</v>
@@ -745,7 +745,7 @@
         <v>84.80000305175781</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.348694277731297</v>
+        <v>5.523077157827524</v>
       </c>
       <c r="F4" t="n">
         <v>0.03183958550796561</v>
@@ -791,7 +791,7 @@
         </is>
       </c>
       <c r="S4" s="1" t="n">
-        <v>43678</v>
+        <v>25569.04217219908</v>
       </c>
       <c r="T4" t="n">
         <v>13</v>
@@ -832,7 +832,7 @@
         <v>15.9399995803833</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1807407096580223</v>
+        <v>0.2261538138756385</v>
       </c>
       <c r="F5" t="n">
         <v>0.7446675155604773</v>
@@ -882,7 +882,7 @@
         </is>
       </c>
       <c r="S5" s="1" t="n">
-        <v>43763</v>
+        <v>25569.04217318287</v>
       </c>
       <c r="T5" t="n">
         <v>13</v>
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="S6" s="1" t="n">
-        <v>43789</v>
+        <v>25569.04217348379</v>
       </c>
       <c r="T6" t="n">
         <v>13</v>
@@ -1014,7 +1014,7 @@
         <v>46800</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>3599</v>
       </c>
       <c r="F7" t="n">
         <v>0.0007692307692307692</v>
@@ -1064,7 +1064,7 @@
         </is>
       </c>
       <c r="S7" s="1" t="n">
-        <v>43770</v>
+        <v>25569.04217326389</v>
       </c>
       <c r="T7" t="n">
         <v>13</v>
@@ -1105,7 +1105,7 @@
         <v>34.66328811645508</v>
       </c>
       <c r="E8" t="n">
-        <v>0.04524235632503221</v>
+        <v>0.2838254857946325</v>
       </c>
       <c r="F8" t="n">
         <v>0.2088800941764475</v>
@@ -1155,7 +1155,7 @@
         </is>
       </c>
       <c r="S8" s="1" t="n">
-        <v>43559</v>
+        <v>25569.04217082176</v>
       </c>
       <c r="T8" t="n">
         <v>27</v>
@@ -1196,7 +1196,7 @@
         <v>28.48999977111816</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2072033606189249</v>
+        <v>0.6758823394775388</v>
       </c>
       <c r="F9" t="n">
         <v>-0.4457704426568583</v>
@@ -1246,7 +1246,7 @@
         </is>
       </c>
       <c r="S9" s="1" t="n">
-        <v>43636</v>
+        <v>25569.04217171296</v>
       </c>
       <c r="T9" t="n">
         <v>17</v>
@@ -1287,7 +1287,7 @@
         <v>16.60000038146973</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.08033234996562545</v>
+        <v>-0.02352938932530999</v>
       </c>
       <c r="F10" t="n">
         <v>-0.0331325982994034</v>
@@ -1337,7 +1337,7 @@
         </is>
       </c>
       <c r="S10" s="1" t="n">
-        <v>43812</v>
+        <v>25569.04217375</v>
       </c>
       <c r="T10" t="n">
         <v>17</v>
@@ -1378,7 +1378,7 @@
         <v>10.47999954223633</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.1338843626578981</v>
+        <v>-0.001904805501301914</v>
       </c>
       <c r="F11" t="n">
         <v>-0.01335872096980674</v>
@@ -1426,7 +1426,7 @@
         </is>
       </c>
       <c r="S11" s="1" t="n">
-        <v>43622</v>
+        <v>25569.04217155093</v>
       </c>
       <c r="T11" t="n">
         <v>10.5</v>
@@ -1467,7 +1467,7 @@
         <v>40.29999923706055</v>
       </c>
       <c r="E12" t="n">
-        <v>0.03306846888058628</v>
+        <v>0.8318181471391157</v>
       </c>
       <c r="F12" t="n">
         <v>0.0330025274499657</v>
@@ -1517,7 +1517,7 @@
         </is>
       </c>
       <c r="S12" s="1" t="n">
-        <v>43643</v>
+        <v>25569.04217179398</v>
       </c>
       <c r="T12" t="n">
         <v>22</v>
@@ -1558,7 +1558,7 @@
         <v>16.67089462280273</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1030303492690578</v>
+        <v>0.2080358422320819</v>
       </c>
       <c r="F13" t="n">
         <v>-0.2780219899660769</v>
@@ -1608,7 +1608,7 @@
         </is>
       </c>
       <c r="S13" s="1" t="n">
-        <v>43587</v>
+        <v>25569.04217114583</v>
       </c>
       <c r="T13" t="n">
         <v>13.8</v>
@@ -1649,7 +1649,7 @@
         <v>7.889999866485596</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.1694736982646741</v>
+        <v>-0.2110000133514404</v>
       </c>
       <c r="F14" t="n">
         <v>0.2040557871684146</v>
@@ -1695,7 +1695,7 @@
         </is>
       </c>
       <c r="S14" s="1" t="n">
-        <v>43592</v>
+        <v>25569.0421712037</v>
       </c>
       <c r="T14" t="n">
         <v>10</v>
@@ -1736,7 +1736,7 @@
         <v>195.1999969482422</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.1029412156570318</v>
+        <v>19.54736809981497</v>
       </c>
       <c r="F15" t="n">
         <v>0.06045083625122502</v>
@@ -1784,7 +1784,7 @@
         </is>
       </c>
       <c r="S15" s="1" t="n">
-        <v>43692</v>
+        <v>25569.04217236111</v>
       </c>
       <c r="T15" t="n">
         <v>9.5</v>
@@ -1825,7 +1825,7 @@
         <v>12.35807037353516</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.04074078827183153</v>
+        <v>-0.2276206016540525</v>
       </c>
       <c r="F16" t="n">
         <v>0.1177606669230774</v>
@@ -1871,7 +1871,7 @@
         </is>
       </c>
       <c r="S16" s="1" t="n">
-        <v>43749</v>
+        <v>25569.04217302083</v>
       </c>
       <c r="T16" t="n">
         <v>16</v>
@@ -1912,7 +1912,7 @@
         <v>16.17000007629395</v>
       </c>
       <c r="E17" t="n">
-        <v>0.02993632310437638</v>
+        <v>0.07800000508626326</v>
       </c>
       <c r="F17" t="n">
         <v>0.05132961779776844</v>
@@ -1962,7 +1962,7 @@
         </is>
       </c>
       <c r="S17" s="1" t="n">
-        <v>43734</v>
+        <v>25569.04217284722</v>
       </c>
       <c r="T17" t="n">
         <v>15</v>
@@ -2003,7 +2003,7 @@
         <v>17.94000053405762</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.05578944557591489</v>
+        <v>0.1212500333786013</v>
       </c>
       <c r="F18" t="n">
         <v>0.2318840425625792</v>
@@ -2049,7 +2049,7 @@
         </is>
       </c>
       <c r="S18" s="1" t="n">
-        <v>43504</v>
+        <v>25569.04217018518</v>
       </c>
       <c r="T18" t="n">
         <v>16</v>
@@ -2090,7 +2090,7 @@
         <v>16.35000038146973</v>
       </c>
       <c r="E19" t="n">
-        <v>0.01426796093437834</v>
+        <v>0.1678571701049807</v>
       </c>
       <c r="F19" t="n">
         <v>0.237308811635503</v>
@@ -2140,7 +2140,7 @@
         </is>
       </c>
       <c r="S19" s="1" t="n">
-        <v>43756</v>
+        <v>25569.04217310185</v>
       </c>
       <c r="T19" t="n">
         <v>14</v>
@@ -2181,7 +2181,7 @@
         <v>10</v>
       </c>
       <c r="E20" t="n">
-        <v>0.1111111111111111</v>
+        <v>-0.09090909090909091</v>
       </c>
       <c r="F20" t="n">
         <v>-0.08900003433227539</v>
@@ -2227,7 +2227,7 @@
         </is>
       </c>
       <c r="S20" s="1" t="n">
-        <v>43763</v>
+        <v>25569.04217318287</v>
       </c>
       <c r="T20" t="n">
         <v>11</v>
@@ -2268,7 +2268,7 @@
         <v>10.92000007629395</v>
       </c>
       <c r="E21" t="n">
-        <v>0.3464858863838703</v>
+        <v>0.3650000095367438</v>
       </c>
       <c r="F21" t="n">
         <v>0.2051281827351764</v>
@@ -2318,7 +2318,7 @@
         </is>
       </c>
       <c r="S21" s="1" t="n">
-        <v>43544</v>
+        <v>25569.04217064815</v>
       </c>
       <c r="T21" t="n">
         <v>8</v>
@@ -2359,7 +2359,7 @@
         <v>11.47609233856201</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.0135849286925119</v>
+        <v>-0.1802791186741421</v>
       </c>
       <c r="F22" t="n">
         <v>-0.2134660123296898</v>
@@ -2409,7 +2409,7 @@
         </is>
       </c>
       <c r="S22" s="1" t="n">
-        <v>43496</v>
+        <v>25569.04217009259</v>
       </c>
       <c r="T22" t="n">
         <v>14</v>
@@ -2450,7 +2450,7 @@
         <v>11.60106563568115</v>
       </c>
       <c r="E23" t="n">
-        <v>0</v>
+        <v>-0.317584374371697</v>
       </c>
       <c r="F23" t="n">
         <v>-0.1023529012341467</v>
@@ -2500,7 +2500,7 @@
         </is>
       </c>
       <c r="S23" s="1" t="n">
-        <v>43600</v>
+        <v>25569.0421712963</v>
       </c>
       <c r="T23" t="n">
         <v>17</v>
@@ -2541,7 +2541,7 @@
         <v>25.07999992370605</v>
       </c>
       <c r="E24" t="n">
-        <v>-0.06242990939416618</v>
+        <v>0.3933333290947806</v>
       </c>
       <c r="F24" t="n">
         <v>0.07496009435748018</v>
@@ -2591,7 +2591,7 @@
         </is>
       </c>
       <c r="S24" s="1" t="n">
-        <v>43664</v>
+        <v>25569.04217203704</v>
       </c>
       <c r="T24" t="n">
         <v>18</v>
@@ -2632,7 +2632,7 @@
         <v>523.2000122070312</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.03111108850549768</v>
+        <v>31.70000076293945</v>
       </c>
       <c r="F25" t="n">
         <v>-0.251720200944715</v>
@@ -2682,7 +2682,7 @@
         </is>
       </c>
       <c r="S25" s="1" t="n">
-        <v>43552</v>
+        <v>25569.04217074074</v>
       </c>
       <c r="T25" t="n">
         <v>16</v>
@@ -2723,7 +2723,7 @@
         <v>328.8999938964844</v>
       </c>
       <c r="E26" t="n">
-        <v>0.6306395581199871</v>
+        <v>18.34705846449908</v>
       </c>
       <c r="F26" t="n">
         <v>0.09121313638407055</v>
@@ -2767,7 +2767,7 @@
         </is>
       </c>
       <c r="S26" s="1" t="n">
-        <v>43594</v>
+        <v>25569.04217122685</v>
       </c>
       <c r="T26" t="n">
         <v>17</v>
@@ -2808,7 +2808,7 @@
         <v>41.56999969482422</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.01023810250418527</v>
+        <v>-0.07622222900390625</v>
       </c>
       <c r="F27" t="n">
         <v>0.03656484168685051</v>
@@ -2858,7 +2858,7 @@
         </is>
       </c>
       <c r="S27" s="1" t="n">
-        <v>43595</v>
+        <v>25569.04217123843</v>
       </c>
       <c r="T27" t="n">
         <v>45</v>
@@ -2899,7 +2899,7 @@
         <v>18.98999977111816</v>
       </c>
       <c r="E28" t="n">
-        <v>0.02648647411449535</v>
+        <v>0.2659999847412107</v>
       </c>
       <c r="F28" t="n">
         <v>0.2216956841792209</v>
@@ -2949,7 +2949,7 @@
         </is>
       </c>
       <c r="S28" s="1" t="n">
-        <v>43572</v>
+        <v>25569.04217097222</v>
       </c>
       <c r="T28" t="n">
         <v>15</v>
@@ -2990,7 +2990,7 @@
         <v>27.95000076293945</v>
       </c>
       <c r="E29" t="n">
-        <v>0.08966866193431032</v>
+        <v>0.2704545801336113</v>
       </c>
       <c r="F29" t="n">
         <v>0.07906973252762926</v>
@@ -3040,7 +3040,7 @@
         </is>
       </c>
       <c r="S29" s="1" t="n">
-        <v>43726</v>
+        <v>25569.04217275463</v>
       </c>
       <c r="T29" t="n">
         <v>22</v>
@@ -3081,7 +3081,7 @@
         <v>28.51000022888184</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.08032257326187627</v>
+        <v>0.2959091013128109</v>
       </c>
       <c r="F30" t="n">
         <v>0.3591722093619842</v>
@@ -3131,7 +3131,7 @@
         </is>
       </c>
       <c r="S30" s="1" t="n">
-        <v>43636</v>
+        <v>25569.04217171296</v>
       </c>
       <c r="T30" t="n">
         <v>22</v>
@@ -3172,7 +3172,7 @@
         <v>60.54000091552734</v>
       </c>
       <c r="E31" t="n">
-        <v>0.1324355022877481</v>
+        <v>3.804761977422805</v>
       </c>
       <c r="F31" t="n">
         <v>-0.127849381589316</v>
@@ -3218,7 +3218,7 @@
         </is>
       </c>
       <c r="S31" s="1" t="n">
-        <v>43682</v>
+        <v>25569.04217224537</v>
       </c>
       <c r="T31" t="n">
         <v>12.6</v>
@@ -3259,7 +3259,7 @@
         <v>13.21000003814697</v>
       </c>
       <c r="E32" t="n">
-        <v>0.01615384908822867</v>
+        <v>-0.1193333307902019</v>
       </c>
       <c r="F32" t="n">
         <v>-0.02498106909561715</v>
@@ -3305,7 +3305,7 @@
         </is>
       </c>
       <c r="S32" s="1" t="n">
-        <v>43664</v>
+        <v>25569.04217203704</v>
       </c>
       <c r="T32" t="n">
         <v>15</v>
@@ -3346,7 +3346,7 @@
         <v>27.54999923706055</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.0999673738084212</v>
+        <v>0.6205881904153265</v>
       </c>
       <c r="F33" t="n">
         <v>-0.02431942268051515</v>
@@ -3396,7 +3396,7 @@
         </is>
       </c>
       <c r="S33" s="1" t="n">
-        <v>43643</v>
+        <v>25569.04217179398</v>
       </c>
       <c r="T33" t="n">
         <v>17</v>
@@ -3437,7 +3437,7 @@
         <v>25.45999908447266</v>
       </c>
       <c r="E34" t="n">
-        <v>0.343535517648359</v>
+        <v>0.7558620058257006</v>
       </c>
       <c r="F34" t="n">
         <v>-0.09426550293923484</v>
@@ -3481,7 +3481,7 @@
         </is>
       </c>
       <c r="S34" s="1" t="n">
-        <v>43567</v>
+        <v>25569.04217091435</v>
       </c>
       <c r="T34" t="n">
         <v>14.5</v>
@@ -3522,7 +3522,7 @@
         <v>15.80155658721924</v>
       </c>
       <c r="E35" t="n">
-        <v>0.03636367599685471</v>
+        <v>-0.2475449244181314</v>
       </c>
       <c r="F35" t="n">
         <v>-0.01253137385040002</v>
@@ -3566,7 +3566,7 @@
         </is>
       </c>
       <c r="S35" s="1" t="n">
-        <v>43467</v>
+        <v>25569.04216975694</v>
       </c>
       <c r="T35" t="n">
         <v>21</v>
@@ -3607,7 +3607,7 @@
         <v>685</v>
       </c>
       <c r="E36" t="n">
-        <v>0.2232142857142857</v>
+        <v>47.92857142857143</v>
       </c>
       <c r="F36" t="n">
         <v>0.1218978102189781</v>
@@ -3655,7 +3655,7 @@
         </is>
       </c>
       <c r="S36" s="1" t="n">
-        <v>43741</v>
+        <v>25569.04217292824</v>
       </c>
       <c r="T36" t="n">
         <v>14</v>
@@ -3696,7 +3696,7 @@
         <v>65.75</v>
       </c>
       <c r="E37" t="n">
-        <v>0.4293478260869565</v>
+        <v>1.63</v>
       </c>
       <c r="F37" t="n">
         <v>1.303878262015803</v>
@@ -3746,7 +3746,7 @@
         </is>
       </c>
       <c r="S37" s="1" t="n">
-        <v>43587</v>
+        <v>25569.04217114583</v>
       </c>
       <c r="T37" t="n">
         <v>25</v>
@@ -3787,7 +3787,7 @@
         <v>12.5</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.07407407407407407</v>
+        <v>-0.2647058823529412</v>
       </c>
       <c r="F38" t="n">
         <v>0.1263999938964844</v>
@@ -3837,7 +3837,7 @@
         </is>
       </c>
       <c r="S38" s="1" t="n">
-        <v>43763</v>
+        <v>25569.04217318287</v>
       </c>
       <c r="T38" t="n">
         <v>17</v>
@@ -3878,7 +3878,7 @@
         <v>15.96886730194092</v>
       </c>
       <c r="E39" t="n">
-        <v>-0.005056188564351589</v>
+        <v>-0.08749329703194744</v>
       </c>
       <c r="F39" t="n">
         <v>-0.02540942971904147</v>
@@ -3924,7 +3924,7 @@
         </is>
       </c>
       <c r="S39" s="1" t="n">
-        <v>43594</v>
+        <v>25569.04217122685</v>
       </c>
       <c r="T39" t="n">
         <v>17.5</v>
@@ -3965,7 +3965,7 @@
         <v>18</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>0.2</v>
       </c>
       <c r="F40" t="n">
         <v>-0.1016666624281141</v>
@@ -4015,7 +4015,7 @@
         </is>
       </c>
       <c r="S40" s="1" t="n">
-        <v>43721</v>
+        <v>25569.04217269676</v>
       </c>
       <c r="T40" t="n">
         <v>15</v>
@@ -4056,7 +4056,7 @@
         <v>410</v>
       </c>
       <c r="E41" t="n">
-        <v>0.3264315493500625</v>
+        <v>26.33333333333333</v>
       </c>
       <c r="F41" t="n">
         <v>0.3190243604706555</v>
@@ -4102,7 +4102,7 @@
         </is>
       </c>
       <c r="S41" s="1" t="n">
-        <v>43741</v>
+        <v>25569.04217292824</v>
       </c>
       <c r="T41" t="n">
         <v>15</v>
@@ -4143,7 +4143,7 @@
         <v>21.39999961853027</v>
       </c>
       <c r="E42" t="n">
-        <v>0.06999998092651367</v>
+        <v>0.3374999761581419</v>
       </c>
       <c r="F42" t="n">
         <v>0.1873831916057407</v>
@@ -4193,7 +4193,7 @@
         </is>
       </c>
       <c r="S42" s="1" t="n">
-        <v>43671</v>
+        <v>25569.04217211806</v>
       </c>
       <c r="T42" t="n">
         <v>16</v>
@@ -4234,7 +4234,7 @@
         <v>25.56999969482422</v>
       </c>
       <c r="E43" t="n">
-        <v>-0.06027193843546656</v>
+        <v>0.4205555386013455</v>
       </c>
       <c r="F43" t="n">
         <v>0.003128663459556003</v>
@@ -4280,7 +4280,7 @@
         </is>
       </c>
       <c r="S43" s="1" t="n">
-        <v>43635</v>
+        <v>25569.04217170139</v>
       </c>
       <c r="T43" t="n">
         <v>18</v>
@@ -4321,7 +4321,7 @@
         <v>23.85000038146973</v>
       </c>
       <c r="E44" t="n">
-        <v>-0.06470586739334405</v>
+        <v>0.4906250238418581</v>
       </c>
       <c r="F44" t="n">
         <v>-0.11865827582564</v>
@@ -4371,7 +4371,7 @@
         </is>
       </c>
       <c r="S44" s="1" t="n">
-        <v>43678</v>
+        <v>25569.04217219908</v>
       </c>
       <c r="T44" t="n">
         <v>16</v>
@@ -4412,7 +4412,7 @@
         <v>30.06999969482422</v>
       </c>
       <c r="E45" t="n">
-        <v>-0.01892332564191617</v>
+        <v>0.113703692400897</v>
       </c>
       <c r="F45" t="n">
         <v>0.1882274660743124</v>
@@ -4462,7 +4462,7 @@
         </is>
       </c>
       <c r="S45" s="1" t="n">
-        <v>43593</v>
+        <v>25569.04217121528</v>
       </c>
       <c r="T45" t="n">
         <v>27</v>
@@ -4503,7 +4503,7 @@
         <v>13.35000038146973</v>
       </c>
       <c r="E46" t="n">
-        <v>-0.02909088134765625</v>
+        <v>0.02692310626690231</v>
       </c>
       <c r="F46" t="n">
         <v>-0.08239702996537483</v>
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="S46" s="1" t="n">
-        <v>43777</v>
+        <v>25569.04217334491</v>
       </c>
       <c r="T46" t="n">
         <v>13</v>
@@ -4594,7 +4594,7 @@
         <v>12.70252990722656</v>
       </c>
       <c r="E47" t="n">
-        <v>0</v>
+        <v>-0.3314457943564968</v>
       </c>
       <c r="F47" t="n">
         <v>0.004660436434575055</v>
@@ -4644,7 +4644,7 @@
         </is>
       </c>
       <c r="S47" s="1" t="n">
-        <v>43791</v>
+        <v>25569.04217350694</v>
       </c>
       <c r="T47" t="n">
         <v>19</v>
@@ -4685,7 +4685,7 @@
         <v>12</v>
       </c>
       <c r="E48" t="n">
-        <v>-0.1024682047334059</v>
+        <v>-0.1428571428571428</v>
       </c>
       <c r="F48" t="n">
         <v>-0.2575000127156575</v>
@@ -4735,7 +4735,7 @@
         </is>
       </c>
       <c r="S48" s="1" t="n">
-        <v>43608</v>
+        <v>25569.04217138889</v>
       </c>
       <c r="T48" t="n">
         <v>14</v>
@@ -4776,7 +4776,7 @@
         <v>13.5</v>
       </c>
       <c r="E49" t="n">
-        <v>-0.06896551724137931</v>
+        <v>-0.15625</v>
       </c>
       <c r="F49" t="n">
         <v>-0.1911111054597077</v>
@@ -4822,7 +4822,7 @@
         </is>
       </c>
       <c r="S49" s="1" t="n">
-        <v>43664</v>
+        <v>25569.04217203704</v>
       </c>
       <c r="T49" t="n">
         <v>16</v>
@@ -4863,7 +4863,7 @@
         <v>14.5</v>
       </c>
       <c r="E50" t="n">
-        <v>-0.01494567004333452</v>
+        <v>0.03571428571428571</v>
       </c>
       <c r="F50" t="n">
         <v>0.2924137773184941</v>
@@ -4913,7 +4913,7 @@
         </is>
       </c>
       <c r="S50" s="1" t="n">
-        <v>43602</v>
+        <v>25569.04217131944</v>
       </c>
       <c r="T50" t="n">
         <v>14</v>
@@ -4954,7 +4954,7 @@
         <v>52.75</v>
       </c>
       <c r="E51" t="n">
-        <v>-0.02314814814814815</v>
+        <v>0.3525641025641026</v>
       </c>
       <c r="F51" t="n">
         <v>0.07715639231894253</v>
@@ -5004,7 +5004,7 @@
         </is>
       </c>
       <c r="S51" s="1" t="n">
-        <v>43720</v>
+        <v>25569.04217268519</v>
       </c>
       <c r="T51" t="n">
         <v>39</v>
@@ -5045,7 +5045,7 @@
         <v>38.25</v>
       </c>
       <c r="E52" t="n">
-        <v>0.04081632653061224</v>
+        <v>0.59375</v>
       </c>
       <c r="F52" t="n">
         <v>0.3911110871757557</v>
@@ -5095,7 +5095,7 @@
         </is>
       </c>
       <c r="S52" s="1" t="n">
-        <v>43566</v>
+        <v>25569.04217090278</v>
       </c>
       <c r="T52" t="n">
         <v>24</v>
@@ -5136,7 +5136,7 @@
         <v>35.5</v>
       </c>
       <c r="E53" t="n">
-        <v>-0.04697986577181208</v>
+        <v>0.6136363636363636</v>
       </c>
       <c r="F53" t="n">
         <v>0.07183096442424075</v>
@@ -5186,7 +5186,7 @@
         </is>
       </c>
       <c r="S53" s="1" t="n">
-        <v>43811</v>
+        <v>25569.04217373843</v>
       </c>
       <c r="T53" t="n">
         <v>22</v>
@@ -5227,7 +5227,7 @@
         <v>14.96708583831787</v>
       </c>
       <c r="E54" t="n">
-        <v>0.03794034263269151</v>
+        <v>0.2472571531931558</v>
       </c>
       <c r="F54" t="n">
         <v>-0.01892950146255348</v>
@@ -5275,7 +5275,7 @@
         </is>
       </c>
       <c r="S54" s="1" t="n">
-        <v>43532</v>
+        <v>25569.04217050926</v>
       </c>
       <c r="T54" t="n">
         <v>12</v>
@@ -5316,7 +5316,7 @@
         <v>21.18467903137207</v>
       </c>
       <c r="E55" t="n">
-        <v>0.04355719768315625</v>
+        <v>0.8421460027280061</v>
       </c>
       <c r="F55" t="n">
         <v>-0.2330435397973849</v>
@@ -5366,7 +5366,7 @@
         </is>
       </c>
       <c r="S55" s="1" t="n">
-        <v>43663</v>
+        <v>25569.04217202546</v>
       </c>
       <c r="T55" t="n">
         <v>11.5</v>
@@ -5407,7 +5407,7 @@
         <v>39.16999816894531</v>
       </c>
       <c r="E56" t="n">
-        <v>0.04816695982093686</v>
+        <v>0.5065383911132812</v>
       </c>
       <c r="F56" t="n">
         <v>-0.07148326188282636</v>
@@ -5457,7 +5457,7 @@
         </is>
       </c>
       <c r="S56" s="1" t="n">
-        <v>43671</v>
+        <v>25569.04217211806</v>
       </c>
       <c r="T56" t="n">
         <v>26</v>
@@ -5548,7 +5548,7 @@
         </is>
       </c>
       <c r="S57" s="1" t="n">
-        <v>43789</v>
+        <v>25569.04217348379</v>
       </c>
       <c r="T57" t="n">
         <v>9</v>
@@ -5589,7 +5589,7 @@
         <v>24.60000038146973</v>
       </c>
       <c r="E58" t="n">
-        <v>0.0933333502875434</v>
+        <v>0.2947368621826174</v>
       </c>
       <c r="F58" t="n">
         <v>-0.05894311953066819</v>
@@ -5635,7 +5635,7 @@
         </is>
       </c>
       <c r="S58" s="1" t="n">
-        <v>43763</v>
+        <v>25569.04217318287</v>
       </c>
       <c r="T58" t="n">
         <v>19</v>
@@ -5676,7 +5676,7 @@
         <v>566</v>
       </c>
       <c r="E59" t="n">
-        <v>0.04814814814814815</v>
+        <v>50.45454545454545</v>
       </c>
       <c r="F59" t="n">
         <v>-0.2261484098939929</v>
@@ -5726,7 +5726,7 @@
         </is>
       </c>
       <c r="S59" s="1" t="n">
-        <v>43588</v>
+        <v>25569.04217115741</v>
       </c>
       <c r="T59" t="n">
         <v>11</v>
@@ -5767,7 +5767,7 @@
         <v>6.050000190734863</v>
       </c>
       <c r="E60" t="n">
-        <v>0.02542374456658211</v>
+        <v>0.1000000346790661</v>
       </c>
       <c r="F60" t="n">
         <v>0.03884291723447068</v>
@@ -5811,7 +5811,7 @@
         </is>
       </c>
       <c r="S60" s="1" t="n">
-        <v>43755</v>
+        <v>25569.04217309028</v>
       </c>
       <c r="T60" t="n">
         <v>5.5</v>
@@ -5852,7 +5852,7 @@
         <v>34</v>
       </c>
       <c r="E61" t="n">
-        <v>0.351351359546894</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="F61" t="n">
         <v>0.01147057028377757</v>
@@ -5902,7 +5902,7 @@
         </is>
       </c>
       <c r="S61" s="1" t="n">
-        <v>43623</v>
+        <v>25569.0421715625</v>
       </c>
       <c r="T61" t="n">
         <v>18</v>
@@ -5943,7 +5943,7 @@
         <v>18.07999992370605</v>
       </c>
       <c r="E62" t="n">
-        <v>-0.03315512374000248</v>
+        <v>-0.04842105664704994</v>
       </c>
       <c r="F62" t="n">
         <v>-0.001659330020581009</v>
@@ -5993,7 +5993,7 @@
         </is>
       </c>
       <c r="S62" s="1" t="n">
-        <v>43503</v>
+        <v>25569.04217017361</v>
       </c>
       <c r="T62" t="n">
         <v>19</v>
@@ -6034,7 +6034,7 @@
         <v>14.02000045776367</v>
       </c>
       <c r="E63" t="n">
-        <v>-0.1318884960419858</v>
+        <v>-0.2989999771118165</v>
       </c>
       <c r="F63" t="n">
         <v>-0.08773184420472135</v>
@@ -6084,7 +6084,7 @@
         </is>
       </c>
       <c r="S63" s="1" t="n">
-        <v>43749</v>
+        <v>25569.04217302083</v>
       </c>
       <c r="T63" t="n">
         <v>20</v>
@@ -6125,7 +6125,7 @@
         <v>238.8000030517578</v>
       </c>
       <c r="E64" t="n">
-        <v>0.2797427397686388</v>
+        <v>14.92000020345052</v>
       </c>
       <c r="F64" t="n">
         <v>-0.2653266323309839</v>
@@ -6175,7 +6175,7 @@
         </is>
       </c>
       <c r="S64" s="1" t="n">
-        <v>43594</v>
+        <v>25569.04217122685</v>
       </c>
       <c r="T64" t="n">
         <v>15</v>
@@ -6216,7 +6216,7 @@
         <v>19.34255027770996</v>
       </c>
       <c r="E65" t="n">
-        <v>0.008550879384745325</v>
+        <v>0.1377970751594095</v>
       </c>
       <c r="F65" t="n">
         <v>0.008924899125506222</v>
@@ -6266,7 +6266,7 @@
         </is>
       </c>
       <c r="S65" s="1" t="n">
-        <v>43545</v>
+        <v>25569.04217065972</v>
       </c>
       <c r="T65" t="n">
         <v>17</v>
@@ -6307,7 +6307,7 @@
         <v>17.11000061035156</v>
       </c>
       <c r="E66" t="n">
-        <v>0.01845246353387667</v>
+        <v>0.2221429007393971</v>
       </c>
       <c r="F66" t="n">
         <v>-0.1198129817420703</v>
@@ -6357,7 +6357,7 @@
         </is>
       </c>
       <c r="S66" s="1" t="n">
-        <v>43727</v>
+        <v>25569.0421727662</v>
       </c>
       <c r="T66" t="n">
         <v>14</v>
@@ -6398,7 +6398,7 @@
         <v>34.9900016784668</v>
       </c>
       <c r="E67" t="n">
-        <v>-0.02805550893147786</v>
+        <v>0.5904546217484907</v>
       </c>
       <c r="F67" t="n">
         <v>-0.02372111435380351</v>
@@ -6448,7 +6448,7 @@
         </is>
       </c>
       <c r="S67" s="1" t="n">
-        <v>43630</v>
+        <v>25569.04217164352</v>
       </c>
       <c r="T67" t="n">
         <v>22</v>
@@ -6489,7 +6489,7 @@
         <v>62</v>
       </c>
       <c r="E68" t="n">
-        <v>-0.04615384615384616</v>
+        <v>0.7222222222222222</v>
       </c>
       <c r="F68" t="n">
         <v>0.2241935729980469</v>
@@ -6539,7 +6539,7 @@
         </is>
       </c>
       <c r="S68" s="1" t="n">
-        <v>43573</v>
+        <v>25569.0421709838</v>
       </c>
       <c r="T68" t="n">
         <v>36</v>
@@ -6580,7 +6580,7 @@
         <v>58</v>
       </c>
       <c r="E69" t="n">
-        <v>-0.08661417322834646</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="F69" t="n">
         <v>0.5910344617120151</v>
@@ -6630,7 +6630,7 @@
         </is>
       </c>
       <c r="S69" s="1" t="n">
-        <v>43628</v>
+        <v>25569.04217162037</v>
       </c>
       <c r="T69" t="n">
         <v>34</v>
@@ -6671,7 +6671,7 @@
         <v>14.05385398864746</v>
       </c>
       <c r="E70" t="n">
-        <v>-0.1369697108413235</v>
+        <v>-0.06307640075683606</v>
       </c>
       <c r="F70" t="n">
         <v>0.3820225298567492</v>
@@ -6717,7 +6717,7 @@
         </is>
       </c>
       <c r="S70" s="1" t="n">
-        <v>43748</v>
+        <v>25569.04217300926</v>
       </c>
       <c r="T70" t="n">
         <v>15</v>
@@ -6758,7 +6758,7 @@
         <v>16.46999931335449</v>
       </c>
       <c r="E71" t="n">
-        <v>-0.03117651097914752</v>
+        <v>-0.03117651097914773</v>
       </c>
       <c r="F71" t="n">
         <v>-0.1311474792829156</v>
@@ -6808,7 +6808,7 @@
         </is>
       </c>
       <c r="S71" s="1" t="n">
-        <v>43594</v>
+        <v>25569.04217122685</v>
       </c>
       <c r="T71" t="n">
         <v>17</v>
@@ -6849,7 +6849,7 @@
         <v>22.36000061035156</v>
       </c>
       <c r="E72" t="n">
-        <v>0.1041975610050154</v>
+        <v>0.3975000381469724</v>
       </c>
       <c r="F72" t="n">
         <v>0.1636851407650549</v>
@@ -6899,7 +6899,7 @@
         </is>
       </c>
       <c r="S72" s="1" t="n">
-        <v>43587</v>
+        <v>25569.04217114583</v>
       </c>
       <c r="T72" t="n">
         <v>16</v>
@@ -6940,7 +6940,7 @@
         <v>40.5</v>
       </c>
       <c r="E73" t="n">
-        <v>0.0125</v>
+        <v>0.7608695652173914</v>
       </c>
       <c r="F73" t="n">
         <v>0.02345680896146798</v>
@@ -6990,7 +6990,7 @@
         </is>
       </c>
       <c r="S73" s="1" t="n">
-        <v>44176</v>
+        <v>25569.04217796296</v>
       </c>
       <c r="T73" t="n">
         <v>23</v>
@@ -7031,7 +7031,7 @@
         <v>27</v>
       </c>
       <c r="E74" t="n">
-        <v>0.03053432113605758</v>
+        <v>0.35</v>
       </c>
       <c r="F74" t="n">
         <v>-0.05037039297598379</v>
@@ -7081,7 +7081,7 @@
         </is>
       </c>
       <c r="S74" s="1" t="n">
-        <v>43972</v>
+        <v>25569.04217560185</v>
       </c>
       <c r="T74" t="n">
         <v>20</v>
@@ -7122,7 +7122,7 @@
         <v>28.89999961853027</v>
       </c>
       <c r="E75" t="n">
-        <v>0.02445943128149221</v>
+        <v>0.6999999775606041</v>
       </c>
       <c r="F75" t="n">
         <v>-0.2221453342918915</v>
@@ -7172,7 +7172,7 @@
         </is>
       </c>
       <c r="S75" s="1" t="n">
-        <v>43874</v>
+        <v>25569.04217446759</v>
       </c>
       <c r="T75" t="n">
         <v>17</v>
@@ -7213,7 +7213,7 @@
         <v>38.08000183105469</v>
       </c>
       <c r="E76" t="n">
-        <v>0.2735786728055651</v>
+        <v>0.6556522535241168</v>
       </c>
       <c r="F76" t="n">
         <v>-0.114495808842003</v>
@@ -7263,7 +7263,7 @@
         </is>
       </c>
       <c r="S76" s="1" t="n">
-        <v>44176</v>
+        <v>25569.04217796296</v>
       </c>
       <c r="T76" t="n">
         <v>23</v>
@@ -7304,7 +7304,7 @@
         <v>211.3999938964844</v>
       </c>
       <c r="E77" t="n">
-        <v>0.006666637602306548</v>
+        <v>19.13333275204613</v>
       </c>
       <c r="F77" t="n">
         <v>0.2119206225355142</v>
@@ -7354,7 +7354,7 @@
         </is>
       </c>
       <c r="S77" s="1" t="n">
-        <v>44169</v>
+        <v>25569.04217788194</v>
       </c>
       <c r="T77" t="n">
         <v>10.5</v>
@@ -7395,7 +7395,7 @@
         <v>16.38999938964844</v>
       </c>
       <c r="E78" t="n">
-        <v>-0.0347467708182391</v>
+        <v>-0.2195238385881695</v>
       </c>
       <c r="F78" t="n">
         <v>0.135448523695811</v>
@@ -7445,7 +7445,7 @@
         </is>
       </c>
       <c r="S78" s="1" t="n">
-        <v>44048</v>
+        <v>25569.04217648148</v>
       </c>
       <c r="T78" t="n">
         <v>21</v>
@@ -7486,7 +7486,7 @@
         <v>23.84000015258789</v>
       </c>
       <c r="E79" t="n">
-        <v>0.1703485110649157</v>
+        <v>0.4023529501522289</v>
       </c>
       <c r="F79" t="n">
         <v>0.123322169263429</v>
@@ -7536,7 +7536,7 @@
         </is>
       </c>
       <c r="S79" s="1" t="n">
-        <v>43959</v>
+        <v>25569.04217545139</v>
       </c>
       <c r="T79" t="n">
         <v>17</v>
@@ -7577,7 +7577,7 @@
         <v>16.97999954223633</v>
       </c>
       <c r="E80" t="n">
-        <v>-0.06446281547573322</v>
+        <v>0.2577777438693579</v>
       </c>
       <c r="F80" t="n">
         <v>-0.02826852503984876</v>
@@ -7621,7 +7621,7 @@
         </is>
       </c>
       <c r="S80" s="1" t="n">
-        <v>44176</v>
+        <v>25569.04217796296</v>
       </c>
       <c r="T80" t="n">
         <v>13.5</v>
@@ -7662,7 +7662,7 @@
         <v>371.25</v>
       </c>
       <c r="E81" t="n">
-        <v>-0.146551724137931</v>
+        <v>23.75</v>
       </c>
       <c r="F81" t="n">
         <v>0.25993265993266</v>
@@ -7712,7 +7712,7 @@
         </is>
       </c>
       <c r="S81" s="1" t="n">
-        <v>44120</v>
+        <v>25569.04217731482</v>
       </c>
       <c r="T81" t="n">
         <v>15</v>
@@ -7753,7 +7753,7 @@
         <v>23.20000076293945</v>
       </c>
       <c r="E82" t="n">
-        <v>-0.07199996948242188</v>
+        <v>0.2888889312744138</v>
       </c>
       <c r="F82" t="n">
         <v>0.7090517337058583</v>
@@ -7799,7 +7799,7 @@
         </is>
       </c>
       <c r="S82" s="1" t="n">
-        <v>43924</v>
+        <v>25569.0421750463</v>
       </c>
       <c r="T82" t="n">
         <v>18</v>
@@ -7840,7 +7840,7 @@
         <v>13.42000007629395</v>
       </c>
       <c r="E83" t="n">
-        <v>-0.1130204907609256</v>
+        <v>-0.06805555025736457</v>
       </c>
       <c r="F83" t="n">
         <v>-0.1140089213318183</v>
@@ -7884,7 +7884,7 @@
         </is>
       </c>
       <c r="S83" s="1" t="n">
-        <v>44022</v>
+        <v>25569.04217618056</v>
       </c>
       <c r="T83" t="n">
         <v>14.4</v>
@@ -7925,7 +7925,7 @@
         <v>35.2599983215332</v>
       </c>
       <c r="E84" t="n">
-        <v>0.007428523472377232</v>
+        <v>0.6027271964333274</v>
       </c>
       <c r="F84" t="n">
         <v>0.03885430549624767</v>
@@ -7975,7 +7975,7 @@
         </is>
       </c>
       <c r="S84" s="1" t="n">
-        <v>44043</v>
+        <v>25569.04217642361</v>
       </c>
       <c r="T84" t="n">
         <v>22</v>
@@ -8016,7 +8016,7 @@
         <v>13.51000022888184</v>
       </c>
       <c r="E85" t="n">
-        <v>-0.02454874680312541</v>
+        <v>0.03923078683706457</v>
       </c>
       <c r="F85" t="n">
         <v>0.02442634479017824</v>
@@ -8062,7 +8062,7 @@
         </is>
       </c>
       <c r="S85" s="1" t="n">
-        <v>43847</v>
+        <v>25569.04217415509</v>
       </c>
       <c r="T85" t="n">
         <v>13</v>
@@ -8103,7 +8103,7 @@
         <v>31.86000061035156</v>
       </c>
       <c r="E86" t="n">
-        <v>0.3852174178413723</v>
+        <v>0.6768421373869241</v>
       </c>
       <c r="F86" t="n">
         <v>0.202134290751287</v>
@@ -8153,7 +8153,7 @@
         </is>
       </c>
       <c r="S86" s="1" t="n">
-        <v>44132</v>
+        <v>25569.0421774537</v>
       </c>
       <c r="T86" t="n">
         <v>19</v>
@@ -8194,7 +8194,7 @@
         <v>58.90000152587891</v>
       </c>
       <c r="E87" t="n">
-        <v>-0.03442620449378842</v>
+        <v>1.945000076293946</v>
       </c>
       <c r="F87" t="n">
         <v>-0.3168081386078311</v>
@@ -8244,7 +8244,7 @@
         </is>
       </c>
       <c r="S87" s="1" t="n">
-        <v>44176</v>
+        <v>25569.04217796296</v>
       </c>
       <c r="T87" t="n">
         <v>20</v>
@@ -8285,7 +8285,7 @@
         <v>13.81010723114014</v>
       </c>
       <c r="E88" t="n">
-        <v>-0.01388888888888889</v>
+        <v>-0.2327718204922144</v>
       </c>
       <c r="F88" t="n">
         <v>-0.006325898437443352</v>
@@ -8335,7 +8335,7 @@
         </is>
       </c>
       <c r="S88" s="1" t="n">
-        <v>44056</v>
+        <v>25569.04217657408</v>
       </c>
       <c r="T88" t="n">
         <v>18</v>
@@ -8376,7 +8376,7 @@
         <v>150</v>
       </c>
       <c r="E89" t="n">
-        <v>0.08695652173913043</v>
+        <v>27.68068833652008</v>
       </c>
       <c r="F89" t="n">
         <v>-0.04400004069010417</v>
@@ -8426,7 +8426,7 @@
         </is>
       </c>
       <c r="S89" s="1" t="n">
-        <v>44008</v>
+        <v>25569.04217601852</v>
       </c>
       <c r="T89" t="n">
         <v>5.23</v>
@@ -8467,7 +8467,7 @@
         <v>256.2000122070312</v>
       </c>
       <c r="E90" t="n">
-        <v>-0.05739505624194535</v>
+        <v>13.23333401150173</v>
       </c>
       <c r="F90" t="n">
         <v>0.2248242499668261</v>
@@ -8517,7 +8517,7 @@
         </is>
       </c>
       <c r="S90" s="1" t="n">
-        <v>44132</v>
+        <v>25569.0421774537</v>
       </c>
       <c r="T90" t="n">
         <v>18</v>
@@ -8558,7 +8558,7 @@
         <v>12.54675769805908</v>
       </c>
       <c r="E91" t="n">
-        <v>0.07355366624710255</v>
+        <v>-0.03486479245699382</v>
       </c>
       <c r="F91" t="n">
         <v>0.283294475947477</v>
@@ -8608,7 +8608,7 @@
         </is>
       </c>
       <c r="S91" s="1" t="n">
-        <v>44106</v>
+        <v>25569.04217715278</v>
       </c>
       <c r="T91" t="n">
         <v>13</v>
@@ -8649,7 +8649,7 @@
         <v>444</v>
       </c>
       <c r="E92" t="n">
-        <v>-0.003143228369261604</v>
+        <v>23.66666666666667</v>
       </c>
       <c r="F92" t="n">
         <v>-0.1531531531531531</v>
@@ -8695,7 +8695,7 @@
         </is>
       </c>
       <c r="S92" s="1" t="n">
-        <v>43889</v>
+        <v>25569.0421746412</v>
       </c>
       <c r="T92" t="n">
         <v>18</v>
@@ -8736,7 +8736,7 @@
         <v>29.46999931335449</v>
       </c>
       <c r="E93" t="n">
-        <v>0.1334615120520959</v>
+        <v>0.4734999656677245</v>
       </c>
       <c r="F93" t="n">
         <v>0.382762163198759</v>
@@ -8786,7 +8786,7 @@
         </is>
       </c>
       <c r="S93" s="1" t="n">
-        <v>44181</v>
+        <v>25569.04217802083</v>
       </c>
       <c r="T93" t="n">
         <v>20</v>
@@ -8827,7 +8827,7 @@
         <v>21.973388671875</v>
       </c>
       <c r="E94" t="n">
-        <v>0.01010101010101009</v>
+        <v>0.2207438151041667</v>
       </c>
       <c r="F94" t="n">
         <v>0.01599998750041665</v>
@@ -8877,7 +8877,7 @@
         </is>
       </c>
       <c r="S94" s="1" t="n">
-        <v>44090</v>
+        <v>25569.04217696759</v>
       </c>
       <c r="T94" t="n">
         <v>18</v>
@@ -8918,7 +8918,7 @@
         <v>246.3000030517578</v>
       </c>
       <c r="E95" t="n">
-        <v>0.08026317127963953</v>
+        <v>13.92727291222775</v>
       </c>
       <c r="F95" t="n">
         <v>0.09703617076387554</v>
@@ -8968,7 +8968,7 @@
         </is>
       </c>
       <c r="S95" s="1" t="n">
-        <v>43994</v>
+        <v>25569.04217585648</v>
       </c>
       <c r="T95" t="n">
         <v>16.5</v>
@@ -9009,7 +9009,7 @@
         <v>21.70000076293945</v>
       </c>
       <c r="E96" t="n">
-        <v>0.06686335300634338</v>
+        <v>0.2055555979410805</v>
       </c>
       <c r="F96" t="n">
         <v>0.8202764336976632</v>
@@ -9059,7 +9059,7 @@
         </is>
       </c>
       <c r="S96" s="1" t="n">
-        <v>44064</v>
+        <v>25569.04217666667</v>
       </c>
       <c r="T96" t="n">
         <v>18</v>
@@ -9100,7 +9100,7 @@
         <v>21.21999931335449</v>
       </c>
       <c r="E97" t="n">
-        <v>-0.08138532628005178</v>
+        <v>0.4146666208902993</v>
       </c>
       <c r="F97" t="n">
         <v>-0.05749290069895072</v>
@@ -9150,7 +9150,7 @@
         </is>
       </c>
       <c r="S97" s="1" t="n">
-        <v>44070</v>
+        <v>25569.04217673611</v>
       </c>
       <c r="T97" t="n">
         <v>15</v>
@@ -9191,7 +9191,7 @@
         <v>28.63999938964844</v>
       </c>
       <c r="E98" t="n">
-        <v>0.1015384380634014</v>
+        <v>0.6847058464499083</v>
       </c>
       <c r="F98" t="n">
         <v>0.3460195551189136</v>
@@ -9241,7 +9241,7 @@
         </is>
       </c>
       <c r="S98" s="1" t="n">
-        <v>43867</v>
+        <v>25569.04217438657</v>
       </c>
       <c r="T98" t="n">
         <v>17</v>
@@ -9282,7 +9282,7 @@
         <v>56.45999908447266</v>
       </c>
       <c r="E99" t="n">
-        <v>0.1762499809265137</v>
+        <v>1.971578899182772</v>
       </c>
       <c r="F99" t="n">
         <v>-0.005667724052659849</v>
@@ -9332,7 +9332,7 @@
         </is>
       </c>
       <c r="S99" s="1" t="n">
-        <v>44169</v>
+        <v>25569.04217788194</v>
       </c>
       <c r="T99" t="n">
         <v>19</v>
@@ -9373,7 +9373,7 @@
         <v>30</v>
       </c>
       <c r="E100" t="n">
-        <v>0</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="F100" t="n">
         <v>0.5603333791097005</v>
@@ -9419,7 +9419,7 @@
         </is>
       </c>
       <c r="S100" s="1" t="n">
-        <v>43969</v>
+        <v>25569.04217556713</v>
       </c>
       <c r="T100" t="n">
         <v>19</v>
@@ -9460,7 +9460,7 @@
         <v>37.0099983215332</v>
       </c>
       <c r="E101" t="n">
-        <v>-0.07451871047402882</v>
+        <v>0.5420832633972168</v>
       </c>
       <c r="F101" t="n">
         <v>-0.1145635789262549</v>
@@ -9510,7 +9510,7 @@
         </is>
       </c>
       <c r="S101" s="1" t="n">
-        <v>44062</v>
+        <v>25569.04217664352</v>
       </c>
       <c r="T101" t="n">
         <v>24</v>
@@ -9551,7 +9551,7 @@
         <v>11.47353267669678</v>
       </c>
       <c r="E102" t="n">
-        <v>-0.01212125835996686</v>
+        <v>-0.3250863131354836</v>
       </c>
       <c r="F102" t="n">
         <v>0.02779399762494337</v>
@@ -9601,7 +9601,7 @@
         </is>
       </c>
       <c r="S102" s="1" t="n">
-        <v>44091</v>
+        <v>25569.04217697917</v>
       </c>
       <c r="T102" t="n">
         <v>17</v>
@@ -9642,7 +9642,7 @@
         <v>92.48999786376953</v>
       </c>
       <c r="E103" t="n">
-        <v>-0.07510002136230469</v>
+        <v>1.202142806280227</v>
       </c>
       <c r="F103" t="n">
         <v>0.5001622143441694</v>
@@ -9692,7 +9692,7 @@
         </is>
       </c>
       <c r="S103" s="1" t="n">
-        <v>44174</v>
+        <v>25569.04217793982</v>
       </c>
       <c r="T103" t="n">
         <v>42</v>
@@ -9733,7 +9733,7 @@
         <v>30</v>
       </c>
       <c r="E104" t="n">
-        <v>-0.2</v>
+        <v>0.5789473684210527</v>
       </c>
       <c r="F104" t="n">
         <v>0.475</v>
@@ -9783,7 +9783,7 @@
         </is>
       </c>
       <c r="S104" s="1" t="n">
-        <v>44029</v>
+        <v>25569.04217626157</v>
       </c>
       <c r="T104" t="n">
         <v>19</v>
@@ -9824,7 +9824,7 @@
         <v>60</v>
       </c>
       <c r="E105" t="n">
-        <v>0.07142857142857142</v>
+        <v>2.75</v>
       </c>
       <c r="F105" t="n">
         <v>0.06800003051757812</v>
@@ -9868,7 +9868,7 @@
         </is>
       </c>
       <c r="S105" s="1" t="n">
-        <v>43902</v>
+        <v>25569.04217479167</v>
       </c>
       <c r="T105" t="n">
         <v>16</v>
@@ -9909,7 +9909,7 @@
         <v>29.45000076293945</v>
       </c>
       <c r="E106" t="n">
-        <v>0.1723726026689972</v>
+        <v>0.4725000381469725</v>
       </c>
       <c r="F106" t="n">
         <v>-0.05059428318731484</v>
@@ -9959,7 +9959,7 @@
         </is>
       </c>
       <c r="S106" s="1" t="n">
-        <v>44174</v>
+        <v>25569.04217793982</v>
       </c>
       <c r="T106" t="n">
         <v>20</v>
@@ -10000,7 +10000,7 @@
         <v>25.48999977111816</v>
       </c>
       <c r="E107" t="n">
-        <v>-0.04172934565537896</v>
+        <v>0.3415789353220084</v>
       </c>
       <c r="F107" t="n">
         <v>0.01333857024875822</v>
@@ -10046,7 +10046,7 @@
         </is>
       </c>
       <c r="S107" s="1" t="n">
-        <v>44106</v>
+        <v>25569.04217715278</v>
       </c>
       <c r="T107" t="n">
         <v>19</v>
@@ -10087,7 +10087,7 @@
         <v>519.9000244140625</v>
       </c>
       <c r="E108" t="n">
-        <v>0.1302174443783967</v>
+        <v>24.99500122070312</v>
       </c>
       <c r="F108" t="n">
         <v>0.01134826524687246</v>
@@ -10137,7 +10137,7 @@
         </is>
       </c>
       <c r="S108" s="1" t="n">
-        <v>44175</v>
+        <v>25569.04217795139</v>
       </c>
       <c r="T108" t="n">
         <v>20</v>
@@ -10178,7 +10178,7 @@
         <v>253.9299926757812</v>
       </c>
       <c r="E109" t="n">
-        <v>0.03644894969706633</v>
+        <v>20.16083272298177</v>
       </c>
       <c r="F109" t="n">
         <v>0.07289414523497682</v>
@@ -10228,7 +10228,7 @@
         </is>
       </c>
       <c r="S109" s="1" t="n">
-        <v>44090</v>
+        <v>25569.04217696759</v>
       </c>
       <c r="T109" t="n">
         <v>12</v>
@@ -10269,7 +10269,7 @@
         <v>25.77000045776367</v>
       </c>
       <c r="E110" t="n">
-        <v>-0.008846136239858774</v>
+        <v>0.6106250286102293</v>
       </c>
       <c r="F110" t="n">
         <v>0.4695381551875663</v>
@@ -10315,7 +10315,7 @@
         </is>
       </c>
       <c r="S110" s="1" t="n">
-        <v>43945</v>
+        <v>25569.04217528935</v>
       </c>
       <c r="T110" t="n">
         <v>16</v>
@@ -10356,7 +10356,7 @@
         <v>39.31000137329102</v>
       </c>
       <c r="E111" t="n">
-        <v>-0.01724996566772461</v>
+        <v>1.068947440699527</v>
       </c>
       <c r="F111" t="n">
         <v>0.1765453671905576</v>
@@ -10406,7 +10406,7 @@
         </is>
       </c>
       <c r="S111" s="1" t="n">
-        <v>44105</v>
+        <v>25569.0421771412</v>
       </c>
       <c r="T111" t="n">
         <v>19</v>
@@ -10447,7 +10447,7 @@
         <v>34.74870681762695</v>
       </c>
       <c r="E112" t="n">
-        <v>0.06788354706771532</v>
+        <v>0.7374353408813477</v>
       </c>
       <c r="F112" t="n">
         <v>0.5216346393988911</v>
@@ -10497,7 +10497,7 @@
         </is>
       </c>
       <c r="S112" s="1" t="n">
-        <v>44056</v>
+        <v>25569.04217657408</v>
       </c>
       <c r="T112" t="n">
         <v>20</v>
@@ -10538,7 +10538,7 @@
         <v>19.01000022888184</v>
       </c>
       <c r="E113" t="n">
-        <v>0.05260248012359958</v>
+        <v>0.0005263278358862889</v>
       </c>
       <c r="F113" t="n">
         <v>0.3298264272631454</v>
@@ -10588,7 +10588,7 @@
         </is>
       </c>
       <c r="S113" s="1" t="n">
-        <v>44036</v>
+        <v>25569.04217634259</v>
       </c>
       <c r="T113" t="n">
         <v>19</v>
@@ -10629,7 +10629,7 @@
         <v>417</v>
       </c>
       <c r="E114" t="n">
-        <v>0.07170391534011412</v>
+        <v>20.94736842105263</v>
       </c>
       <c r="F114" t="n">
         <v>0.4913669650217326</v>
@@ -10675,7 +10675,7 @@
         </is>
       </c>
       <c r="S114" s="1" t="n">
-        <v>44120</v>
+        <v>25569.04217731482</v>
       </c>
       <c r="T114" t="n">
         <v>19</v>
@@ -10716,7 +10716,7 @@
         <v>20.29000091552734</v>
       </c>
       <c r="E115" t="n">
-        <v>-0.07351592379210178</v>
+        <v>0.1935294656192553</v>
       </c>
       <c r="F115" t="n">
         <v>0.6254311510157547</v>
@@ -10766,7 +10766,7 @@
         </is>
       </c>
       <c r="S115" s="1" t="n">
-        <v>44154</v>
+        <v>25569.04217770833</v>
       </c>
       <c r="T115" t="n">
         <v>17</v>
@@ -10807,7 +10807,7 @@
         <v>49</v>
       </c>
       <c r="E116" t="n">
-        <v>0.07668648224967065</v>
+        <v>1.45</v>
       </c>
       <c r="F116" t="n">
         <v>0.1622449135293766</v>
@@ -10857,7 +10857,7 @@
         </is>
       </c>
       <c r="S116" s="1" t="n">
-        <v>44183</v>
+        <v>25569.04217804398</v>
       </c>
       <c r="T116" t="n">
         <v>20</v>
@@ -10898,7 +10898,7 @@
         <v>18.80436515808105</v>
       </c>
       <c r="E117" t="n">
-        <v>-0.1442623160981712</v>
+        <v>-0.05978174209594744</v>
       </c>
       <c r="F117" t="n">
         <v>-0.03735638741957396</v>
@@ -10948,7 +10948,7 @@
         </is>
       </c>
       <c r="S117" s="1" t="n">
-        <v>44119</v>
+        <v>25569.04217730324</v>
       </c>
       <c r="T117" t="n">
         <v>20</v>
@@ -10989,7 +10989,7 @@
         <v>144.7100067138672</v>
       </c>
       <c r="E118" t="n">
-        <v>-0.008835570452964469</v>
+        <v>1.128088334027459</v>
       </c>
       <c r="F118" t="n">
         <v>0.01444265248375768</v>
@@ -11039,7 +11039,7 @@
         </is>
       </c>
       <c r="S118" s="1" t="n">
-        <v>44175</v>
+        <v>25569.04217795139</v>
       </c>
       <c r="T118" t="n">
         <v>68</v>
@@ -11080,7 +11080,7 @@
         <v>49</v>
       </c>
       <c r="E119" t="n">
-        <v>0.08888888888888889</v>
+        <v>1.578947368421053</v>
       </c>
       <c r="F119" t="n">
         <v>-0.01877547283561862</v>
@@ -11126,7 +11126,7 @@
         </is>
       </c>
       <c r="S119" s="1" t="n">
-        <v>44154</v>
+        <v>25569.04217770833</v>
       </c>
       <c r="T119" t="n">
         <v>19</v>
@@ -11167,7 +11167,7 @@
         <v>14.33684539794922</v>
       </c>
       <c r="E120" t="n">
-        <v>0.3201320256664291</v>
+        <v>0.1947371164957684</v>
       </c>
       <c r="F120" t="n">
         <v>0.6124999268289698</v>
@@ -11217,7 +11217,7 @@
         </is>
       </c>
       <c r="S120" s="1" t="n">
-        <v>44113</v>
+        <v>25569.0421772338</v>
       </c>
       <c r="T120" t="n">
         <v>12</v>
@@ -11258,7 +11258,7 @@
         <v>18.75</v>
       </c>
       <c r="E121" t="n">
-        <v>-0.21875</v>
+        <v>0.1029411764705882</v>
       </c>
       <c r="F121" t="n">
         <v>0.03466664632161458</v>
@@ -11308,7 +11308,7 @@
         </is>
       </c>
       <c r="S121" s="1" t="n">
-        <v>43867</v>
+        <v>25569.04217438657</v>
       </c>
       <c r="T121" t="n">
         <v>17</v>
@@ -11349,7 +11349,7 @@
         <v>20.07999992370605</v>
       </c>
       <c r="E122" t="n">
-        <v>-0.0369304769149071</v>
+        <v>0.2549999952316282</v>
       </c>
       <c r="F122" t="n">
         <v>0.3605577588957439</v>
@@ -11399,7 +11399,7 @@
         </is>
       </c>
       <c r="S122" s="1" t="n">
-        <v>43929</v>
+        <v>25569.04217510416</v>
       </c>
       <c r="T122" t="n">
         <v>16</v>
@@ -11440,7 +11440,7 @@
         <v>47.90000152587891</v>
       </c>
       <c r="E123" t="n">
-        <v>-0.1202938318693046</v>
+        <v>1.661111195882162</v>
       </c>
       <c r="F123" t="n">
         <v>-0.4582463478854075</v>
@@ -11490,7 +11490,7 @@
         </is>
       </c>
       <c r="S123" s="1" t="n">
-        <v>44022</v>
+        <v>25569.04217618056</v>
       </c>
       <c r="T123" t="n">
         <v>18</v>
@@ -11531,7 +11531,7 @@
         <v>7</v>
       </c>
       <c r="E124" t="n">
-        <v>-0.282051282051282</v>
+        <v>-0.06666666666666667</v>
       </c>
       <c r="F124" t="n">
         <v>0.3157142911638532</v>
@@ -11581,7 +11581,7 @@
         </is>
       </c>
       <c r="S124" s="1" t="n">
-        <v>44104</v>
+        <v>25569.04217712963</v>
       </c>
       <c r="T124" t="n">
         <v>7.5</v>
@@ -11622,7 +11622,7 @@
         <v>26.14999961853027</v>
       </c>
       <c r="E125" t="n">
-        <v>0.2572115662358932</v>
+        <v>0.6343749761581419</v>
       </c>
       <c r="F125" t="n">
         <v>0.1992352224789099</v>
@@ -11668,7 +11668,7 @@
         </is>
       </c>
       <c r="S125" s="1" t="n">
-        <v>43994</v>
+        <v>25569.04217585648</v>
       </c>
       <c r="T125" t="n">
         <v>16</v>
@@ -11709,7 +11709,7 @@
         <v>32.71664428710938</v>
       </c>
       <c r="E126" t="n">
-        <v>0.1960714885166712</v>
+        <v>0.4871201948686083</v>
       </c>
       <c r="F126" t="n">
         <v>0.05733056669455693</v>
@@ -11759,7 +11759,7 @@
         </is>
       </c>
       <c r="S126" s="1" t="n">
-        <v>44097</v>
+        <v>25569.04217704861</v>
       </c>
       <c r="T126" t="n">
         <v>22</v>
@@ -11800,7 +11800,7 @@
         <v>19.35000038146973</v>
       </c>
       <c r="E127" t="n">
-        <v>-0.1204545281150124</v>
+        <v>0.1382353165570429</v>
       </c>
       <c r="F127" t="n">
         <v>0.6837209916674988</v>
@@ -11850,7 +11850,7 @@
         </is>
       </c>
       <c r="S127" s="1" t="n">
-        <v>44113</v>
+        <v>25569.0421772338</v>
       </c>
       <c r="T127" t="n">
         <v>17</v>
@@ -11891,7 +11891,7 @@
         <v>35.04999923706055</v>
       </c>
       <c r="E128" t="n">
-        <v>0.005883139881643124</v>
+        <v>0.7524999618530274</v>
       </c>
       <c r="F128" t="n">
         <v>0.03651933300588247</v>
@@ -11941,7 +11941,7 @@
         </is>
       </c>
       <c r="S128" s="1" t="n">
-        <v>44028</v>
+        <v>25569.04217625</v>
       </c>
       <c r="T128" t="n">
         <v>20</v>
@@ -11982,7 +11982,7 @@
         <v>37.5</v>
       </c>
       <c r="E129" t="n">
-        <v>0.01241898145525754</v>
+        <v>0.9736842105263158</v>
       </c>
       <c r="F129" t="n">
         <v>-0.4717333475748698</v>
@@ -12032,7 +12032,7 @@
         </is>
       </c>
       <c r="S129" s="1" t="n">
-        <v>43861</v>
+        <v>25569.04217431713</v>
       </c>
       <c r="T129" t="n">
         <v>19</v>
@@ -12073,7 +12073,7 @@
         <v>23.93000030517578</v>
       </c>
       <c r="E130" t="n">
-        <v>-0.06377148649547143</v>
+        <v>0.2594737002724095</v>
       </c>
       <c r="F130" t="n">
         <v>-0.01755119393805876</v>
@@ -12123,7 +12123,7 @@
         </is>
       </c>
       <c r="S130" s="1" t="n">
-        <v>44041</v>
+        <v>25569.04217640046</v>
       </c>
       <c r="T130" t="n">
         <v>19</v>
@@ -12164,7 +12164,7 @@
         <v>30.34000015258789</v>
       </c>
       <c r="E131" t="n">
-        <v>0.122456506912992</v>
+        <v>0.2641666730244954</v>
       </c>
       <c r="F131" t="n">
         <v>0.02307187737043388</v>
@@ -12214,7 +12214,7 @@
         </is>
       </c>
       <c r="S131" s="1" t="n">
-        <v>44134</v>
+        <v>25569.04217747685</v>
       </c>
       <c r="T131" t="n">
         <v>24</v>
@@ -12255,7 +12255,7 @@
         <v>16.45999908447266</v>
       </c>
       <c r="E132" t="n">
-        <v>0.06262100243300854</v>
+        <v>0.4313042682150139</v>
       </c>
       <c r="F132" t="n">
         <v>-0.01518833620324041</v>
@@ -12305,7 +12305,7 @@
         </is>
       </c>
       <c r="S132" s="1" t="n">
-        <v>44042</v>
+        <v>25569.04217641204</v>
       </c>
       <c r="T132" t="n">
         <v>11.5</v>
@@ -12346,7 +12346,7 @@
         <v>189.5099945068359</v>
       </c>
       <c r="E133" t="n">
-        <v>0.04126370608151614</v>
+        <v>0.8579411226160383</v>
       </c>
       <c r="F133" t="n">
         <v>-0.2467415749154551</v>
@@ -12396,7 +12396,7 @@
         </is>
       </c>
       <c r="S133" s="1" t="n">
-        <v>44174</v>
+        <v>25569.04217793982</v>
       </c>
       <c r="T133" t="n">
         <v>102</v>
@@ -12437,7 +12437,7 @@
         <v>50</v>
       </c>
       <c r="E134" t="n">
-        <v>-0.06103286384976526</v>
+        <v>3.761904761904762</v>
       </c>
       <c r="F134" t="n">
         <v>-0.06</v>
@@ -12487,7 +12487,7 @@
         </is>
       </c>
       <c r="S134" s="1" t="n">
-        <v>43873</v>
+        <v>25569.04217445602</v>
       </c>
       <c r="T134" t="n">
         <v>10.5</v>
@@ -12528,7 +12528,7 @@
         <v>20.57999992370605</v>
       </c>
       <c r="E135" t="n">
-        <v>0.2703703058327425</v>
+        <v>0.2862499952316282</v>
       </c>
       <c r="F135" t="n">
         <v>0.174441213114514</v>
@@ -12578,7 +12578,7 @@
         </is>
       </c>
       <c r="S135" s="1" t="n">
-        <v>44120</v>
+        <v>25569.04217731482</v>
       </c>
       <c r="T135" t="n">
         <v>16</v>
@@ -12619,7 +12619,7 @@
         <v>434</v>
       </c>
       <c r="E136" t="n">
-        <v>0.04983068797208033</v>
+        <v>24.52941176470588</v>
       </c>
       <c r="F136" t="n">
         <v>-0.06405527141237038</v>
@@ -12669,7 +12669,7 @@
         </is>
       </c>
       <c r="S136" s="1" t="n">
-        <v>44133</v>
+        <v>25569.04217746528</v>
       </c>
       <c r="T136" t="n">
         <v>17</v>
@@ -12710,7 +12710,7 @@
         <v>1551</v>
       </c>
       <c r="E137" t="n">
-        <v>0.01538461538461539</v>
+        <v>85.16666666666667</v>
       </c>
       <c r="F137" t="n">
         <v>0.09638942617666021</v>
@@ -12756,7 +12756,7 @@
         </is>
       </c>
       <c r="S137" s="1" t="n">
-        <v>44181</v>
+        <v>25569.04217802083</v>
       </c>
       <c r="T137" t="n">
         <v>18</v>
@@ -12797,7 +12797,7 @@
         <v>486</v>
       </c>
       <c r="E138" t="n">
-        <v>0.03846153846153846</v>
+        <v>17</v>
       </c>
       <c r="F138" t="n">
         <v>-0.4807407394848733</v>
@@ -12847,7 +12847,7 @@
         </is>
       </c>
       <c r="S138" s="1" t="n">
-        <v>44132</v>
+        <v>25569.0421774537</v>
       </c>
       <c r="T138" t="n">
         <v>27</v>
@@ -12888,7 +12888,7 @@
         <v>40.79999923706055</v>
       </c>
       <c r="E139" t="n">
-        <v>0.2160953849438955</v>
+        <v>0.8545454198663885</v>
       </c>
       <c r="F139" t="n">
         <v>0.1698529518324338</v>
@@ -12938,7 +12938,7 @@
         </is>
       </c>
       <c r="S139" s="1" t="n">
-        <v>44097</v>
+        <v>25569.04217704861</v>
       </c>
       <c r="T139" t="n">
         <v>22</v>
@@ -12979,7 +12979,7 @@
         <v>29</v>
       </c>
       <c r="E140" t="n">
-        <v>0.239316259519728</v>
+        <v>0.7058823529411765</v>
       </c>
       <c r="F140" t="n">
         <v>0.103448275862069</v>
@@ -13025,7 +13025,7 @@
         </is>
       </c>
       <c r="S140" s="1" t="n">
-        <v>44092</v>
+        <v>25569.04217699074</v>
       </c>
       <c r="T140" t="n">
         <v>17</v>
@@ -13066,7 +13066,7 @@
         <v>18.1200008392334</v>
       </c>
       <c r="E141" t="n">
-        <v>-0.04631574530350534</v>
+        <v>0.1325000524520874</v>
       </c>
       <c r="F141" t="n">
         <v>0.2130242011162199</v>
@@ -13116,7 +13116,7 @@
         </is>
       </c>
       <c r="S141" s="1" t="n">
-        <v>44127</v>
+        <v>25569.04217739583</v>
       </c>
       <c r="T141" t="n">
         <v>16</v>
@@ -13157,7 +13157,7 @@
         <v>21.29999923706055</v>
       </c>
       <c r="E142" t="n">
-        <v>-0.1480000305175781</v>
+        <v>0.3312499523162844</v>
       </c>
       <c r="F142" t="n">
         <v>0.1488262999924602</v>
@@ -13207,7 +13207,7 @@
         </is>
       </c>
       <c r="S142" s="1" t="n">
-        <v>43985</v>
+        <v>25569.04217575231</v>
       </c>
       <c r="T142" t="n">
         <v>16</v>
@@ -13248,7 +13248,7 @@
         <v>26.20000076293945</v>
       </c>
       <c r="E143" t="n">
-        <v>0.03844634317488958</v>
+        <v>0.3789474085757605</v>
       </c>
       <c r="F143" t="n">
         <v>0.6744273913892385</v>
@@ -13294,7 +13294,7 @@
         </is>
       </c>
       <c r="S143" s="1" t="n">
-        <v>44099</v>
+        <v>25569.04217707176</v>
       </c>
       <c r="T143" t="n">
         <v>19</v>
@@ -13335,7 +13335,7 @@
         <v>37</v>
       </c>
       <c r="E144" t="n">
-        <v>-0.0002701519045296981</v>
+        <v>0.6086956521739131</v>
       </c>
       <c r="F144" t="n">
         <v>-0.04540541365339949</v>
@@ -13381,7 +13381,7 @@
         </is>
       </c>
       <c r="S144" s="1" t="n">
-        <v>43987</v>
+        <v>25569.04217577546</v>
       </c>
       <c r="T144" t="n">
         <v>23</v>
@@ -13422,7 +13422,7 @@
         <v>21.79999923706055</v>
       </c>
       <c r="E145" t="n">
-        <v>-0.05464008057514255</v>
+        <v>0.2823528962976795</v>
       </c>
       <c r="F145" t="n">
         <v>-0.1293577886934119</v>
@@ -13472,7 +13472,7 @@
         </is>
       </c>
       <c r="S145" s="1" t="n">
-        <v>43861</v>
+        <v>25569.04217431713</v>
       </c>
       <c r="T145" t="n">
         <v>17</v>
@@ -13513,7 +13513,7 @@
         <v>29.85000038146973</v>
       </c>
       <c r="E146" t="n">
-        <v>-0.06572770990057789</v>
+        <v>0.1055555696840641</v>
       </c>
       <c r="F146" t="n">
         <v>-0.06030154510572749</v>
@@ -13563,7 +13563,7 @@
         </is>
       </c>
       <c r="S146" s="1" t="n">
-        <v>44155</v>
+        <v>25569.04217771991</v>
       </c>
       <c r="T146" t="n">
         <v>27</v>
@@ -13604,7 +13604,7 @@
         <v>14.50252628326416</v>
       </c>
       <c r="E147" t="n">
-        <v>0.007989339673891696</v>
+        <v>0.20854385693868</v>
       </c>
       <c r="F147" t="n">
         <v>-0.6684280154910228</v>
@@ -13654,7 +13654,7 @@
         </is>
       </c>
       <c r="S147" s="1" t="n">
-        <v>43868</v>
+        <v>25569.04217439815</v>
       </c>
       <c r="T147" t="n">
         <v>12</v>
@@ -13695,7 +13695,7 @@
         <v>37.5099983215332</v>
       </c>
       <c r="E148" t="n">
-        <v>0.07171423775809152</v>
+        <v>1.083888795640733</v>
       </c>
       <c r="F148" t="n">
         <v>-0.01359633016140208</v>
@@ -13741,7 +13741,7 @@
         </is>
       </c>
       <c r="S148" s="1" t="n">
-        <v>44099</v>
+        <v>25569.04217707176</v>
       </c>
       <c r="T148" t="n">
         <v>18</v>
@@ -13782,7 +13782,7 @@
         <v>33.2599983215332</v>
       </c>
       <c r="E149" t="n">
-        <v>-0.04998572076262132</v>
+        <v>0.6629999160766602</v>
       </c>
       <c r="F149" t="n">
         <v>-0.1560432618347089</v>
@@ -13832,7 +13832,7 @@
         </is>
       </c>
       <c r="S149" s="1" t="n">
-        <v>44064</v>
+        <v>25569.04217666667</v>
       </c>
       <c r="T149" t="n">
         <v>20</v>
@@ -13873,7 +13873,7 @@
         <v>50.5</v>
       </c>
       <c r="E150" t="n">
-        <v>0.08137043201241614</v>
+        <v>0.5303030303030303</v>
       </c>
       <c r="F150" t="n">
         <v>0</v>
@@ -13923,7 +13923,7 @@
         </is>
       </c>
       <c r="S150" s="1" t="n">
-        <v>44097</v>
+        <v>25569.04217704861</v>
       </c>
       <c r="T150" t="n">
         <v>33</v>
@@ -13964,7 +13964,7 @@
         <v>33.54000091552734</v>
       </c>
       <c r="E151" t="n">
-        <v>0.0132931257308142</v>
+        <v>0.4582609093707538</v>
       </c>
       <c r="F151" t="n">
         <v>0.1344662551707117</v>
@@ -14014,7 +14014,7 @@
         </is>
       </c>
       <c r="S151" s="1" t="n">
-        <v>43987</v>
+        <v>25569.04217577546</v>
       </c>
       <c r="T151" t="n">
         <v>23</v>
@@ -14055,7 +14055,7 @@
         <v>14.25</v>
       </c>
       <c r="E152" t="n">
-        <v>-0.05753967540634757</v>
+        <v>-0.1617647058823529</v>
       </c>
       <c r="F152" t="n">
         <v>0.8652631525407758</v>
@@ -14105,7 +14105,7 @@
         </is>
       </c>
       <c r="S152" s="1" t="n">
-        <v>44097</v>
+        <v>25569.04217704861</v>
       </c>
       <c r="T152" t="n">
         <v>17</v>
@@ -14146,7 +14146,7 @@
         <v>92</v>
       </c>
       <c r="E153" t="n">
-        <v>0.05082806160053973</v>
+        <v>7.761904761904762</v>
       </c>
       <c r="F153" t="n">
         <v>-0.07608695652173914</v>
@@ -14196,7 +14196,7 @@
         </is>
       </c>
       <c r="S153" s="1" t="n">
-        <v>44154</v>
+        <v>25569.04217770833</v>
       </c>
       <c r="T153" t="n">
         <v>10.5</v>
@@ -14237,7 +14237,7 @@
         <v>910.2000122070312</v>
       </c>
       <c r="E154" t="n">
-        <v>0.166923092573117</v>
+        <v>32.71111156322338</v>
       </c>
       <c r="F154" t="n">
         <v>-0.1914963584436022</v>
@@ -14287,7 +14287,7 @@
         </is>
       </c>
       <c r="S154" s="1" t="n">
-        <v>44089</v>
+        <v>25569.04217695602</v>
       </c>
       <c r="T154" t="n">
         <v>27</v>
@@ -14328,7 +14328,7 @@
         <v>25.10000038146973</v>
       </c>
       <c r="E155" t="n">
-        <v>-0.07037035624186198</v>
+        <v>0.0913043644117274</v>
       </c>
       <c r="F155" t="n">
         <v>0.09322709629579982</v>
@@ -14378,7 +14378,7 @@
         </is>
       </c>
       <c r="S155" s="1" t="n">
-        <v>44155</v>
+        <v>25569.04217771991</v>
       </c>
       <c r="T155" t="n">
         <v>23</v>
@@ -14419,7 +14419,7 @@
         <v>291.8999938964844</v>
       </c>
       <c r="E156" t="n">
-        <v>-0.2216000162760417</v>
+        <v>12.8999997093564</v>
       </c>
       <c r="F156" t="n">
         <v>-0.2826310439364269</v>
@@ -14469,7 +14469,7 @@
         </is>
       </c>
       <c r="S156" s="1" t="n">
-        <v>44027</v>
+        <v>25569.04217623842</v>
       </c>
       <c r="T156" t="n">
         <v>21</v>
@@ -14510,7 +14510,7 @@
         <v>570</v>
       </c>
       <c r="E157" t="n">
-        <v>0.1875</v>
+        <v>34.625</v>
       </c>
       <c r="F157" t="n">
         <v>-0.252105284573739</v>
@@ -14556,7 +14556,7 @@
         </is>
       </c>
       <c r="S157" s="1" t="n">
-        <v>44008</v>
+        <v>25569.04217601852</v>
       </c>
       <c r="T157" t="n">
         <v>16</v>
@@ -14597,7 +14597,7 @@
         <v>16.64971923828125</v>
       </c>
       <c r="E158" t="n">
-        <v>-0.04000004359654024</v>
+        <v>-0.1238142750542692</v>
       </c>
       <c r="F158" t="n">
         <v>-0.1154763846782678</v>
@@ -14643,7 +14643,7 @@
         </is>
       </c>
       <c r="S158" s="1" t="n">
-        <v>43893</v>
+        <v>25569.0421746875</v>
       </c>
       <c r="T158" t="n">
         <v>19.0025</v>
@@ -14684,7 +14684,7 @@
         <v>64.79000091552734</v>
       </c>
       <c r="E159" t="n">
-        <v>-0.09092179083425672</v>
+        <v>0.4725000208074396</v>
       </c>
       <c r="F159" t="n">
         <v>0.1489427595233483</v>
@@ -14734,7 +14734,7 @@
         </is>
       </c>
       <c r="S159" s="1" t="n">
-        <v>44090</v>
+        <v>25569.04217696759</v>
       </c>
       <c r="T159" t="n">
         <v>44</v>
@@ -14775,7 +14775,7 @@
         <v>17.70000076293945</v>
       </c>
       <c r="E160" t="n">
-        <v>-0.08762880871229681</v>
+        <v>0.2642857687813893</v>
       </c>
       <c r="F160" t="n">
         <v>0.473446259861908</v>
@@ -14825,7 +14825,7 @@
         </is>
       </c>
       <c r="S160" s="1" t="n">
-        <v>44133</v>
+        <v>25569.04217746528</v>
       </c>
       <c r="T160" t="n">
         <v>14</v>
@@ -14866,7 +14866,7 @@
         <v>15.39999961853027</v>
       </c>
       <c r="E161" t="n">
-        <v>-0.144444465637207</v>
+        <v>-0.1894737042878805</v>
       </c>
       <c r="F161" t="n">
         <v>-0.3662337356724364</v>
@@ -14912,7 +14912,7 @@
         </is>
       </c>
       <c r="S161" s="1" t="n">
-        <v>44050</v>
+        <v>25569.04217650463</v>
       </c>
       <c r="T161" t="n">
         <v>19</v>
@@ -14953,7 +14953,7 @@
         <v>50.5</v>
       </c>
       <c r="E162" t="n">
-        <v>0.1222222222222222</v>
+        <v>1.525</v>
       </c>
       <c r="F162" t="n">
         <v>-0.2574257425742574</v>
@@ -15003,7 +15003,7 @@
         </is>
       </c>
       <c r="S162" s="1" t="n">
-        <v>44008</v>
+        <v>25569.04217601852</v>
       </c>
       <c r="T162" t="n">
         <v>20</v>
@@ -15044,7 +15044,7 @@
         <v>461.3999938964844</v>
       </c>
       <c r="E163" t="n">
-        <v>-0.09564879879058996</v>
+        <v>24.63333299424913</v>
       </c>
       <c r="F163" t="n">
         <v>0.1811877052652744</v>
@@ -15094,7 +15094,7 @@
         </is>
       </c>
       <c r="S163" s="1" t="n">
-        <v>44091</v>
+        <v>25569.04217697917</v>
       </c>
       <c r="T163" t="n">
         <v>18</v>
@@ -15135,7 +15135,7 @@
         <v>17.76000022888184</v>
       </c>
       <c r="E164" t="n">
-        <v>0.02068969070368121</v>
+        <v>0.04470589581657879</v>
       </c>
       <c r="F164" t="n">
         <v>0.4127252156104025</v>
@@ -15181,7 +15181,7 @@
         </is>
       </c>
       <c r="S164" s="1" t="n">
-        <v>44036</v>
+        <v>25569.04217634259</v>
       </c>
       <c r="T164" t="n">
         <v>17</v>
@@ -15222,7 +15222,7 @@
         <v>18.90427017211914</v>
       </c>
       <c r="E165" t="n">
-        <v>0.1077586171459783</v>
+        <v>0.4003163090458623</v>
       </c>
       <c r="F165" t="n">
         <v>0.03190666959127992</v>
@@ -15272,7 +15272,7 @@
         </is>
       </c>
       <c r="S165" s="1" t="n">
-        <v>44134</v>
+        <v>25569.04217747685</v>
       </c>
       <c r="T165" t="n">
         <v>13.5</v>
@@ -15313,7 +15313,7 @@
         <v>24.05999946594238</v>
       </c>
       <c r="E166" t="n">
-        <v>0.08183451949436393</v>
+        <v>0.202999973297119</v>
       </c>
       <c r="F166" t="n">
         <v>-0.1404820962507122</v>
@@ -15359,7 +15359,7 @@
         </is>
       </c>
       <c r="S166" s="1" t="n">
-        <v>44098</v>
+        <v>25569.04217706019</v>
       </c>
       <c r="T166" t="n">
         <v>20</v>
@@ -15400,7 +15400,7 @@
         <v>23.89999961853027</v>
       </c>
       <c r="E167" t="n">
-        <v>0.05799023714447875</v>
+        <v>0.2578947167647511</v>
       </c>
       <c r="F167" t="n">
         <v>-0.1778242706206936</v>
@@ -15446,7 +15446,7 @@
         </is>
       </c>
       <c r="S167" s="1" t="n">
-        <v>44091</v>
+        <v>25569.04217697917</v>
       </c>
       <c r="T167" t="n">
         <v>19</v>
@@ -15487,7 +15487,7 @@
         <v>26.78811645507812</v>
       </c>
       <c r="E168" t="n">
-        <v>0.1155555866382741</v>
+        <v>0.575771556181066</v>
       </c>
       <c r="F168" t="n">
         <v>-0.01427614483141242</v>
@@ -15537,7 +15537,7 @@
         </is>
       </c>
       <c r="S168" s="1" t="n">
-        <v>43985</v>
+        <v>25569.04217575231</v>
       </c>
       <c r="T168" t="n">
         <v>17</v>
@@ -15578,7 +15578,7 @@
         <v>24.45000076293945</v>
       </c>
       <c r="E169" t="n">
-        <v>-0.1267856870378767</v>
+        <v>-0.1267856870378768</v>
       </c>
       <c r="F169" t="n">
         <v>-0.3386503242648595</v>
@@ -15628,7 +15628,7 @@
         </is>
       </c>
       <c r="S169" s="1" t="n">
-        <v>44517</v>
+        <v>25569.04218190972</v>
       </c>
       <c r="T169" t="n">
         <v>28</v>
@@ -15669,7 +15669,7 @@
         <v>17.74175071716309</v>
       </c>
       <c r="E170" t="n">
-        <v>-0.007556655700132948</v>
+        <v>0.182783381144206</v>
       </c>
       <c r="F170" t="n">
         <v>-0.04619284445021156</v>
@@ -15719,7 +15719,7 @@
         </is>
       </c>
       <c r="S170" s="1" t="n">
-        <v>44370</v>
+        <v>25569.04218020833</v>
       </c>
       <c r="T170" t="n">
         <v>15</v>
@@ -15760,7 +15760,7 @@
         <v>17</v>
       </c>
       <c r="E171" t="n">
-        <v>0.000588594998031468</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="F171" t="n">
         <v>-0.0994117400225471</v>
@@ -15808,7 +15808,7 @@
         </is>
       </c>
       <c r="S171" s="1" t="n">
-        <v>44407</v>
+        <v>25569.04218063657</v>
       </c>
       <c r="T171" t="n">
         <v>13</v>
@@ -15849,7 +15849,7 @@
         <v>224</v>
       </c>
       <c r="E172" t="n">
-        <v>0.06666666666666667</v>
+        <v>13</v>
       </c>
       <c r="F172" t="n">
         <v>-0.25</v>
@@ -15899,7 +15899,7 @@
         </is>
       </c>
       <c r="S172" s="1" t="n">
-        <v>44491</v>
+        <v>25569.04218160879</v>
       </c>
       <c r="T172" t="n">
         <v>16</v>
@@ -15940,7 +15940,7 @@
         <v>21.59000015258789</v>
       </c>
       <c r="E173" t="n">
-        <v>0.02809524536132812</v>
+        <v>0.3493750095367432</v>
       </c>
       <c r="F173" t="n">
         <v>-0.1009726859550057</v>
@@ -15990,7 +15990,7 @@
         </is>
       </c>
       <c r="S173" s="1" t="n">
-        <v>44399</v>
+        <v>25569.04218054398</v>
       </c>
       <c r="T173" t="n">
         <v>16</v>
@@ -16031,7 +16031,7 @@
         <v>19.13193893432617</v>
       </c>
       <c r="E174" t="n">
-        <v>0.1257894415604439</v>
+        <v>0.1254081726074217</v>
       </c>
       <c r="F174" t="n">
         <v>0.4151472397690039</v>
@@ -16081,7 +16081,7 @@
         </is>
       </c>
       <c r="S174" s="1" t="n">
-        <v>44413</v>
+        <v>25569.04218070602</v>
       </c>
       <c r="T174" t="n">
         <v>17</v>
@@ -16122,7 +16122,7 @@
         <v>26.88839340209961</v>
       </c>
       <c r="E175" t="n">
-        <v>0.0742187339928934</v>
+        <v>0.1441869532808344</v>
       </c>
       <c r="F175" t="n">
         <v>0.2250909431916638</v>
@@ -16172,7 +16172,7 @@
         </is>
       </c>
       <c r="S175" s="1" t="n">
-        <v>44399</v>
+        <v>25569.04218054398</v>
       </c>
       <c r="T175" t="n">
         <v>23.5</v>
@@ -16213,7 +16213,7 @@
         <v>14.80000019073486</v>
       </c>
       <c r="E176" t="n">
-        <v>0.04964537520049142</v>
+        <v>0.0571428707667757</v>
       </c>
       <c r="F176" t="n">
         <v>0.1114865237121772</v>
@@ -16263,7 +16263,7 @@
         </is>
       </c>
       <c r="S176" s="1" t="n">
-        <v>44498</v>
+        <v>25569.04218168982</v>
       </c>
       <c r="T176" t="n">
         <v>14</v>
@@ -16304,7 +16304,7 @@
         <v>195.8999938964844</v>
       </c>
       <c r="E177" t="n">
-        <v>-0.07046266241288553</v>
+        <v>11.24374961853028</v>
       </c>
       <c r="F177" t="n">
         <v>-0.1975497608677399</v>
@@ -16354,7 +16354,7 @@
         </is>
       </c>
       <c r="S177" s="1" t="n">
-        <v>44511</v>
+        <v>25569.04218184028</v>
       </c>
       <c r="T177" t="n">
         <v>16</v>
@@ -16395,7 +16395,7 @@
         <v>22.18000030517578</v>
       </c>
       <c r="E178" t="n">
-        <v>-0.1163346626261272</v>
+        <v>0.1673684371145148</v>
       </c>
       <c r="F178" t="n">
         <v>0.1406672177167059</v>
@@ -16445,7 +16445,7 @@
         </is>
       </c>
       <c r="S178" s="1" t="n">
-        <v>44398</v>
+        <v>25569.04218053241</v>
       </c>
       <c r="T178" t="n">
         <v>19</v>
@@ -16486,7 +16486,7 @@
         <v>12.68192291259766</v>
       </c>
       <c r="E179" t="n">
-        <v>0.05328380686948067</v>
+        <v>-0.3200041333727796</v>
       </c>
       <c r="F179" t="n">
         <v>-0.05235291728956923</v>
@@ -16536,7 +16536,7 @@
         </is>
       </c>
       <c r="S179" s="1" t="n">
-        <v>44503</v>
+        <v>25569.04218174769</v>
       </c>
       <c r="T179" t="n">
         <v>18.65</v>
@@ -16577,7 +16577,7 @@
         <v>35</v>
       </c>
       <c r="E180" t="n">
-        <v>0.04477611940298507</v>
+        <v>0.25</v>
       </c>
       <c r="F180" t="n">
         <v>-0.08114286150251115</v>
@@ -16627,7 +16627,7 @@
         </is>
       </c>
       <c r="S180" s="1" t="n">
-        <v>44497</v>
+        <v>25569.04218167824</v>
       </c>
       <c r="T180" t="n">
         <v>28</v>
@@ -16668,7 +16668,7 @@
         <v>28.29999923706055</v>
       </c>
       <c r="E181" t="n">
-        <v>0.2042552866834275</v>
+        <v>0.5722221798366972</v>
       </c>
       <c r="F181" t="n">
         <v>-0.4674911625054339</v>
@@ -16718,7 +16718,7 @@
         </is>
       </c>
       <c r="S181" s="1" t="n">
-        <v>44504</v>
+        <v>25569.04218175926</v>
       </c>
       <c r="T181" t="n">
         <v>18</v>
@@ -16759,7 +16759,7 @@
         <v>36.68000030517578</v>
       </c>
       <c r="E182" t="n">
-        <v>0.1286153940054087</v>
+        <v>0.5947826219641644</v>
       </c>
       <c r="F182" t="n">
         <v>0.8503272132471913</v>
@@ -16809,7 +16809,7 @@
         </is>
       </c>
       <c r="S182" s="1" t="n">
-        <v>44454</v>
+        <v>25569.04218118056</v>
       </c>
       <c r="T182" t="n">
         <v>23</v>
@@ -16900,7 +16900,7 @@
         </is>
       </c>
       <c r="S183" s="1" t="n">
-        <v>44406</v>
+        <v>25569.042180625</v>
       </c>
       <c r="T183" t="n">
         <v>38</v>
@@ -16941,7 +16941,7 @@
         <v>17.43000030517578</v>
       </c>
       <c r="E184" t="n">
-        <v>0.09622646058823833</v>
+        <v>0.08937501907348633</v>
       </c>
       <c r="F184" t="n">
         <v>0.320137683649328</v>
@@ -16991,7 +16991,7 @@
         </is>
       </c>
       <c r="S184" s="1" t="n">
-        <v>44393</v>
+        <v>25569.04218047454</v>
       </c>
       <c r="T184" t="n">
         <v>16</v>
@@ -17032,7 +17032,7 @@
         <v>35</v>
       </c>
       <c r="E185" t="n">
-        <v>-0.01129947764512067</v>
+        <v>0.4583333333333333</v>
       </c>
       <c r="F185" t="n">
         <v>-0.02857142857142857</v>
@@ -17082,7 +17082,7 @@
         </is>
       </c>
       <c r="S185" s="1" t="n">
-        <v>44454</v>
+        <v>25569.04218118056</v>
       </c>
       <c r="T185" t="n">
         <v>24</v>
@@ -17123,7 +17123,7 @@
         <v>21.02000045776367</v>
       </c>
       <c r="E186" t="n">
-        <v>0.1270777955876531</v>
+        <v>0.3137500286102293</v>
       </c>
       <c r="F186" t="n">
         <v>-0.143672711322337</v>
@@ -17171,7 +17171,7 @@
         </is>
       </c>
       <c r="S186" s="1" t="n">
-        <v>44490</v>
+        <v>25569.04218159722</v>
       </c>
       <c r="T186" t="n">
         <v>16</v>
@@ -17212,7 +17212,7 @@
         <v>12.25</v>
       </c>
       <c r="E187" t="n">
-        <v>0.09375001862645181</v>
+        <v>0.02083333333333333</v>
       </c>
       <c r="F187" t="n">
         <v>-0.03265303008410395</v>
@@ -17262,7 +17262,7 @@
         </is>
       </c>
       <c r="S187" s="1" t="n">
-        <v>44400</v>
+        <v>25569.04218055556</v>
       </c>
       <c r="T187" t="n">
         <v>12</v>
@@ -17303,7 +17303,7 @@
         <v>13.19999980926514</v>
       </c>
       <c r="E188" t="n">
-        <v>-0.3052631679334138</v>
+        <v>-0.1750000119209287</v>
       </c>
       <c r="F188" t="n">
         <v>-0.02121210128917262</v>
@@ -17349,7 +17349,7 @@
         </is>
       </c>
       <c r="S188" s="1" t="n">
-        <v>44477</v>
+        <v>25569.04218144676</v>
       </c>
       <c r="T188" t="n">
         <v>16</v>
@@ -17390,7 +17390,7 @@
         <v>15.2312650680542</v>
       </c>
       <c r="E189" t="n">
-        <v>0.2375389528418454</v>
+        <v>0.3846604607321999</v>
       </c>
       <c r="F189" t="n">
         <v>-0.2001259271489654</v>
@@ -17440,7 +17440,7 @@
         </is>
       </c>
       <c r="S189" s="1" t="n">
-        <v>44498</v>
+        <v>25569.04218168982</v>
       </c>
       <c r="T189" t="n">
         <v>11</v>
@@ -17481,7 +17481,7 @@
         <v>37.84999847412109</v>
       </c>
       <c r="E190" t="n">
-        <v>0.02993193126860119</v>
+        <v>0.3517856597900388</v>
       </c>
       <c r="F190" t="n">
         <v>-0.07529718861335497</v>
@@ -17531,7 +17531,7 @@
         </is>
       </c>
       <c r="S190" s="1" t="n">
-        <v>44377</v>
+        <v>25569.04218028935</v>
       </c>
       <c r="T190" t="n">
         <v>28</v>
@@ -17572,7 +17572,7 @@
         <v>17.60000038146973</v>
       </c>
       <c r="E191" t="n">
-        <v>0.2054794466860145</v>
+        <v>0.1000000238418581</v>
       </c>
       <c r="F191" t="n">
         <v>0.05795457020771351</v>
@@ -17622,7 +17622,7 @@
         </is>
       </c>
       <c r="S191" s="1" t="n">
-        <v>44370</v>
+        <v>25569.04218020833</v>
       </c>
       <c r="T191" t="n">
         <v>16</v>
@@ -17663,7 +17663,7 @@
         <v>577.7999877929688</v>
       </c>
       <c r="E192" t="n">
-        <v>0.3487394865196575</v>
+        <v>37.51999918619791</v>
       </c>
       <c r="F192" t="n">
         <v>-0.5199030810712314</v>
@@ -17713,7 +17713,7 @@
         </is>
       </c>
       <c r="S192" s="1" t="n">
-        <v>44503</v>
+        <v>25569.04218174769</v>
       </c>
       <c r="T192" t="n">
         <v>15</v>
@@ -17754,7 +17754,7 @@
         <v>112.8000030517578</v>
       </c>
       <c r="E193" t="n">
-        <v>-0.05495976478760867</v>
+        <v>7.676923311673677</v>
       </c>
       <c r="F193" t="n">
         <v>-0.1914894106306411</v>
@@ -17804,7 +17804,7 @@
         </is>
       </c>
       <c r="S193" s="1" t="n">
-        <v>44406</v>
+        <v>25569.042180625</v>
       </c>
       <c r="T193" t="n">
         <v>13</v>
@@ -17845,7 +17845,7 @@
         <v>20.0541820526123</v>
       </c>
       <c r="E194" t="n">
-        <v>0.2883436185845506</v>
+        <v>0.1796577678007236</v>
       </c>
       <c r="F194" t="n">
         <v>-0.2842857641504077</v>
@@ -17895,7 +17895,7 @@
         </is>
       </c>
       <c r="S194" s="1" t="n">
-        <v>44378</v>
+        <v>25569.04218030093</v>
       </c>
       <c r="T194" t="n">
         <v>17</v>
@@ -17936,7 +17936,7 @@
         <v>1100</v>
       </c>
       <c r="E195" t="n">
-        <v>0</v>
+        <v>60.11111111111111</v>
       </c>
       <c r="F195" t="n">
         <v>0.09181818181818181</v>
@@ -17986,7 +17986,7 @@
         </is>
       </c>
       <c r="S195" s="1" t="n">
-        <v>44406</v>
+        <v>25569.042180625</v>
       </c>
       <c r="T195" t="n">
         <v>18</v>
@@ -18027,7 +18027,7 @@
         <v>7</v>
       </c>
       <c r="E196" t="n">
-        <v>-0.1504854132963036</v>
+        <v>-0.125</v>
       </c>
       <c r="F196" t="n">
         <v>0.601428576878139</v>
@@ -18077,7 +18077,7 @@
         </is>
       </c>
       <c r="S196" s="1" t="n">
-        <v>44404</v>
+        <v>25569.04218060185</v>
       </c>
       <c r="T196" t="n">
         <v>8</v>
@@ -18118,7 +18118,7 @@
         <v>9.184384346008301</v>
       </c>
       <c r="E197" t="n">
-        <v>0.005487814309836803</v>
+        <v>-0.4259759783744812</v>
       </c>
       <c r="F197" t="n">
         <v>0.009702897817097199</v>
@@ -18168,7 +18168,7 @@
         </is>
       </c>
       <c r="S197" s="1" t="n">
-        <v>44538</v>
+        <v>25569.04218215278</v>
       </c>
       <c r="T197" t="n">
         <v>16</v>
@@ -18209,7 +18209,7 @@
         <v>18.20000076293945</v>
       </c>
       <c r="E198" t="n">
-        <v>0.1023622356528626</v>
+        <v>0.300000054495675</v>
       </c>
       <c r="F198" t="n">
         <v>0.3840659053900622</v>
@@ -18259,7 +18259,7 @@
         </is>
       </c>
       <c r="S198" s="1" t="n">
-        <v>44496</v>
+        <v>25569.04218166667</v>
       </c>
       <c r="T198" t="n">
         <v>14</v>
@@ -18300,7 +18300,7 @@
         <v>53</v>
       </c>
       <c r="E199" t="n">
-        <v>0.2873452114937937</v>
+        <v>1.038461538461539</v>
       </c>
       <c r="F199" t="n">
         <v>-0.01207546018204599</v>
@@ -18350,7 +18350,7 @@
         </is>
       </c>
       <c r="S199" s="1" t="n">
-        <v>44371</v>
+        <v>25569.04218021991</v>
       </c>
       <c r="T199" t="n">
         <v>26</v>
@@ -18391,7 +18391,7 @@
         <v>26</v>
       </c>
       <c r="E200" t="n">
-        <v>-0.03703703703703703</v>
+        <v>0.2380952380952381</v>
       </c>
       <c r="F200" t="n">
         <v>0.1107691984910231</v>
@@ -18441,7 +18441,7 @@
         </is>
       </c>
       <c r="S200" s="1" t="n">
-        <v>44406</v>
+        <v>25569.042180625</v>
       </c>
       <c r="T200" t="n">
         <v>21</v>
@@ -18482,7 +18482,7 @@
         <v>15.22619533538818</v>
       </c>
       <c r="E201" t="n">
-        <v>0.3169231414794921</v>
+        <v>0.2688496112823484</v>
       </c>
       <c r="F201" t="n">
         <v>-0.1676402149767037</v>
@@ -18532,7 +18532,7 @@
         </is>
       </c>
       <c r="S201" s="1" t="n">
-        <v>44462</v>
+        <v>25569.04218127315</v>
       </c>
       <c r="T201" t="n">
         <v>12</v>
@@ -18573,7 +18573,7 @@
         <v>19.89999961853027</v>
       </c>
       <c r="E202" t="n">
-        <v>0.04736840097527755</v>
+        <v>0.2437499761581419</v>
       </c>
       <c r="F202" t="n">
         <v>-0.06733669237561811</v>
@@ -18623,7 +18623,7 @@
         </is>
       </c>
       <c r="S202" s="1" t="n">
-        <v>44511</v>
+        <v>25569.04218184028</v>
       </c>
       <c r="T202" t="n">
         <v>16</v>
@@ -18664,7 +18664,7 @@
         <v>11.78792953491211</v>
       </c>
       <c r="E203" t="n">
-        <v>0.02400001525878901</v>
+        <v>-0.09323618962214543</v>
       </c>
       <c r="F203" t="n">
         <v>-0.09921880435644398</v>
@@ -18714,7 +18714,7 @@
         </is>
       </c>
       <c r="S203" s="1" t="n">
-        <v>44504</v>
+        <v>25569.04218175926</v>
       </c>
       <c r="T203" t="n">
         <v>13</v>
@@ -18755,7 +18755,7 @@
         <v>0.2763159871101379</v>
       </c>
       <c r="E204" t="n">
-        <v>-0.1249981007200654</v>
+        <v>-0.9854570533099928</v>
       </c>
       <c r="F204" t="n">
         <v>1.85809371516927</v>
@@ -18805,7 +18805,7 @@
         </is>
       </c>
       <c r="S204" s="1" t="n">
-        <v>44393</v>
+        <v>25569.04218047454</v>
       </c>
       <c r="T204" t="n">
         <v>19</v>
@@ -18846,7 +18846,7 @@
         <v>46.40000152587891</v>
       </c>
       <c r="E205" t="n">
-        <v>-0.01297589486138918</v>
+        <v>-0.01276592498129972</v>
       </c>
       <c r="F205" t="n">
         <v>0.3756465459479448</v>
@@ -18896,7 +18896,7 @@
         </is>
       </c>
       <c r="S205" s="1" t="n">
-        <v>44497</v>
+        <v>25569.04218167824</v>
       </c>
       <c r="T205" t="n">
         <v>47</v>
@@ -18937,7 +18937,7 @@
         <v>18.76000022888184</v>
       </c>
       <c r="E206" t="n">
-        <v>-0.06666667299286433</v>
+        <v>0.1035294252283435</v>
       </c>
       <c r="F206" t="n">
         <v>0.2915777850009399</v>
@@ -18987,7 +18987,7 @@
         </is>
       </c>
       <c r="S206" s="1" t="n">
-        <v>44400</v>
+        <v>25569.04218055556</v>
       </c>
       <c r="T206" t="n">
         <v>17</v>
@@ -19028,7 +19028,7 @@
         <v>14.48850727081299</v>
       </c>
       <c r="E207" t="n">
-        <v>0.01933333079020182</v>
+        <v>0.1145005592933069</v>
       </c>
       <c r="F207" t="n">
         <v>0.352631836349214</v>
@@ -19078,7 +19078,7 @@
         </is>
       </c>
       <c r="S207" s="1" t="n">
-        <v>44504</v>
+        <v>25569.04218175926</v>
       </c>
       <c r="T207" t="n">
         <v>13</v>
@@ -19119,7 +19119,7 @@
         <v>61.6407585144043</v>
       </c>
       <c r="E208" t="n">
-        <v>-0.1628959110883068</v>
+        <v>2.625926971435547</v>
       </c>
       <c r="F208" t="n">
         <v>0.1216215605719624</v>
@@ -19165,7 +19165,7 @@
         </is>
       </c>
       <c r="S208" s="1" t="n">
-        <v>44372</v>
+        <v>25569.04218023148</v>
       </c>
       <c r="T208" t="n">
         <v>17</v>
@@ -19206,7 +19206,7 @@
         <v>49.5</v>
       </c>
       <c r="E209" t="n">
-        <v>-0.04807692307692308</v>
+        <v>0.7678571428571429</v>
       </c>
       <c r="F209" t="n">
         <v>-0.3535353535353535</v>
@@ -19256,7 +19256,7 @@
         </is>
       </c>
       <c r="S209" s="1" t="n">
-        <v>44518</v>
+        <v>25569.0421819213</v>
       </c>
       <c r="T209" t="n">
         <v>28</v>
@@ -19297,7 +19297,7 @@
         <v>23.95000076293945</v>
       </c>
       <c r="E210" t="n">
-        <v>-0.09622638630417157</v>
+        <v>0.1975000381469725</v>
       </c>
       <c r="F210" t="n">
         <v>-0.1691023388473626</v>
@@ -19347,7 +19347,7 @@
         </is>
       </c>
       <c r="S210" s="1" t="n">
-        <v>44498</v>
+        <v>25569.04218168982</v>
       </c>
       <c r="T210" t="n">
         <v>20</v>
@@ -19388,7 +19388,7 @@
         <v>10.5</v>
       </c>
       <c r="E211" t="n">
-        <v>-0.125</v>
+        <v>-0.3</v>
       </c>
       <c r="F211" t="n">
         <v>-0.1514285859607515</v>
@@ -19438,7 +19438,7 @@
         </is>
       </c>
       <c r="S211" s="1" t="n">
-        <v>44393</v>
+        <v>25569.04218047454</v>
       </c>
       <c r="T211" t="n">
         <v>15</v>
@@ -19479,7 +19479,7 @@
         <v>28</v>
       </c>
       <c r="E212" t="n">
-        <v>0.1089108910891089</v>
+        <v>0.07692307692307693</v>
       </c>
       <c r="F212" t="n">
         <v>0.1500000272478376</v>
@@ -19529,7 +19529,7 @@
         </is>
       </c>
       <c r="S212" s="1" t="n">
-        <v>44377</v>
+        <v>25569.04218028935</v>
       </c>
       <c r="T212" t="n">
         <v>26</v>
@@ -19570,7 +19570,7 @@
         <v>43.29000091552734</v>
       </c>
       <c r="E213" t="n">
-        <v>0.1621476755846267</v>
+        <v>0.6033333672417532</v>
       </c>
       <c r="F213" t="n">
         <v>-0.1672442024797911</v>
@@ -19620,7 +19620,7 @@
         </is>
       </c>
       <c r="S213" s="1" t="n">
-        <v>44454</v>
+        <v>25569.04218118056</v>
       </c>
       <c r="T213" t="n">
         <v>27</v>
@@ -19661,7 +19661,7 @@
         <v>11.89999961853027</v>
       </c>
       <c r="E214" t="n">
-        <v>-0.2071952407014214</v>
+        <v>-0.2562500238418581</v>
       </c>
       <c r="F214" t="n">
         <v>-0.163865535443267</v>
@@ -19711,7 +19711,7 @@
         </is>
       </c>
       <c r="S214" s="1" t="n">
-        <v>44392</v>
+        <v>25569.04218046296</v>
       </c>
       <c r="T214" t="n">
         <v>16</v>
@@ -19752,7 +19752,7 @@
         <v>19.25</v>
       </c>
       <c r="E215" t="n">
-        <v>-0.125</v>
+        <v>0.203125</v>
       </c>
       <c r="F215" t="n">
         <v>-0.04207789433466923</v>
@@ -19802,7 +19802,7 @@
         </is>
       </c>
       <c r="S215" s="1" t="n">
-        <v>44372</v>
+        <v>25569.04218023148</v>
       </c>
       <c r="T215" t="n">
         <v>16</v>
@@ -19843,7 +19843,7 @@
         <v>16.76000022888184</v>
       </c>
       <c r="E216" t="n">
-        <v>-0.09159894114759735</v>
+        <v>-0.06888887617323114</v>
       </c>
       <c r="F216" t="n">
         <v>0.1610977815464477</v>
@@ -19893,7 +19893,7 @@
         </is>
       </c>
       <c r="S216" s="1" t="n">
-        <v>44400</v>
+        <v>25569.04218055556</v>
       </c>
       <c r="T216" t="n">
         <v>18</v>
@@ -19934,7 +19934,7 @@
         <v>62.5099983215332</v>
       </c>
       <c r="E217" t="n">
-        <v>-0.04213919283907812</v>
+        <v>0.5627499580383301</v>
       </c>
       <c r="F217" t="n">
         <v>0.007678825305107136</v>
@@ -19984,7 +19984,7 @@
         </is>
       </c>
       <c r="S217" s="1" t="n">
-        <v>44461</v>
+        <v>25569.04218126158</v>
       </c>
       <c r="T217" t="n">
         <v>40</v>
@@ -20025,7 +20025,7 @@
         <v>134.2550048828125</v>
       </c>
       <c r="E218" t="n">
-        <v>-0.05053033466820765</v>
+        <v>0.3162255380667892</v>
       </c>
       <c r="F218" t="n">
         <v>0.2643848931231287</v>
@@ -20075,7 +20075,7 @@
         </is>
       </c>
       <c r="S218" s="1" t="n">
-        <v>44405</v>
+        <v>25569.04218061343</v>
       </c>
       <c r="T218" t="n">
         <v>102</v>
@@ -20116,7 +20116,7 @@
         <v>19.44734764099121</v>
       </c>
       <c r="E219" t="n">
-        <v>0.1813814130303418</v>
+        <v>-0.07393582661946614</v>
       </c>
       <c r="F219" t="n">
         <v>0.2785966982577794</v>
@@ -20166,7 +20166,7 @@
         </is>
       </c>
       <c r="S219" s="1" t="n">
-        <v>44393</v>
+        <v>25569.04218047454</v>
       </c>
       <c r="T219" t="n">
         <v>21</v>
@@ -20207,7 +20207,7 @@
         <v>20.29999923706055</v>
       </c>
       <c r="E220" t="n">
-        <v>0.07407405538557053</v>
+        <v>0.3533332824707033</v>
       </c>
       <c r="F220" t="n">
         <v>-0.0009851503037758176</v>
@@ -20257,7 +20257,7 @@
         </is>
       </c>
       <c r="S220" s="1" t="n">
-        <v>44372</v>
+        <v>25569.04218023148</v>
       </c>
       <c r="T220" t="n">
         <v>15</v>
@@ -20298,7 +20298,7 @@
         <v>20.10000038146973</v>
       </c>
       <c r="E221" t="n">
-        <v>-0.2269230622511644</v>
+        <v>0.2562500238418581</v>
       </c>
       <c r="F221" t="n">
         <v>-0.245273642368722</v>
@@ -20348,7 +20348,7 @@
         </is>
       </c>
       <c r="S221" s="1" t="n">
-        <v>44378</v>
+        <v>25569.04218030093</v>
       </c>
       <c r="T221" t="n">
         <v>16</v>
@@ -20389,7 +20389,7 @@
         <v>22.1299991607666</v>
       </c>
       <c r="E222" t="n">
-        <v>0.05380948384602865</v>
+        <v>0.2294443978203667</v>
       </c>
       <c r="F222" t="n">
         <v>-0.09353817321846263</v>
@@ -20439,7 +20439,7 @@
         </is>
       </c>
       <c r="S222" s="1" t="n">
-        <v>44470</v>
+        <v>25569.04218136574</v>
       </c>
       <c r="T222" t="n">
         <v>18</v>
@@ -20480,7 +20480,7 @@
         <v>24.5</v>
       </c>
       <c r="E223" t="n">
-        <v>-0.02</v>
+        <v>0.1666666666666667</v>
       </c>
       <c r="F223" t="n">
         <v>0.03102041750538106</v>
@@ -20530,7 +20530,7 @@
         </is>
       </c>
       <c r="S223" s="1" t="n">
-        <v>44469</v>
+        <v>25569.04218135417</v>
       </c>
       <c r="T223" t="n">
         <v>21</v>
@@ -20571,7 +20571,7 @@
         <v>17.75</v>
       </c>
       <c r="E224" t="n">
-        <v>0.07121305533544244</v>
+        <v>-0.01388888888888889</v>
       </c>
       <c r="F224" t="n">
         <v>0.0963379765900088</v>
@@ -20621,7 +20621,7 @@
         </is>
       </c>
       <c r="S224" s="1" t="n">
-        <v>44476</v>
+        <v>25569.04218143519</v>
       </c>
       <c r="T224" t="n">
         <v>18</v>
@@ -20662,7 +20662,7 @@
         <v>13.64999961853027</v>
       </c>
       <c r="E225" t="n">
-        <v>0.09199996948242188</v>
+        <v>-0.02500002724783787</v>
       </c>
       <c r="F225" t="n">
         <v>0.1267399666123154</v>
@@ -20712,7 +20712,7 @@
         </is>
       </c>
       <c r="S225" s="1" t="n">
-        <v>44399</v>
+        <v>25569.04218054398</v>
       </c>
       <c r="T225" t="n">
         <v>14</v>
@@ -20753,7 +20753,7 @@
         <v>24</v>
       </c>
       <c r="E226" t="n">
-        <v>0</v>
+        <v>-0.2</v>
       </c>
       <c r="F226" t="n">
         <v>0.125</v>
@@ -20801,7 +20801,7 @@
         </is>
       </c>
       <c r="S226" s="1" t="n">
-        <v>44314</v>
+        <v>25569.04217956019</v>
       </c>
       <c r="T226" t="n">
         <v>30</v>
@@ -20842,7 +20842,7 @@
         <v>11.76000022888184</v>
       </c>
       <c r="E227" t="n">
-        <v>-0.07764704087201287</v>
+        <v>-0.1599999836512972</v>
       </c>
       <c r="F227" t="n">
         <v>-0.282312974819917</v>
@@ -20892,7 +20892,7 @@
         </is>
       </c>
       <c r="S227" s="1" t="n">
-        <v>44483</v>
+        <v>25569.0421815162</v>
       </c>
       <c r="T227" t="n">
         <v>14</v>
@@ -20933,7 +20933,7 @@
         <v>41.93999862670898</v>
       </c>
       <c r="E228" t="n">
-        <v>0.1982856750488281</v>
+        <v>0.6775999450683591</v>
       </c>
       <c r="F228" t="n">
         <v>-0.0004768826518495598</v>
@@ -20983,7 +20983,7 @@
         </is>
       </c>
       <c r="S228" s="1" t="n">
-        <v>44454</v>
+        <v>25569.04218118056</v>
       </c>
       <c r="T228" t="n">
         <v>25</v>
@@ -21024,7 +21024,7 @@
         <v>21.39999961853027</v>
       </c>
       <c r="E229" t="n">
-        <v>-0.04888890584309896</v>
+        <v>0.06999998092651349</v>
       </c>
       <c r="F229" t="n">
         <v>0.04672897279559292</v>
@@ -21074,7 +21074,7 @@
         </is>
       </c>
       <c r="S229" s="1" t="n">
-        <v>44392</v>
+        <v>25569.04218046296</v>
       </c>
       <c r="T229" t="n">
         <v>20</v>
@@ -21165,7 +21165,7 @@
         </is>
       </c>
       <c r="S230" s="1" t="n">
-        <v>44399</v>
+        <v>25569.04218054398</v>
       </c>
       <c r="T230" t="n">
         <v>20</v>
@@ -21206,7 +21206,7 @@
         <v>103.8899993896484</v>
       </c>
       <c r="E231" t="n">
-        <v>0.1022811606328747</v>
+        <v>0.349220771294135</v>
       </c>
       <c r="F231" t="n">
         <v>-0.07604198259978101</v>
@@ -21256,7 +21256,7 @@
         </is>
       </c>
       <c r="S231" s="1" t="n">
-        <v>44483</v>
+        <v>25569.0421815162</v>
       </c>
       <c r="T231" t="n">
         <v>77</v>
@@ -21297,7 +21297,7 @@
         <v>252</v>
       </c>
       <c r="E232" t="n">
-        <v>-0.16</v>
+        <v>30.5</v>
       </c>
       <c r="F232" t="n">
         <v>-0.3698412577311198</v>
@@ -21347,7 +21347,7 @@
         </is>
       </c>
       <c r="S232" s="1" t="n">
-        <v>44397</v>
+        <v>25569.04218052083</v>
       </c>
       <c r="T232" t="n">
         <v>8</v>
@@ -21388,7 +21388,7 @@
         <v>385.7999877929688</v>
       </c>
       <c r="E233" t="n">
-        <v>-0.1613043743631114</v>
+        <v>17.37142799014137</v>
       </c>
       <c r="F233" t="n">
         <v>-0.4287195415497077</v>
@@ -21438,7 +21438,7 @@
         </is>
       </c>
       <c r="S233" s="1" t="n">
-        <v>44496</v>
+        <v>25569.04218166667</v>
       </c>
       <c r="T233" t="n">
         <v>21</v>
@@ -21479,7 +21479,7 @@
         <v>41.06000137329102</v>
       </c>
       <c r="E234" t="n">
-        <v>0.03295600939096895</v>
+        <v>0.5207407916033712</v>
       </c>
       <c r="F234" t="n">
         <v>-0.1005845331218558</v>
@@ -21529,7 +21529,7 @@
         </is>
       </c>
       <c r="S234" s="1" t="n">
-        <v>44510</v>
+        <v>25569.0421818287</v>
       </c>
       <c r="T234" t="n">
         <v>27</v>
@@ -21570,7 +21570,7 @@
         <v>87.38999938964844</v>
       </c>
       <c r="E235" t="n">
-        <v>0.3041336607031544</v>
+        <v>0.9861363497647372</v>
       </c>
       <c r="F235" t="n">
         <v>-0.08216043432111833</v>
@@ -21620,7 +21620,7 @@
         </is>
       </c>
       <c r="S235" s="1" t="n">
-        <v>44377</v>
+        <v>25569.04218028935</v>
       </c>
       <c r="T235" t="n">
         <v>44</v>
@@ -21661,7 +21661,7 @@
         <v>24.14999961853027</v>
       </c>
       <c r="E236" t="n">
-        <v>0.03870966101205477</v>
+        <v>0.1499999818347748</v>
       </c>
       <c r="F236" t="n">
         <v>0.2277432748189302</v>
@@ -21711,7 +21711,7 @@
         </is>
       </c>
       <c r="S236" s="1" t="n">
-        <v>44378</v>
+        <v>25569.04218030093</v>
       </c>
       <c r="T236" t="n">
         <v>21</v>
@@ -21752,7 +21752,7 @@
         <v>13.43000030517578</v>
       </c>
       <c r="E237" t="n">
-        <v>0.05333335726868873</v>
+        <v>0.1191666920979816</v>
       </c>
       <c r="F237" t="n">
         <v>-0.03574091474336433</v>
@@ -21800,7 +21800,7 @@
         </is>
       </c>
       <c r="S237" s="1" t="n">
-        <v>44378</v>
+        <v>25569.04218030093</v>
       </c>
       <c r="T237" t="n">
         <v>12</v>
@@ -21841,7 +21841,7 @@
         <v>23.52000045776367</v>
       </c>
       <c r="E238" t="n">
-        <v>-0.1599999836512974</v>
+        <v>0.000851083309092269</v>
       </c>
       <c r="F238" t="n">
         <v>-0.1211734832483379</v>
@@ -21891,7 +21891,7 @@
         </is>
       </c>
       <c r="S238" s="1" t="n">
-        <v>44376</v>
+        <v>25569.04218027778</v>
       </c>
       <c r="T238" t="n">
         <v>23.5</v>
@@ -21932,7 +21932,7 @@
         <v>119.879997253418</v>
       </c>
       <c r="E239" t="n">
-        <v>0.05157892327559622</v>
+        <v>9.898181568492545</v>
       </c>
       <c r="F239" t="n">
         <v>0.1461461214920647</v>
@@ -21982,7 +21982,7 @@
         </is>
       </c>
       <c r="S239" s="1" t="n">
-        <v>44461</v>
+        <v>25569.04218126158</v>
       </c>
       <c r="T239" t="n">
         <v>11</v>
@@ -22023,7 +22023,7 @@
         <v>20.20919036865234</v>
       </c>
       <c r="E240" t="n">
-        <v>0.04477609957460444</v>
+        <v>0.06364159835012317</v>
       </c>
       <c r="F240" t="n">
         <v>-0.4304761974872955</v>
@@ -22073,7 +22073,7 @@
         </is>
       </c>
       <c r="S240" s="1" t="n">
-        <v>44370</v>
+        <v>25569.04218020833</v>
       </c>
       <c r="T240" t="n">
         <v>19</v>
@@ -22114,7 +22114,7 @@
         <v>28</v>
       </c>
       <c r="E241" t="n">
-        <v>0.06666666666666667</v>
+        <v>0.5555555555555556</v>
       </c>
       <c r="F241" t="n">
         <v>-0.2807143075125558</v>
@@ -22164,7 +22164,7 @@
         </is>
       </c>
       <c r="S241" s="1" t="n">
-        <v>44377</v>
+        <v>25569.04218028935</v>
       </c>
       <c r="T241" t="n">
         <v>18</v>
@@ -22205,7 +22205,7 @@
         <v>13.04839897155762</v>
       </c>
       <c r="E242" t="n">
-        <v>-0.03333333333333338</v>
+        <v>0.04387191772460966</v>
       </c>
       <c r="F242" t="n">
         <v>0.01931029119651332</v>
@@ -22255,7 +22255,7 @@
         </is>
       </c>
       <c r="S242" s="1" t="n">
-        <v>44407</v>
+        <v>25569.04218063657</v>
       </c>
       <c r="T242" t="n">
         <v>12.5</v>
@@ -22296,7 +22296,7 @@
         <v>48.45000076293945</v>
       </c>
       <c r="E243" t="n">
-        <v>-0.08412099498262762</v>
+        <v>0.1267442037892896</v>
       </c>
       <c r="F243" t="n">
         <v>-0.2988647949271535</v>
@@ -22346,7 +22346,7 @@
         </is>
       </c>
       <c r="S243" s="1" t="n">
-        <v>44462</v>
+        <v>25569.04218127315</v>
       </c>
       <c r="T243" t="n">
         <v>43</v>
@@ -22387,7 +22387,7 @@
         <v>16</v>
       </c>
       <c r="E244" t="n">
-        <v>-0.08571428571428572</v>
+        <v>0</v>
       </c>
       <c r="F244" t="n">
         <v>-0.143750011920929</v>
@@ -22437,7 +22437,7 @@
         </is>
       </c>
       <c r="S244" s="1" t="n">
-        <v>44407</v>
+        <v>25569.04218063657</v>
       </c>
       <c r="T244" t="n">
         <v>16</v>
@@ -22478,7 +22478,7 @@
         <v>12</v>
       </c>
       <c r="E245" t="n">
-        <v>0.04347826086956522</v>
+        <v>0.2</v>
       </c>
       <c r="F245" t="n">
         <v>-0.03500000635782877</v>
@@ -22528,7 +22528,7 @@
         </is>
       </c>
       <c r="S245" s="1" t="n">
-        <v>44398</v>
+        <v>25569.04218053241</v>
       </c>
       <c r="T245" t="n">
         <v>10</v>
@@ -22569,7 +22569,7 @@
         <v>3618</v>
       </c>
       <c r="E246" t="n">
-        <v>0.1159227484390492</v>
+        <v>240.2</v>
       </c>
       <c r="F246" t="n">
         <v>0.03343282502418463</v>
@@ -22617,7 +22617,7 @@
         </is>
       </c>
       <c r="S246" s="1" t="n">
-        <v>44462</v>
+        <v>25569.04218127315</v>
       </c>
       <c r="T246" t="n">
         <v>15</v>
@@ -22658,7 +22658,7 @@
         <v>13.52000045776367</v>
       </c>
       <c r="E247" t="n">
-        <v>-0.1203643097963573</v>
+        <v>-0.09866663614908866</v>
       </c>
       <c r="F247" t="n">
         <v>-0.1812130680463531</v>
@@ -22708,7 +22708,7 @@
         </is>
       </c>
       <c r="S247" s="1" t="n">
-        <v>44490</v>
+        <v>25569.04218159722</v>
       </c>
       <c r="T247" t="n">
         <v>15</v>
@@ -22799,7 +22799,7 @@
         </is>
       </c>
       <c r="S248" s="1" t="n">
-        <v>44439</v>
+        <v>25569.04218100695</v>
       </c>
       <c r="T248" t="n">
         <v>18</v>
@@ -22840,7 +22840,7 @@
         <v>17.60000038146973</v>
       </c>
       <c r="E249" t="n">
-        <v>-0.1199999809265137</v>
+        <v>0.03529414008645471</v>
       </c>
       <c r="F249" t="n">
         <v>0.1039772661387429</v>
@@ -22890,7 +22890,7 @@
         </is>
       </c>
       <c r="S249" s="1" t="n">
-        <v>44378</v>
+        <v>25569.04218030093</v>
       </c>
       <c r="T249" t="n">
         <v>17</v>
@@ -22931,7 +22931,7 @@
         <v>18.79000091552734</v>
       </c>
       <c r="E250" t="n">
-        <v>-0.1380733223337059</v>
+        <v>-0.2170832951863608</v>
       </c>
       <c r="F250" t="n">
         <v>-0.170835595285611</v>
@@ -22981,7 +22981,7 @@
         </is>
       </c>
       <c r="S250" s="1" t="n">
-        <v>44511</v>
+        <v>25569.04218184028</v>
       </c>
       <c r="T250" t="n">
         <v>24</v>
@@ -23022,7 +23022,7 @@
         <v>25.01000022888184</v>
       </c>
       <c r="E251" t="n">
-        <v>-0.03807691427377554</v>
+        <v>0.0004000091552735796</v>
       </c>
       <c r="F251" t="n">
         <v>0.05957615983535638</v>
@@ -23072,7 +23072,7 @@
         </is>
       </c>
       <c r="S251" s="1" t="n">
-        <v>44509</v>
+        <v>25569.04218181713</v>
       </c>
       <c r="T251" t="n">
         <v>25</v>
@@ -23113,7 +23113,7 @@
         <v>16.51037979125977</v>
       </c>
       <c r="E252" t="n">
-        <v>0.02449998855590823</v>
+        <v>-0.1310326425652753</v>
       </c>
       <c r="F252" t="n">
         <v>0.125426833086227</v>
@@ -23163,7 +23163,7 @@
         </is>
       </c>
       <c r="S252" s="1" t="n">
-        <v>44455</v>
+        <v>25569.04218119213</v>
       </c>
       <c r="T252" t="n">
         <v>19</v>
@@ -23204,7 +23204,7 @@
         <v>26</v>
       </c>
       <c r="E253" t="n">
-        <v>-0.1304347715146217</v>
+        <v>0.625</v>
       </c>
       <c r="F253" t="n">
         <v>-0.1357692571786734</v>
@@ -23254,7 +23254,7 @@
         </is>
       </c>
       <c r="S253" s="1" t="n">
-        <v>44454</v>
+        <v>25569.04218118056</v>
       </c>
       <c r="T253" t="n">
         <v>16</v>
@@ -23295,7 +23295,7 @@
         <v>20.8799991607666</v>
       </c>
       <c r="E254" t="n">
-        <v>-0.005714325677780878</v>
+        <v>0.2282352447509766</v>
       </c>
       <c r="F254" t="n">
         <v>1.214080526837483</v>
@@ -23339,7 +23339,7 @@
         </is>
       </c>
       <c r="S254" s="1" t="n">
-        <v>44414</v>
+        <v>25569.04218071759</v>
       </c>
       <c r="T254" t="n">
         <v>17</v>
@@ -23380,7 +23380,7 @@
         <v>4.885919570922852</v>
       </c>
       <c r="E255" t="n">
-        <v>0</v>
+        <v>-0.825502872467041</v>
       </c>
       <c r="F255" t="n">
         <v>0</v>
@@ -23430,7 +23430,7 @@
         </is>
       </c>
       <c r="S255" s="1" t="n">
-        <v>44252</v>
+        <v>25569.04217884259</v>
       </c>
       <c r="T255" t="n">
         <v>28</v>
@@ -23471,7 +23471,7 @@
         <v>21.18000030517578</v>
       </c>
       <c r="E256" t="n">
-        <v>-0.03727271340110085</v>
+        <v>0.1147368581671464</v>
       </c>
       <c r="F256" t="n">
         <v>0.448064194257782</v>
@@ -23521,7 +23521,7 @@
         </is>
       </c>
       <c r="S256" s="1" t="n">
-        <v>44371</v>
+        <v>25569.04218021991</v>
       </c>
       <c r="T256" t="n">
         <v>19</v>
@@ -23562,7 +23562,7 @@
         <v>25</v>
       </c>
       <c r="E257" t="n">
-        <v>0.2065637465483386</v>
+        <v>0.5625</v>
       </c>
       <c r="F257" t="n">
         <v>-0.1512000274658203</v>
@@ -23612,7 +23612,7 @@
         </is>
       </c>
       <c r="S257" s="1" t="n">
-        <v>44372</v>
+        <v>25569.04218023148</v>
       </c>
       <c r="T257" t="n">
         <v>16</v>
@@ -23653,7 +23653,7 @@
         <v>11</v>
       </c>
       <c r="E258" t="n">
-        <v>-0.02654868899744272</v>
+        <v>0</v>
       </c>
       <c r="F258" t="n">
         <v>0.948181845925071</v>
@@ -23703,7 +23703,7 @@
         </is>
       </c>
       <c r="S258" s="1" t="n">
-        <v>44407</v>
+        <v>25569.04218063657</v>
       </c>
       <c r="T258" t="n">
         <v>11</v>
@@ -23744,7 +23744,7 @@
         <v>24.70000076293945</v>
       </c>
       <c r="E259" t="n">
-        <v>-0.00803208267690027</v>
+        <v>0.07391307664954129</v>
       </c>
       <c r="F259" t="n">
         <v>0.1380566697199688</v>
@@ -23794,7 +23794,7 @@
         </is>
       </c>
       <c r="S259" s="1" t="n">
-        <v>44545</v>
+        <v>25569.0421822338</v>
       </c>
       <c r="T259" t="n">
         <v>23</v>
@@ -23835,7 +23835,7 @@
         <v>17</v>
       </c>
       <c r="E260" t="n">
-        <v>-0.03682717465035273</v>
+        <v>-0.4925373134328358</v>
       </c>
       <c r="F260" t="n">
         <v>-0.1517647013944738</v>
@@ -23885,7 +23885,7 @@
         </is>
       </c>
       <c r="S260" s="1" t="n">
-        <v>44483</v>
+        <v>25569.0421815162</v>
       </c>
       <c r="T260" t="n">
         <v>33.5</v>
@@ -23926,7 +23926,7 @@
         <v>100.7300033569336</v>
       </c>
       <c r="E261" t="n">
-        <v>-0.0563934111762661</v>
+        <v>0.2914102994478666</v>
       </c>
       <c r="F261" t="n">
         <v>-0.03861815635266934</v>
@@ -23976,7 +23976,7 @@
         </is>
       </c>
       <c r="S261" s="1" t="n">
-        <v>44510</v>
+        <v>25569.0421818287</v>
       </c>
       <c r="T261" t="n">
         <v>78</v>
@@ -24017,7 +24017,7 @@
         <v>4.690000057220459</v>
       </c>
       <c r="E262" t="n">
-        <v>-0.1314814862236891</v>
+        <v>-0.7394444412655301</v>
       </c>
       <c r="F262" t="n">
         <v>-0.2921108970709896</v>
@@ -24067,7 +24067,7 @@
         </is>
       </c>
       <c r="S262" s="1" t="n">
-        <v>44511</v>
+        <v>25569.04218184028</v>
       </c>
       <c r="T262" t="n">
         <v>18</v>
@@ -24108,7 +24108,7 @@
         <v>15.35000038146973</v>
       </c>
       <c r="E263" t="n">
-        <v>-0.2128204932579627</v>
+        <v>0.02333335876464867</v>
       </c>
       <c r="F263" t="n">
         <v>0.4527686438353934</v>
@@ -24158,7 +24158,7 @@
         </is>
       </c>
       <c r="S263" s="1" t="n">
-        <v>44407</v>
+        <v>25569.04218063657</v>
       </c>
       <c r="T263" t="n">
         <v>15</v>
@@ -24199,7 +24199,7 @@
         <v>27.5</v>
       </c>
       <c r="E264" t="n">
-        <v>0.01851851851851852</v>
+        <v>-0.05172413793103448</v>
       </c>
       <c r="F264" t="n">
         <v>-0.2545454545454545</v>
@@ -24249,7 +24249,7 @@
         </is>
       </c>
       <c r="S264" s="1" t="n">
-        <v>44498</v>
+        <v>25569.04218168982</v>
       </c>
       <c r="T264" t="n">
         <v>29</v>
@@ -24290,7 +24290,7 @@
         <v>17.59000015258789</v>
       </c>
       <c r="E265" t="n">
-        <v>-0.09794871012369792</v>
+        <v>0.1726666768391927</v>
       </c>
       <c r="F265" t="n">
         <v>0.3297327564950154</v>
@@ -24340,7 +24340,7 @@
         </is>
       </c>
       <c r="S265" s="1" t="n">
-        <v>44407</v>
+        <v>25569.04218063657</v>
       </c>
       <c r="T265" t="n">
         <v>15</v>
@@ -24381,7 +24381,7 @@
         <v>42.5</v>
       </c>
       <c r="E266" t="n">
-        <v>-0.07608695652173914</v>
+        <v>0.2142857142857143</v>
       </c>
       <c r="F266" t="n">
         <v>0.1689411836511948</v>
@@ -24431,7 +24431,7 @@
         </is>
       </c>
       <c r="S266" s="1" t="n">
-        <v>44377</v>
+        <v>25569.04218028935</v>
       </c>
       <c r="T266" t="n">
         <v>35</v>
@@ -24472,7 +24472,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="E267" t="n">
-        <v>0.1379310155831483</v>
+        <v>-0.3812500238418579</v>
       </c>
       <c r="F267" t="n">
         <v>-0.4545454238947637</v>
@@ -24522,7 +24522,7 @@
         </is>
       </c>
       <c r="S267" s="1" t="n">
-        <v>44512</v>
+        <v>25569.04218185185</v>
       </c>
       <c r="T267" t="n">
         <v>16</v>
@@ -24563,7 +24563,7 @@
         <v>29.10000038146973</v>
       </c>
       <c r="E268" t="n">
-        <v>0.1192307839026818</v>
+        <v>0.4550000190734865</v>
       </c>
       <c r="F268" t="n">
         <v>0.2178693526504706</v>
@@ -24613,7 +24613,7 @@
         </is>
       </c>
       <c r="S268" s="1" t="n">
-        <v>44490</v>
+        <v>25569.04218159722</v>
       </c>
       <c r="T268" t="n">
         <v>20</v>
@@ -24654,7 +24654,7 @@
         <v>93.38999938964844</v>
       </c>
       <c r="E269" t="n">
-        <v>0.07098626901421044</v>
+        <v>0.4367692213792067</v>
       </c>
       <c r="F269" t="n">
         <v>-0.1737872987858487</v>
@@ -24704,7 +24704,7 @@
         </is>
       </c>
       <c r="S269" s="1" t="n">
-        <v>44517</v>
+        <v>25569.04218190972</v>
       </c>
       <c r="T269" t="n">
         <v>65</v>
@@ -24745,7 +24745,7 @@
         <v>35.48819732666016</v>
       </c>
       <c r="E270" t="n">
-        <v>0.03761350951066875</v>
+        <v>0.1447805589245214</v>
       </c>
       <c r="F270" t="n">
         <v>0.3177500032785059</v>
@@ -24795,7 +24795,7 @@
         </is>
       </c>
       <c r="S270" s="1" t="n">
-        <v>44377</v>
+        <v>25569.04218028935</v>
       </c>
       <c r="T270" t="n">
         <v>31</v>
@@ -24836,7 +24836,7 @@
         <v>16.31999969482422</v>
       </c>
       <c r="E271" t="n">
-        <v>-0.07535410495475153</v>
+        <v>0.01999998092651367</v>
       </c>
       <c r="F271" t="n">
         <v>0.8370098102234823</v>
@@ -24886,7 +24886,7 @@
         </is>
       </c>
       <c r="S271" s="1" t="n">
-        <v>44400</v>
+        <v>25569.04218055556</v>
       </c>
       <c r="T271" t="n">
         <v>16</v>
@@ -24927,7 +24927,7 @@
         <v>33.5</v>
       </c>
       <c r="E272" t="n">
-        <v>0.1166666666666667</v>
+        <v>0.3958333333333333</v>
       </c>
       <c r="F272" t="n">
         <v>0.01731348749416978</v>
@@ -24977,7 +24977,7 @@
         </is>
       </c>
       <c r="S272" s="1" t="n">
-        <v>44392</v>
+        <v>25569.04218046296</v>
       </c>
       <c r="T272" t="n">
         <v>24</v>
@@ -25018,7 +25018,7 @@
         <v>16.63999938964844</v>
       </c>
       <c r="E273" t="n">
-        <v>0.2464418662298576</v>
+        <v>0.3311999511718753</v>
       </c>
       <c r="F273" t="n">
         <v>-0.2788461273943875</v>
@@ -25068,7 +25068,7 @@
         </is>
       </c>
       <c r="S273" s="1" t="n">
-        <v>44880</v>
+        <v>25569.04218611111</v>
       </c>
       <c r="T273" t="n">
         <v>12.5</v>
@@ -25109,7 +25109,7 @@
         <v>28.96999931335449</v>
       </c>
       <c r="E274" t="n">
-        <v>0.0846125161492665</v>
+        <v>0.3795237768264042</v>
       </c>
       <c r="F274" t="n">
         <v>0.09043841564834416</v>
@@ -25159,7 +25159,7 @@
         </is>
       </c>
       <c r="S274" s="1" t="n">
-        <v>44860</v>
+        <v>25569.04218587963</v>
       </c>
       <c r="T274" t="n">
         <v>21</v>
@@ -25200,7 +25200,7 @@
         <v>18.06999969482422</v>
       </c>
       <c r="E275" t="n">
-        <v>-0.1395238240559896</v>
+        <v>-0.04894738448293585</v>
       </c>
       <c r="F275" t="n">
         <v>0.6591034891286404</v>
@@ -25250,7 +25250,7 @@
         </is>
       </c>
       <c r="S275" s="1" t="n">
-        <v>44568</v>
+        <v>25569.0421825</v>
       </c>
       <c r="T275" t="n">
         <v>19</v>
@@ -25291,7 +25291,7 @@
         <v>18.11000061035156</v>
       </c>
       <c r="E276" t="n">
-        <v>0.02897728510385675</v>
+        <v>0.006111145019531052</v>
       </c>
       <c r="F276" t="n">
         <v>0.07675313875218329</v>
@@ -25339,7 +25339,7 @@
         </is>
       </c>
       <c r="S276" s="1" t="n">
-        <v>44694</v>
+        <v>25569.04218395833</v>
       </c>
       <c r="T276" t="n">
         <v>18</v>
@@ -25380,7 +25380,7 @@
         <v>165</v>
       </c>
       <c r="E277" t="n">
-        <v>-0.3023255813953488</v>
+        <v>3.817518248175182</v>
       </c>
       <c r="F277" t="n">
         <v>-0.2333333333333333</v>
@@ -25430,7 +25430,7 @@
         </is>
       </c>
       <c r="S277" s="1" t="n">
-        <v>44603</v>
+        <v>25569.04218290509</v>
       </c>
       <c r="T277" t="n">
         <v>34.25</v>
@@ -25471,7 +25471,7 @@
         <v>12.22514629364014</v>
       </c>
       <c r="E278" t="n">
-        <v>-0.1690322506812311</v>
+        <v>0.1113769357854673</v>
       </c>
       <c r="F278" t="n">
         <v>0.3858694850883396</v>
@@ -25521,7 +25521,7 @@
         </is>
       </c>
       <c r="S278" s="1" t="n">
-        <v>44876</v>
+        <v>25569.04218606482</v>
       </c>
       <c r="T278" t="n">
         <v>11</v>
@@ -25562,7 +25562,7 @@
         <v>16.20999908447266</v>
       </c>
       <c r="E279" t="n">
-        <v>0.2469230064978966</v>
+        <v>1.078205010829828</v>
       </c>
       <c r="F279" t="n">
         <v>9.178902487295716</v>
@@ -25612,7 +25612,7 @@
         </is>
       </c>
       <c r="S279" s="1" t="n">
-        <v>44757</v>
+        <v>25569.0421846875</v>
       </c>
       <c r="T279" t="n">
         <v>7.8</v>
@@ -25653,7 +25653,7 @@
         <v>16.21714019775391</v>
       </c>
       <c r="E280" t="n">
-        <v>0.007782093947869446</v>
+        <v>-0.2277552286783852</v>
       </c>
       <c r="F280" t="n">
         <v>0.1231531798121295</v>
@@ -25703,7 +25703,7 @@
         </is>
       </c>
       <c r="S280" s="1" t="n">
-        <v>44820</v>
+        <v>25569.04218541667</v>
       </c>
       <c r="T280" t="n">
         <v>21</v>
@@ -25744,7 +25744,7 @@
         <v>15.6899995803833</v>
       </c>
       <c r="E281" t="n">
-        <v>-0.182812554327148</v>
+        <v>0.3074999650319417</v>
       </c>
       <c r="F281" t="n">
         <v>-0.3556405400215911</v>
@@ -25794,7 +25794,7 @@
         </is>
       </c>
       <c r="S281" s="1" t="n">
-        <v>44791</v>
+        <v>25569.04218508102</v>
       </c>
       <c r="T281" t="n">
         <v>12</v>
@@ -25835,7 +25835,7 @@
         <v>10.80000019073486</v>
       </c>
       <c r="E282" t="n">
-        <v>-0.08085104759703292</v>
+        <v>-0.08085104759703321</v>
       </c>
       <c r="F282" t="n">
         <v>-0.1120370385905188</v>
@@ -25885,7 +25885,7 @@
         </is>
       </c>
       <c r="S282" s="1" t="n">
-        <v>44740</v>
+        <v>25569.04218449074</v>
       </c>
       <c r="T282" t="n">
         <v>11.75</v>
@@ -25926,7 +25926,7 @@
         <v>11.64999961853027</v>
       </c>
       <c r="E283" t="n">
-        <v>-0.03719014452500321</v>
+        <v>0.164999961853027</v>
       </c>
       <c r="F283" t="n">
         <v>0.3313305353428439</v>
@@ -25976,7 +25976,7 @@
         </is>
       </c>
       <c r="S283" s="1" t="n">
-        <v>44588</v>
+        <v>25569.04218273148</v>
       </c>
       <c r="T283" t="n">
         <v>10</v>
@@ -26017,7 +26017,7 @@
         <v>28.90410041809082</v>
       </c>
       <c r="E284" t="n">
-        <v>0.03030303030303031</v>
+        <v>-0.02019998582742982</v>
       </c>
       <c r="F284" t="n">
         <v>-0.09588214336832085</v>
@@ -26067,7 +26067,7 @@
         </is>
       </c>
       <c r="S284" s="1" t="n">
-        <v>44574</v>
+        <v>25569.04218256944</v>
       </c>
       <c r="T284" t="n">
         <v>29.5</v>
@@ -26108,7 +26108,7 @@
         <v>15.39999961853027</v>
       </c>
       <c r="E285" t="n">
-        <v>-0.08605345579303648</v>
+        <v>0.02666664123535133</v>
       </c>
       <c r="F285" t="n">
         <v>-0.01818180129266222</v>
@@ -26158,7 +26158,7 @@
         </is>
       </c>
       <c r="S285" s="1" t="n">
-        <v>44645</v>
+        <v>25569.0421833912</v>
       </c>
       <c r="T285" t="n">
         <v>15</v>
@@ -26199,7 +26199,7 @@
         <v>16.79999923706055</v>
       </c>
       <c r="E286" t="n">
-        <v>-0.1157895138389186</v>
+        <v>0.11999994913737</v>
       </c>
       <c r="F286" t="n">
         <v>-0.1261904183428818</v>
@@ -26249,7 +26249,7 @@
         </is>
       </c>
       <c r="S286" s="1" t="n">
-        <v>44596</v>
+        <v>25569.04218282407</v>
       </c>
       <c r="T286" t="n">
         <v>15</v>
@@ -26290,7 +26290,7 @@
         <v>20</v>
       </c>
       <c r="E287" t="n">
-        <v>0.08108108108108109</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="F287" t="n">
         <v>-0.225</v>
@@ -26340,7 +26340,7 @@
         </is>
       </c>
       <c r="S287" s="1" t="n">
-        <v>44687</v>
+        <v>25569.04218387731</v>
       </c>
       <c r="T287" t="n">
         <v>18</v>
@@ -26381,7 +26381,7 @@
         <v>12.89000034332275</v>
       </c>
       <c r="E288" t="n">
-        <v>-0.1737179469153099</v>
+        <v>0.07416669527689586</v>
       </c>
       <c r="F288" t="n">
         <v>-0.08378587237707201</v>
@@ -26431,7 +26431,7 @@
         </is>
       </c>
       <c r="S288" s="1" t="n">
-        <v>44687</v>
+        <v>25569.04218387731</v>
       </c>
       <c r="T288" t="n">
         <v>12</v>
@@ -26472,7 +26472,7 @@
         <v>26.16184425354004</v>
       </c>
       <c r="E289" t="n">
-        <v>-0.04787235265766027</v>
+        <v>0.09007684389750163</v>
       </c>
       <c r="F289" t="n">
         <v>0.004841597332699734</v>
@@ -26522,7 +26522,7 @@
         </is>
       </c>
       <c r="S289" s="1" t="n">
-        <v>44664</v>
+        <v>25569.04218361111</v>
       </c>
       <c r="T289" t="n">
         <v>24</v>
@@ -26563,7 +26563,7 @@
         <v>15.36999988555908</v>
       </c>
       <c r="E290" t="n">
-        <v>-0.1897733030101421</v>
+        <v>-0.09588235967299528</v>
       </c>
       <c r="F290" t="n">
         <v>0.1307741893411475</v>
@@ -26613,7 +26613,7 @@
         </is>
       </c>
       <c r="S290" s="1" t="n">
-        <v>44854</v>
+        <v>25569.04218581018</v>
       </c>
       <c r="T290" t="n">
         <v>17</v>
@@ -26654,7 +26654,7 @@
         <v>15.56606006622314</v>
       </c>
       <c r="E291" t="n">
-        <v>0</v>
+        <v>-0.221696996688843</v>
       </c>
       <c r="F291" t="n">
         <v>0.015909194087046</v>
@@ -26704,7 +26704,7 @@
         </is>
       </c>
       <c r="S291" s="1" t="n">
-        <v>44953</v>
+        <v>25569.04218695602</v>
       </c>
       <c r="T291" t="n">
         <v>20</v>
@@ -26745,7 +26745,7 @@
         <v>10.01000022888184</v>
       </c>
       <c r="E292" t="n">
-        <v>0</v>
+        <v>0.001000022888183949</v>
       </c>
       <c r="F292" t="inlineStr"/>
       <c r="G292" t="n">
@@ -26791,7 +26791,7 @@
         </is>
       </c>
       <c r="S292" s="1" t="n">
-        <v>45289</v>
+        <v>25569.04219084491</v>
       </c>
       <c r="T292" t="n">
         <v>10</v>
@@ -26832,7 +26832,7 @@
         <v>12.95170879364014</v>
       </c>
       <c r="E293" t="n">
-        <v>-0.03473683407432154</v>
+        <v>-0.3183311161242031</v>
       </c>
       <c r="F293" t="n">
         <v>-0.07360952564754594</v>
@@ -26882,7 +26882,7 @@
         </is>
       </c>
       <c r="S293" s="1" t="n">
-        <v>45224</v>
+        <v>25569.04219009259</v>
       </c>
       <c r="T293" t="n">
         <v>19</v>
@@ -26923,7 +26923,7 @@
         <v>47.52999877929688</v>
       </c>
       <c r="E294" t="n">
-        <v>-0.03197555485977685</v>
+        <v>0.357999965122768</v>
       </c>
       <c r="F294" t="n">
         <v>-0.1009888356898366</v>
@@ -26973,7 +26973,7 @@
         </is>
       </c>
       <c r="S294" s="1" t="n">
-        <v>45126</v>
+        <v>25569.04218895833</v>
       </c>
       <c r="T294" t="n">
         <v>35</v>
@@ -27014,7 +27014,7 @@
         <v>15.94999980926514</v>
       </c>
       <c r="E295" t="n">
-        <v>0.02903224575904108</v>
+        <v>-0.003125011920928733</v>
       </c>
       <c r="F295" t="n">
         <v>-0.2451410591955521</v>
@@ -27064,7 +27064,7 @@
         </is>
       </c>
       <c r="S295" s="1" t="n">
-        <v>45121</v>
+        <v>25569.04218890046</v>
       </c>
       <c r="T295" t="n">
         <v>16</v>
@@ -27105,7 +27105,7 @@
         <v>10.10000038146973</v>
       </c>
       <c r="E296" t="n">
-        <v>-0.004926033393071871</v>
+        <v>0.01000003814697301</v>
       </c>
       <c r="F296" t="n">
         <v>0.008910811437066278</v>
@@ -27153,7 +27153,7 @@
         </is>
       </c>
       <c r="S296" s="1" t="n">
-        <v>45061</v>
+        <v>25569.04218820602</v>
       </c>
       <c r="T296" t="n">
         <v>10</v>
@@ -27194,7 +27194,7 @@
         <v>24.09622383117676</v>
       </c>
       <c r="E297" t="n">
-        <v>0.05366231472925109</v>
+        <v>0.09528290141712552</v>
       </c>
       <c r="F297" t="n">
         <v>-0.02416356185816269</v>
@@ -27244,7 +27244,7 @@
         </is>
       </c>
       <c r="S297" s="1" t="n">
-        <v>45050</v>
+        <v>25569.0421880787</v>
       </c>
       <c r="T297" t="n">
         <v>22</v>
@@ -27285,7 +27285,7 @@
         <v>14.82497215270996</v>
       </c>
       <c r="E298" t="n">
-        <v>-0.0314285278320313</v>
+        <v>-0.1763904359605578</v>
       </c>
       <c r="F298" t="n">
         <v>0.07256609956442894</v>
@@ -27335,7 +27335,7 @@
         </is>
       </c>
       <c r="S298" s="1" t="n">
-        <v>44994</v>
+        <v>25569.04218743055</v>
       </c>
       <c r="T298" t="n">
         <v>18</v>
@@ -27426,7 +27426,7 @@
         </is>
       </c>
       <c r="S299" s="1" t="n">
-        <v>45275</v>
+        <v>25569.04219068287</v>
       </c>
       <c r="T299" t="n">
         <v>15.5</v>
@@ -27467,7 +27467,7 @@
         <v>15</v>
       </c>
       <c r="E300" t="n">
-        <v>-0.1666666666666667</v>
+        <v>-0.3478260869565217</v>
       </c>
       <c r="F300" t="n">
         <v>-0.4173333485921224</v>
@@ -27517,7 +27517,7 @@
         </is>
       </c>
       <c r="S300" s="1" t="n">
-        <v>45198</v>
+        <v>25569.04218979167</v>
       </c>
       <c r="T300" t="n">
         <v>23</v>
@@ -27558,7 +27558,7 @@
         <v>22.90999984741211</v>
       </c>
       <c r="E301" t="n">
-        <v>-0.0750908589413684</v>
+        <v>0.2727777693006728</v>
       </c>
       <c r="F301" t="n">
         <v>0.1230903410565829</v>
@@ -27608,7 +27608,7 @@
         </is>
       </c>
       <c r="S301" s="1" t="n">
-        <v>45106</v>
+        <v>25569.04218872685</v>
       </c>
       <c r="T301" t="n">
         <v>18</v>
@@ -27649,7 +27649,7 @@
         <v>21.45981216430664</v>
       </c>
       <c r="E302" t="n">
-        <v>-0.0009229560541419344</v>
+        <v>0.1005031879131611</v>
       </c>
       <c r="F302" t="n">
         <v>0.09838343233679273</v>
@@ -27699,7 +27699,7 @@
         </is>
       </c>
       <c r="S302" s="1" t="n">
-        <v>45072</v>
+        <v>25569.04218833333</v>
       </c>
       <c r="T302" t="n">
         <v>19.5</v>
@@ -27740,7 +27740,7 @@
         <v>10.17000007629395</v>
       </c>
       <c r="E303" t="n">
-        <v>0</v>
+        <v>0.01700000762939506</v>
       </c>
       <c r="F303" t="n">
         <v>0.001966519561388587</v>
@@ -27788,7 +27788,7 @@
         </is>
       </c>
       <c r="S303" s="1" t="n">
-        <v>45184</v>
+        <v>25569.04218962963</v>
       </c>
       <c r="T303" t="n">
         <v>10</v>
@@ -27829,7 +27829,7 @@
         <v>10.05000019073486</v>
       </c>
       <c r="E304" t="n">
-        <v>0.05789475691945929</v>
+        <v>-0.08636361902410367</v>
       </c>
       <c r="F304" t="n">
         <v>0.3532338431204831</v>
@@ -27879,7 +27879,7 @@
         </is>
       </c>
       <c r="S304" s="1" t="n">
-        <v>45233</v>
+        <v>25569.04219019676</v>
       </c>
       <c r="T304" t="n">
         <v>11</v>
@@ -27920,7 +27920,7 @@
         <v>13.66757106781006</v>
       </c>
       <c r="E305" t="n">
-        <v>0.00899738983759526</v>
+        <v>-0.3491632824852352</v>
       </c>
       <c r="F305" t="n">
         <v>0.2324839704351684</v>
@@ -27970,7 +27970,7 @@
         </is>
       </c>
       <c r="S305" s="1" t="n">
-        <v>45106</v>
+        <v>25569.04218872685</v>
       </c>
       <c r="T305" t="n">
         <v>21</v>
@@ -28011,7 +28011,7 @@
         <v>12.35171318054199</v>
       </c>
       <c r="E306" t="n">
-        <v>-0.0152672333675928</v>
+        <v>-0.1177347728184293</v>
       </c>
       <c r="F306" t="n">
         <v>0.04263560564589541</v>
@@ -28061,7 +28061,7 @@
         </is>
       </c>
       <c r="S306" s="1" t="n">
-        <v>45106</v>
+        <v>25569.04218872685</v>
       </c>
       <c r="T306" t="n">
         <v>14</v>
@@ -28102,7 +28102,7 @@
         <v>14.01768207550049</v>
       </c>
       <c r="E307" t="n">
-        <v>-0.01639344262295082</v>
+        <v>-0.06548786163330066</v>
       </c>
       <c r="F307" t="n">
         <v>-0.03333329931649976</v>
@@ -28152,7 +28152,7 @@
         </is>
       </c>
       <c r="S307" s="1" t="n">
-        <v>45240</v>
+        <v>25569.04219027778</v>
       </c>
       <c r="T307" t="n">
         <v>15</v>
@@ -28193,7 +28193,7 @@
         <v>21.04999923706055</v>
       </c>
       <c r="E308" t="n">
-        <v>-0.1136842426500822</v>
+        <v>0.1078946966873974</v>
       </c>
       <c r="F308" t="n">
         <v>-0.2289786161292655</v>
@@ -28243,7 +28243,7 @@
         </is>
       </c>
       <c r="S308" s="1" t="n">
-        <v>44966</v>
+        <v>25569.04218710648</v>
       </c>
       <c r="T308" t="n">
         <v>19</v>
@@ -28284,7 +28284,7 @@
         <v>6.199999809265137</v>
       </c>
       <c r="E309" t="n">
-        <v>-0.1142857415335519</v>
+        <v>-0.6736842205649928</v>
       </c>
       <c r="F309" t="n">
         <v>-0.08064516377126521</v>
@@ -28334,7 +28334,7 @@
         </is>
       </c>
       <c r="S309" s="1" t="n">
-        <v>45196</v>
+        <v>25569.04218976852</v>
       </c>
       <c r="T309" t="n">
         <v>19</v>
@@ -28375,7 +28375,7 @@
         <v>63.59000015258789</v>
       </c>
       <c r="E310" t="n">
-        <v>0.1335116200033754</v>
+        <v>0.2468627480899586</v>
       </c>
       <c r="F310" t="n">
         <v>-0.2110395023028858</v>
@@ -28425,7 +28425,7 @@
         </is>
       </c>
       <c r="S310" s="1" t="n">
-        <v>45183</v>
+        <v>25569.04218961806</v>
       </c>
       <c r="T310" t="n">
         <v>51</v>
@@ -28466,7 +28466,7 @@
         <v>40.20000076293945</v>
       </c>
       <c r="E311" t="n">
-        <v>-0.01951217651367188</v>
+        <v>-0.1260869399360988</v>
       </c>
       <c r="F311" t="n">
         <v>0.04104471840465188</v>
@@ -28516,7 +28516,7 @@
         </is>
       </c>
       <c r="S311" s="1" t="n">
-        <v>45210</v>
+        <v>25569.04218993055</v>
       </c>
       <c r="T311" t="n">
         <v>46</v>
@@ -28557,7 +28557,7 @@
         <v>30.45999908447266</v>
       </c>
       <c r="E312" t="n">
-        <v>0.004948849263386476</v>
+        <v>0.2691666285196941</v>
       </c>
       <c r="F312" t="n">
         <v>0.02429421210468852</v>
@@ -28607,7 +28607,7 @@
         </is>
       </c>
       <c r="S312" s="1" t="n">
-        <v>44966</v>
+        <v>25569.04218710648</v>
       </c>
       <c r="T312" t="n">
         <v>24</v>
@@ -28648,7 +28648,7 @@
         <v>19.10000038146973</v>
       </c>
       <c r="E313" t="n">
-        <v>0.01058205116276113</v>
+        <v>0.2733333587646486</v>
       </c>
       <c r="F313" t="n">
         <v>0.02198953235107877</v>
@@ -28698,7 +28698,7 @@
         </is>
       </c>
       <c r="S313" s="1" t="n">
-        <v>44939</v>
+        <v>25569.04218679398</v>
       </c>
       <c r="T313" t="n">
         <v>15</v>
@@ -28739,7 +28739,7 @@
         <v>10.07999992370605</v>
       </c>
       <c r="E314" t="n">
-        <v>-0.001980243268145447</v>
+        <v>0.007999992370604937</v>
       </c>
       <c r="F314" t="n">
         <v>0.002976164007763363</v>
@@ -28787,7 +28787,7 @@
         </is>
       </c>
       <c r="S314" s="1" t="n">
-        <v>45260</v>
+        <v>25569.04219050926</v>
       </c>
       <c r="T314" t="n">
         <v>10</v>
@@ -28828,7 +28828,7 @@
         <v>10.09000015258789</v>
       </c>
       <c r="E315" t="n">
-        <v>0.0009920862061037806</v>
+        <v>0.009000015258789063</v>
       </c>
       <c r="F315" t="n">
         <v>-0.0009911029465416877</v>
@@ -28876,7 +28876,7 @@
         </is>
       </c>
       <c r="S315" s="1" t="n">
-        <v>45091</v>
+        <v>25569.04218855324</v>
       </c>
       <c r="T315" t="n">
         <v>10</v>
@@ -28917,7 +28917,7 @@
         <v>21.22999954223633</v>
       </c>
       <c r="E316" t="n">
-        <v>-0.0125581608262173</v>
+        <v>0.2488235024844901</v>
       </c>
       <c r="F316" t="n">
         <v>0.1186999770183801</v>
@@ -28967,7 +28967,7 @@
         </is>
       </c>
       <c r="S316" s="1" t="n">
-        <v>45121</v>
+        <v>25569.04218890046</v>
       </c>
       <c r="T316" t="n">
         <v>17</v>
@@ -29008,7 +29008,7 @@
         <v>6.079999923706055</v>
       </c>
       <c r="E317" t="n">
-        <v>0.3362636634799973</v>
+        <v>-0.3920000076293945</v>
       </c>
       <c r="F317" t="n">
         <v>-0.6463815588246089</v>
@@ -29058,7 +29058,7 @@
         </is>
       </c>
       <c r="S317" s="1" t="n">
-        <v>45176</v>
+        <v>25569.04218953704</v>
       </c>
       <c r="T317" t="n">
         <v>10</v>
@@ -29099,7 +29099,7 @@
         <v>10.14000034332275</v>
       </c>
       <c r="E318" t="n">
-        <v>-0.005882300692582611</v>
+        <v>0.01400003433227504</v>
       </c>
       <c r="F318" t="n">
         <v>0.01183430783985157</v>
@@ -29147,7 +29147,7 @@
         </is>
       </c>
       <c r="S318" s="1" t="n">
-        <v>45184</v>
+        <v>25569.04218962963</v>
       </c>
       <c r="T318" t="n">
         <v>10</v>
@@ -29188,7 +29188,7 @@
         <v>18.44000053405762</v>
       </c>
       <c r="E319" t="n">
-        <v>-0.1260663412000766</v>
+        <v>0.1525000333786013</v>
       </c>
       <c r="F319" t="n">
         <v>-0.1339479498640394</v>
@@ -29238,7 +29238,7 @@
         </is>
       </c>
       <c r="S319" s="1" t="n">
-        <v>44967</v>
+        <v>25569.04218711806</v>
       </c>
       <c r="T319" t="n">
         <v>16</v>
@@ -29279,7 +29279,7 @@
         <v>26</v>
       </c>
       <c r="E320" t="n">
-        <v>0.04</v>
+        <v>0.7333333333333333</v>
       </c>
       <c r="F320" t="n">
         <v>-0.1284615443303035</v>
@@ -29329,7 +29329,7 @@
         </is>
       </c>
       <c r="S320" s="1" t="n">
-        <v>44960</v>
+        <v>25569.04218703704</v>
       </c>
       <c r="T320" t="n">
         <v>15</v>
@@ -29370,7 +29370,7 @@
         <v>43.77999877929688</v>
       </c>
       <c r="E321" t="n">
-        <v>0.04238092331659226</v>
+        <v>0.9899999445134946</v>
       </c>
       <c r="F321" t="n">
         <v>0.3044769804187001</v>
@@ -29420,7 +29420,7 @@
         </is>
       </c>
       <c r="S321" s="1" t="n">
-        <v>45092</v>
+        <v>25569.04218856481</v>
       </c>
       <c r="T321" t="n">
         <v>22</v>
@@ -29461,7 +29461,7 @@
         <v>32.7599983215332</v>
       </c>
       <c r="E322" t="n">
-        <v>-0.1085714742439945</v>
+        <v>0.09199994405110677</v>
       </c>
       <c r="F322" t="n">
         <v>-0.1312576146938979</v>
@@ -29511,7 +29511,7 @@
         </is>
       </c>
       <c r="S322" s="1" t="n">
-        <v>45189</v>
+        <v>25569.0421896875</v>
       </c>
       <c r="T322" t="n">
         <v>30</v>
@@ -29552,7 +29552,7 @@
         <v>34.33864212036133</v>
       </c>
       <c r="E323" t="n">
-        <v>0.02074201267798989</v>
+        <v>0.2263800757271903</v>
       </c>
       <c r="F323" t="n">
         <v>0.2017745820247334</v>
@@ -29602,7 +29602,7 @@
         </is>
       </c>
       <c r="S323" s="1" t="n">
-        <v>45394</v>
+        <v>25569.04219206018</v>
       </c>
       <c r="T323" t="n">
         <v>28</v>
@@ -29643,7 +29643,7 @@
         <v>16</v>
       </c>
       <c r="E324" t="n">
-        <v>0.1065006886438692</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="F324" t="n">
         <v>0.3125</v>
@@ -29693,7 +29693,7 @@
         </is>
       </c>
       <c r="S324" s="1" t="n">
-        <v>45561</v>
+        <v>25569.04219399306</v>
       </c>
       <c r="T324" t="n">
         <v>14</v>
@@ -29734,7 +29734,7 @@
         <v>20</v>
       </c>
       <c r="E325" t="n">
-        <v>-0.1666666666666667</v>
+        <v>0.1111111111111111</v>
       </c>
       <c r="F325" t="n">
         <v>-0.03350000381469727</v>
@@ -29784,7 +29784,7 @@
         </is>
       </c>
       <c r="S325" s="1" t="n">
-        <v>45317</v>
+        <v>25569.04219116898</v>
       </c>
       <c r="T325" t="n">
         <v>18</v>
@@ -29825,7 +29825,7 @@
         <v>37</v>
       </c>
       <c r="E326" t="n">
-        <v>-0.0414507393101011</v>
+        <v>0.15625</v>
       </c>
       <c r="F326" t="n">
         <v>-0.08567562618771114</v>
@@ -29875,7 +29875,7 @@
         </is>
       </c>
       <c r="S326" s="1" t="n">
-        <v>45407</v>
+        <v>25569.04219221065</v>
       </c>
       <c r="T326" t="n">
         <v>32</v>
@@ -29916,7 +29916,7 @@
         <v>40.25</v>
       </c>
       <c r="E327" t="n">
-        <v>0.00625</v>
+        <v>0.08783783783783784</v>
       </c>
       <c r="F327" t="n">
         <v>0.142111831570264</v>
@@ -29966,7 +29966,7 @@
         </is>
       </c>
       <c r="S327" s="1" t="n">
-        <v>45457</v>
+        <v>25569.04219278935</v>
       </c>
       <c r="T327" t="n">
         <v>37</v>
@@ -30007,7 +30007,7 @@
         <v>22.01000022888184</v>
       </c>
       <c r="E328" t="n">
-        <v>0.0004545558582652699</v>
+        <v>0.2947058958165788</v>
       </c>
       <c r="F328" t="n">
         <v>0.2421626473548125</v>
@@ -30057,7 +30057,7 @@
         </is>
       </c>
       <c r="S328" s="1" t="n">
-        <v>45491</v>
+        <v>25569.04219318287</v>
       </c>
       <c r="T328" t="n">
         <v>17</v>
@@ -30098,7 +30098,7 @@
         <v>10.03999996185303</v>
       </c>
       <c r="E329" t="n">
-        <v>0.003999996185302735</v>
+        <v>0.003999996185302912</v>
       </c>
       <c r="F329" t="n">
         <v>0.003984059960658085</v>
@@ -30146,7 +30146,7 @@
         </is>
       </c>
       <c r="S329" s="1" t="n">
-        <v>45478</v>
+        <v>25569.04219303241</v>
       </c>
       <c r="T329" t="n">
         <v>10</v>
@@ -30187,7 +30187,7 @@
         <v>37.16999816894531</v>
       </c>
       <c r="E330" t="n">
-        <v>0.2817240747912177</v>
+        <v>0.9563156931023848</v>
       </c>
       <c r="F330" t="n">
         <v>-0.04465966987318825</v>
@@ -30237,7 +30237,7 @@
         </is>
       </c>
       <c r="S330" s="1" t="n">
-        <v>45316</v>
+        <v>25569.04219115741</v>
       </c>
       <c r="T330" t="n">
         <v>19</v>
@@ -30278,7 +30278,7 @@
         <v>90.14015197753906</v>
       </c>
       <c r="E331" t="n">
-        <v>0.03751352671030413</v>
+        <v>-0.02021573937457541</v>
       </c>
       <c r="F331" t="n">
         <v>0.1106594666881086</v>
@@ -30326,7 +30326,7 @@
         </is>
       </c>
       <c r="S331" s="1" t="n">
-        <v>45310</v>
+        <v>25569.04219108796</v>
       </c>
       <c r="T331" t="n">
         <v>92</v>
@@ -30367,7 +30367,7 @@
         <v>18.30999946594238</v>
       </c>
       <c r="E332" t="n">
-        <v>-0.1862222459581163</v>
+        <v>0.8309999465942379</v>
       </c>
       <c r="F332" t="n">
         <v>0.1261606466776663</v>
@@ -30417,7 +30417,7 @@
         </is>
       </c>
       <c r="S332" s="1" t="n">
-        <v>45561</v>
+        <v>25569.04219399306</v>
       </c>
       <c r="T332" t="n">
         <v>10</v>
@@ -30458,7 +30458,7 @@
         <v>98</v>
       </c>
       <c r="E333" t="n">
-        <v>-0.05084745762711865</v>
+        <v>0.1136363636363636</v>
       </c>
       <c r="F333" t="n">
         <v>-0.1252040473782286</v>
@@ -30508,7 +30508,7 @@
         </is>
       </c>
       <c r="S333" s="1" t="n">
-        <v>45401</v>
+        <v>25569.04219214121</v>
       </c>
       <c r="T333" t="n">
         <v>88</v>
@@ -30549,7 +30549,7 @@
         <v>23.64999961853027</v>
       </c>
       <c r="E334" t="n">
-        <v>0.02826085297957711</v>
+        <v>0.3138888676961261</v>
       </c>
       <c r="F334" t="n">
         <v>-0.1019027436061277</v>
@@ -30599,7 +30599,7 @@
         </is>
       </c>
       <c r="S334" s="1" t="n">
-        <v>45548</v>
+        <v>25569.04219384259</v>
       </c>
       <c r="T334" t="n">
         <v>18</v>
@@ -30640,7 +30640,7 @@
         <v>9.989999771118164</v>
       </c>
       <c r="E335" t="n">
-        <v>0.002005968260150868</v>
+        <v>-0.001000022888183594</v>
       </c>
       <c r="F335" t="n">
         <v>0.004004000277224252</v>
@@ -30688,7 +30688,7 @@
         </is>
       </c>
       <c r="S335" s="1" t="n">
-        <v>45558</v>
+        <v>25569.04219395833</v>
       </c>
       <c r="T335" t="n">
         <v>10</v>
@@ -30729,7 +30729,7 @@
         <v>9.960000038146973</v>
       </c>
       <c r="E336" t="n">
-        <v>-0.002003958417504492</v>
+        <v>-0.003999996185302735</v>
       </c>
       <c r="F336" t="n">
         <v>0</v>
@@ -30777,7 +30777,7 @@
         </is>
       </c>
       <c r="S336" s="1" t="n">
-        <v>45490</v>
+        <v>25569.0421931713</v>
       </c>
       <c r="T336" t="n">
         <v>10</v>
@@ -30818,7 +30818,7 @@
         <v>12</v>
       </c>
       <c r="E337" t="n">
-        <v>-0.25</v>
+        <v>0</v>
       </c>
       <c r="F337" t="n">
         <v>-0.03833333651224772</v>
@@ -30868,7 +30868,7 @@
         </is>
       </c>
       <c r="S337" s="1" t="n">
-        <v>45492</v>
+        <v>25569.04219319444</v>
       </c>
       <c r="T337" t="n">
         <v>12</v>
@@ -30909,7 +30909,7 @@
         <v>9.899999618530273</v>
       </c>
       <c r="E338" t="n">
-        <v>-0.005025144893802372</v>
+        <v>-0.01000003814697266</v>
       </c>
       <c r="F338" t="n">
         <v>0.003030372505202342</v>
@@ -30957,7 +30957,7 @@
         </is>
       </c>
       <c r="S338" s="1" t="n">
-        <v>45639</v>
+        <v>25569.04219489583</v>
       </c>
       <c r="T338" t="n">
         <v>10</v>
@@ -30998,7 +30998,7 @@
         <v>10.02999973297119</v>
       </c>
       <c r="E339" t="n">
-        <v>-0.004960336419970924</v>
+        <v>0.002999973297118963</v>
       </c>
       <c r="F339" t="n">
         <v>0</v>
@@ -31048,7 +31048,7 @@
         </is>
       </c>
       <c r="S339" s="1" t="n">
-        <v>45464</v>
+        <v>25569.04219287037</v>
       </c>
       <c r="T339" t="n">
         <v>10</v>
@@ -31089,7 +31089,7 @@
         <v>9.939999580383301</v>
       </c>
       <c r="E340" t="n">
-        <v>-0.001005048148093835</v>
+        <v>-0.006000041961669922</v>
       </c>
       <c r="F340" t="n">
         <v>0.001006059286116219</v>
@@ -31137,7 +31137,7 @@
         </is>
       </c>
       <c r="S340" s="1" t="n">
-        <v>45625</v>
+        <v>25569.0421947338</v>
       </c>
       <c r="T340" t="n">
         <v>10</v>
@@ -31178,7 +31178,7 @@
         <v>663.352294921875</v>
       </c>
       <c r="E341" t="n">
-        <v>-0.02631578947368427</v>
+        <v>34.3787890625</v>
       </c>
       <c r="F341" t="n">
         <v>-0.4243243969377544</v>
@@ -31228,7 +31228,7 @@
         </is>
       </c>
       <c r="S341" s="1" t="n">
-        <v>45485</v>
+        <v>25569.04219311343</v>
       </c>
       <c r="T341" t="n">
         <v>18.75</v>
@@ -31269,7 +31269,7 @@
         <v>23.95000076293945</v>
       </c>
       <c r="E342" t="n">
-        <v>0.01526072946260958</v>
+        <v>0.1404762268066405</v>
       </c>
       <c r="F342" t="n">
         <v>0.1465552488401011</v>
@@ -31319,7 +31319,7 @@
         </is>
       </c>
       <c r="S342" s="1" t="n">
-        <v>45401</v>
+        <v>25569.04219214121</v>
       </c>
       <c r="T342" t="n">
         <v>21</v>
@@ -31360,7 +31360,7 @@
         <v>9.979999542236328</v>
       </c>
       <c r="E343" t="n">
-        <v>0.003015048597614702</v>
+        <v>-0.002000045776367187</v>
       </c>
       <c r="F343" t="n">
         <v>0.005010039381590912</v>
@@ -31408,7 +31408,7 @@
         </is>
       </c>
       <c r="S343" s="1" t="n">
-        <v>45572</v>
+        <v>25569.04219412037</v>
       </c>
       <c r="T343" t="n">
         <v>10</v>
@@ -31449,7 +31449,7 @@
         <v>22.93155097961426</v>
       </c>
       <c r="E344" t="n">
-        <v>0.2184210325542249</v>
+        <v>0.3489147635067212</v>
       </c>
       <c r="F344" t="n">
         <v>0.4600434160707333</v>
@@ -31499,7 +31499,7 @@
         </is>
       </c>
       <c r="S344" s="1" t="n">
-        <v>45471</v>
+        <v>25569.04219295139</v>
       </c>
       <c r="T344" t="n">
         <v>17</v>
@@ -31540,7 +31540,7 @@
         <v>18</v>
       </c>
       <c r="E345" t="n">
-        <v>-0.02964955577797104</v>
+        <v>0</v>
       </c>
       <c r="F345" t="n">
         <v>0.07166671752929688</v>
@@ -31590,7 +31590,7 @@
         </is>
       </c>
       <c r="S345" s="1" t="n">
-        <v>45561</v>
+        <v>25569.04219399306</v>
       </c>
       <c r="T345" t="n">
         <v>18</v>
@@ -31631,7 +31631,7 @@
         <v>15.39999961853027</v>
       </c>
       <c r="E346" t="n">
-        <v>0.06206893920898438</v>
+        <v>-0.03750002384185813</v>
       </c>
       <c r="F346" t="n">
         <v>0.006493531425117677</v>
@@ -31681,7 +31681,7 @@
         </is>
       </c>
       <c r="S346" s="1" t="n">
-        <v>45387</v>
+        <v>25569.04219197917</v>
       </c>
       <c r="T346" t="n">
         <v>16</v>
@@ -31722,7 +31722,7 @@
         <v>20.79999923706055</v>
       </c>
       <c r="E347" t="n">
-        <v>0.1555555131700304</v>
+        <v>0.2235293668859147</v>
       </c>
       <c r="F347" t="n">
         <v>-0.02163456115849426</v>
@@ -31772,7 +31772,7 @@
         </is>
       </c>
       <c r="S347" s="1" t="n">
-        <v>45450</v>
+        <v>25569.04219270833</v>
       </c>
       <c r="T347" t="n">
         <v>17</v>
@@ -31813,7 +31813,7 @@
         <v>13.51000022888184</v>
       </c>
       <c r="E348" t="n">
-        <v>0.0895161810080061</v>
+        <v>-0.1812121073404946</v>
       </c>
       <c r="F348" t="n">
         <v>-0.4300518372454216</v>
@@ -31863,7 +31863,7 @@
         </is>
       </c>
       <c r="S348" s="1" t="n">
-        <v>45623</v>
+        <v>25569.04219471065</v>
       </c>
       <c r="T348" t="n">
         <v>16.5</v>
@@ -31904,7 +31904,7 @@
         <v>10.02000045776367</v>
       </c>
       <c r="E349" t="n">
-        <v>0.004008107952115226</v>
+        <v>0.00200004577636701</v>
       </c>
       <c r="F349" t="n">
         <v>-0.004491025373065573</v>
@@ -31954,7 +31954,7 @@
         </is>
       </c>
       <c r="S349" s="1" t="n">
-        <v>45505</v>
+        <v>25569.04219334491</v>
       </c>
       <c r="T349" t="n">
         <v>10</v>
@@ -31995,7 +31995,7 @@
         <v>9.854999542236328</v>
       </c>
       <c r="E350" t="n">
-        <v>-0.0005071110157221824</v>
+        <v>-0.01450004577636719</v>
       </c>
       <c r="F350" t="n">
         <v>0.001522104923340258</v>
@@ -32043,7 +32043,7 @@
         </is>
       </c>
       <c r="S350" s="1" t="n">
-        <v>45642</v>
+        <v>25569.04219493056</v>
       </c>
       <c r="T350" t="n">
         <v>10</v>
@@ -32132,7 +32132,7 @@
         </is>
       </c>
       <c r="S351" s="1" t="n">
-        <v>45642</v>
+        <v>25569.04219493056</v>
       </c>
       <c r="T351" t="n">
         <v>10</v>
@@ -32173,7 +32173,7 @@
         <v>22</v>
       </c>
       <c r="E352" t="n">
-        <v>0.02325581395348837</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="F352" t="n">
         <v>-0.173181793906472</v>
@@ -32223,7 +32223,7 @@
         </is>
       </c>
       <c r="S352" s="1" t="n">
-        <v>45576</v>
+        <v>25569.04219416667</v>
       </c>
       <c r="T352" t="n">
         <v>17</v>
@@ -32264,7 +32264,7 @@
         <v>26.85000038146973</v>
       </c>
       <c r="E353" t="n">
-        <v>0.03269232236422025</v>
+        <v>0.3425000190734865</v>
       </c>
       <c r="F353" t="n">
         <v>0.08081936854613792</v>
@@ -32312,7 +32312,7 @@
         </is>
       </c>
       <c r="S353" s="1" t="n">
-        <v>45497</v>
+        <v>25569.04219325231</v>
       </c>
       <c r="T353" t="n">
         <v>20</v>
@@ -32353,7 +32353,7 @@
         <v>10.01000022888184</v>
       </c>
       <c r="E354" t="n">
-        <v>0</v>
+        <v>0.001000022888183949</v>
       </c>
       <c r="F354" t="n">
         <v>0.002996976252271526</v>
@@ -32401,7 +32401,7 @@
         </is>
       </c>
       <c r="S354" s="1" t="n">
-        <v>45604</v>
+        <v>25569.04219449074</v>
       </c>
       <c r="T354" t="n">
         <v>10</v>
@@ -32442,7 +32442,7 @@
         <v>9.960000038146973</v>
       </c>
       <c r="E355" t="n">
-        <v>0</v>
+        <v>-0.003999996185302735</v>
       </c>
       <c r="F355" t="n">
         <v>0.005020099452144747</v>
@@ -32488,7 +32488,7 @@
         </is>
       </c>
       <c r="S355" s="1" t="n">
-        <v>45593</v>
+        <v>25569.04219436342</v>
       </c>
       <c r="T355" t="n">
         <v>10</v>
@@ -32529,7 +32529,7 @@
         <v>23.79999923706055</v>
       </c>
       <c r="E356" t="n">
-        <v>0.0347825755243716</v>
+        <v>0.3999999551212088</v>
       </c>
       <c r="F356" t="n">
         <v>0.09201683211180205</v>
@@ -32579,7 +32579,7 @@
         </is>
       </c>
       <c r="S356" s="1" t="n">
-        <v>45435</v>
+        <v>25569.04219253472</v>
       </c>
       <c r="T356" t="n">
         <v>17</v>
@@ -32620,7 +32620,7 @@
         <v>10.3100004196167</v>
       </c>
       <c r="E357" t="n">
-        <v>0.005853699474799924</v>
+        <v>-0.3126666386922201</v>
       </c>
       <c r="F357" t="n">
         <v>0.08147421578328154</v>
@@ -32670,7 +32670,7 @@
         </is>
       </c>
       <c r="S357" s="1" t="n">
-        <v>45331</v>
+        <v>25569.04219133102</v>
       </c>
       <c r="T357" t="n">
         <v>15</v>
@@ -32711,7 +32711,7 @@
         <v>10.05000019073486</v>
       </c>
       <c r="E358" t="n">
-        <v>-0.0009940584954982498</v>
+        <v>0.005000019073485973</v>
       </c>
       <c r="F358" t="n">
         <v>0.003980095631232273</v>
@@ -32761,7 +32761,7 @@
         </is>
       </c>
       <c r="S358" s="1" t="n">
-        <v>45455</v>
+        <v>25569.0421927662</v>
       </c>
       <c r="T358" t="n">
         <v>10</v>
@@ -32802,7 +32802,7 @@
         <v>5.599999904632568</v>
       </c>
       <c r="E359" t="n">
-        <v>-0.0666666825612386</v>
+        <v>-0.8697674440783124</v>
       </c>
       <c r="F359" t="n">
         <v>-0.003571425226269879</v>
@@ -32852,7 +32852,7 @@
         </is>
       </c>
       <c r="S359" s="1" t="n">
-        <v>45639</v>
+        <v>25569.04219489583</v>
       </c>
       <c r="T359" t="n">
         <v>43</v>
@@ -32893,7 +32893,7 @@
         <v>9.989999771118164</v>
       </c>
       <c r="E360" t="n">
-        <v>0.001002026988028807</v>
+        <v>-0.001000022888183594</v>
       </c>
       <c r="F360" t="n">
         <v>0.003003071805090731</v>
@@ -32941,7 +32941,7 @@
         </is>
       </c>
       <c r="S360" s="1" t="n">
-        <v>45475</v>
+        <v>25569.04219299768</v>
       </c>
       <c r="T360" t="n">
         <v>10</v>
@@ -32982,7 +32982,7 @@
         <v>23</v>
       </c>
       <c r="E361" t="n">
-        <v>0</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="F361" t="n">
         <v>0.2704347527545432</v>
@@ -33032,7 +33032,7 @@
         </is>
       </c>
       <c r="S361" s="1" t="n">
-        <v>45393</v>
+        <v>25569.04219204861</v>
       </c>
       <c r="T361" t="n">
         <v>21</v>
@@ -33073,7 +33073,7 @@
         <v>19.79999923706055</v>
       </c>
       <c r="E362" t="n">
-        <v>-0.05714289347330729</v>
+        <v>0.04210522300318686</v>
       </c>
       <c r="F362" t="n">
         <v>-0.08333331727820954</v>
@@ -33123,7 +33123,7 @@
         </is>
       </c>
       <c r="S362" s="1" t="n">
-        <v>45421</v>
+        <v>25569.04219237269</v>
       </c>
       <c r="T362" t="n">
         <v>19</v>
@@ -33164,7 +33164,7 @@
         <v>16.54999923706055</v>
       </c>
       <c r="E363" t="n">
-        <v>0.06774188626197077</v>
+        <v>0.1033332824707034</v>
       </c>
       <c r="F363" t="n">
         <v>0.0368580446206658</v>
@@ -33214,7 +33214,7 @@
         </is>
       </c>
       <c r="S363" s="1" t="n">
-        <v>45590</v>
+        <v>25569.0421943287</v>
       </c>
       <c r="T363" t="n">
         <v>15</v>
@@ -33255,7 +33255,7 @@
         <v>9.949999809265137</v>
       </c>
       <c r="E364" t="n">
-        <v>0</v>
+        <v>-0.005000019073486328</v>
       </c>
       <c r="F364" t="n">
         <v>0.00201009629618767</v>
@@ -33303,7 +33303,7 @@
         </is>
       </c>
       <c r="S364" s="1" t="n">
-        <v>45593</v>
+        <v>25569.04219436342</v>
       </c>
       <c r="T364" t="n">
         <v>10</v>
@@ -33344,7 +33344,7 @@
         <v>24</v>
       </c>
       <c r="E365" t="n">
-        <v>0.02127659574468085</v>
+        <v>0.1428571428571428</v>
       </c>
       <c r="F365" t="n">
         <v>0.2012499968210856</v>
@@ -33394,7 +33394,7 @@
         </is>
       </c>
       <c r="S365" s="1" t="n">
-        <v>45302</v>
+        <v>25569.04219099537</v>
       </c>
       <c r="T365" t="n">
         <v>21</v>
@@ -33435,7 +33435,7 @@
         <v>9.890000343322754</v>
       </c>
       <c r="E366" t="n">
-        <v>-0.001010027837658038</v>
+        <v>-0.01099996566772461</v>
       </c>
       <c r="F366" t="n">
         <v>0</v>
@@ -33483,7 +33483,7 @@
         </is>
       </c>
       <c r="S366" s="1" t="n">
-        <v>45656</v>
+        <v>25569.04219509259</v>
       </c>
       <c r="T366" t="n">
         <v>10</v>
@@ -33524,7 +33524,7 @@
         <v>9.960000038146973</v>
       </c>
       <c r="E367" t="n">
-        <v>-0.001003031957271566</v>
+        <v>-0.003999996185302735</v>
       </c>
       <c r="F367" t="n">
         <v>0.003012021371113646</v>
@@ -33574,7 +33574,7 @@
         </is>
       </c>
       <c r="S367" s="1" t="n">
-        <v>45534</v>
+        <v>25569.04219368055</v>
       </c>
       <c r="T367" t="n">
         <v>10</v>
@@ -33615,7 +33615,7 @@
         <v>13.30000019073486</v>
       </c>
       <c r="E368" t="n">
-        <v>-0.01481480068630642</v>
+        <v>-0.1687499880790713</v>
       </c>
       <c r="F368" t="n">
         <v>-0.09849627073909974</v>
@@ -33665,7 +33665,7 @@
         </is>
       </c>
       <c r="S368" s="1" t="n">
-        <v>45471</v>
+        <v>25569.04219295139</v>
       </c>
       <c r="T368" t="n">
         <v>16</v>
@@ -33706,7 +33706,7 @@
         <v>10.05000019073486</v>
       </c>
       <c r="E369" t="n">
-        <v>0.005000019073486328</v>
+        <v>0.005000019073485973</v>
       </c>
       <c r="F369" t="n">
         <v>0.004975143262281594</v>
@@ -33754,7 +33754,7 @@
         </is>
       </c>
       <c r="S369" s="1" t="n">
-        <v>45379</v>
+        <v>25569.04219188658</v>
       </c>
       <c r="T369" t="n">
         <v>10</v>
@@ -33795,7 +33795,7 @@
         <v>9.989999771118164</v>
       </c>
       <c r="E370" t="n">
-        <v>-0.02058823941900664</v>
+        <v>-0.001000022888183594</v>
       </c>
       <c r="F370" t="n">
         <v>0.002002047870060487</v>
@@ -33845,7 +33845,7 @@
         </is>
       </c>
       <c r="S370" s="1" t="n">
-        <v>45520</v>
+        <v>25569.04219351852</v>
       </c>
       <c r="T370" t="n">
         <v>10</v>
@@ -33886,7 +33886,7 @@
         <v>9.850000381469727</v>
       </c>
       <c r="E371" t="n">
-        <v>-0.002026292231129302</v>
+        <v>-0.01499996185302734</v>
       </c>
       <c r="F371" t="n">
         <v>0.001015154804088193</v>
@@ -33932,7 +33932,7 @@
         </is>
       </c>
       <c r="S371" s="1" t="n">
-        <v>45628</v>
+        <v>25569.04219476852</v>
       </c>
       <c r="T371" t="n">
         <v>10</v>
@@ -33973,7 +33973,7 @@
         <v>18.01000022888184</v>
       </c>
       <c r="E372" t="n">
-        <v>0.09151516538677794</v>
+        <v>0.09151516538677815</v>
       </c>
       <c r="F372" t="n">
         <v>-0.4934480827863429</v>
@@ -34023,7 +34023,7 @@
         </is>
       </c>
       <c r="S372" s="1" t="n">
-        <v>45569</v>
+        <v>25569.04219408565</v>
       </c>
       <c r="T372" t="n">
         <v>16.5</v>
@@ -34064,7 +34064,7 @@
         <v>9.970000267028809</v>
       </c>
       <c r="E373" t="n">
-        <v>0.001004039040515551</v>
+        <v>-0.00299997329711914</v>
       </c>
       <c r="F373" t="n">
         <v>0.006018000434844867</v>
@@ -34112,7 +34112,7 @@
         </is>
       </c>
       <c r="S373" s="1" t="n">
-        <v>45565</v>
+        <v>25569.04219403935</v>
       </c>
       <c r="T373" t="n">
         <v>10</v>
@@ -34203,7 +34203,7 @@
         </is>
       </c>
       <c r="S374" s="1" t="n">
-        <v>45421</v>
+        <v>25569.04219237269</v>
       </c>
       <c r="T374" t="n">
         <v>15</v>
@@ -34244,7 +34244,7 @@
         <v>17.0953540802002</v>
       </c>
       <c r="E375" t="n">
-        <v>0.0257533870331228</v>
+        <v>-0.1002445220947264</v>
       </c>
       <c r="F375" t="n">
         <v>0.01816244739837791</v>
@@ -34294,7 +34294,7 @@
         </is>
       </c>
       <c r="S375" s="1" t="n">
-        <v>45567</v>
+        <v>25569.0421940625</v>
       </c>
       <c r="T375" t="n">
         <v>19</v>
@@ -34335,7 +34335,7 @@
         <v>22.08971786499023</v>
       </c>
       <c r="E376" t="n">
-        <v>0.02181816101074221</v>
+        <v>-0.06001200574509656</v>
       </c>
       <c r="F376" t="n">
         <v>0.07962647609860453</v>
@@ -34385,7 +34385,7 @@
         </is>
       </c>
       <c r="S376" s="1" t="n">
-        <v>45498</v>
+        <v>25569.04219326389</v>
       </c>
       <c r="T376" t="n">
         <v>23.5</v>
@@ -34426,7 +34426,7 @@
         <v>9.970000267028809</v>
       </c>
       <c r="E377" t="n">
-        <v>0.001004039040515551</v>
+        <v>-0.7820764968955451</v>
       </c>
       <c r="F377" t="n">
         <v>0.004012032174693999</v>
@@ -34474,7 +34474,7 @@
         </is>
       </c>
       <c r="S377" s="1" t="n">
-        <v>45516</v>
+        <v>25569.04219347222</v>
       </c>
       <c r="T377" t="n">
         <v>45.75</v>
@@ -34515,7 +34515,7 @@
         <v>11</v>
       </c>
       <c r="E378" t="n">
-        <v>-0.08333333333333333</v>
+        <v>-0.1538461538461539</v>
       </c>
       <c r="F378" t="n">
         <v>-0.1600000208074396</v>
@@ -34565,7 +34565,7 @@
         </is>
       </c>
       <c r="S378" s="1" t="n">
-        <v>45317</v>
+        <v>25569.04219116898</v>
       </c>
       <c r="T378" t="n">
         <v>13</v>
@@ -34606,7 +34606,7 @@
         <v>26.10000038146973</v>
       </c>
       <c r="E379" t="n">
-        <v>-0.001912016741488466</v>
+        <v>0.08750001589457208</v>
       </c>
       <c r="F379" t="n">
         <v>0.2639847201645552</v>
@@ -34656,7 +34656,7 @@
         </is>
       </c>
       <c r="S379" s="1" t="n">
-        <v>45413</v>
+        <v>25569.04219228009</v>
       </c>
       <c r="T379" t="n">
         <v>24</v>
@@ -34697,7 +34697,7 @@
         <v>23</v>
       </c>
       <c r="E380" t="n">
-        <v>0.07981224525029877</v>
+        <v>0.09523809523809523</v>
       </c>
       <c r="F380" t="n">
         <v>-0.4456521739130435</v>
@@ -34747,7 +34747,7 @@
         </is>
       </c>
       <c r="S380" s="1" t="n">
-        <v>45470</v>
+        <v>25569.04219293981</v>
       </c>
       <c r="T380" t="n">
         <v>21</v>
@@ -34788,7 +34788,7 @@
         <v>9.949999809265137</v>
       </c>
       <c r="E381" t="n">
-        <v>-0.002006063914543131</v>
+        <v>-0.005000019073486328</v>
       </c>
       <c r="F381" t="n">
         <v>0.004020096745708537</v>
@@ -34838,7 +34838,7 @@
         </is>
       </c>
       <c r="S381" s="1" t="n">
-        <v>45589</v>
+        <v>25569.04219431713</v>
       </c>
       <c r="T381" t="n">
         <v>10</v>
@@ -34879,7 +34879,7 @@
         <v>10.13000011444092</v>
       </c>
       <c r="E382" t="n">
-        <v>-0.006862715307174296</v>
+        <v>0.01300001144409197</v>
       </c>
       <c r="F382" t="n">
         <v>0.001974284685431048</v>
@@ -34927,7 +34927,7 @@
         </is>
       </c>
       <c r="S382" s="1" t="n">
-        <v>45425</v>
+        <v>25569.04219241898</v>
       </c>
       <c r="T382" t="n">
         <v>10</v>
@@ -34968,7 +34968,7 @@
         <v>13.39999961853027</v>
       </c>
       <c r="E383" t="n">
-        <v>0</v>
+        <v>0.03076920142540538</v>
       </c>
       <c r="F383" t="n">
         <v>0.1291045182955306</v>
@@ -35018,7 +35018,7 @@
         </is>
       </c>
       <c r="S383" s="1" t="n">
-        <v>45323</v>
+        <v>25569.04219123843</v>
       </c>
       <c r="T383" t="n">
         <v>13</v>
@@ -35059,7 +35059,7 @@
         <v>10.72000026702881</v>
       </c>
       <c r="E384" t="n">
-        <v>-0.03942648623649687</v>
+        <v>-0.02545452117919906</v>
       </c>
       <c r="F384" t="n">
         <v>-0.4953358477003506</v>
@@ -35109,7 +35109,7 @@
         </is>
       </c>
       <c r="S384" s="1" t="n">
-        <v>45576</v>
+        <v>25569.04219416667</v>
       </c>
       <c r="T384" t="n">
         <v>11</v>
@@ -35150,7 +35150,7 @@
         <v>25</v>
       </c>
       <c r="E385" t="n">
-        <v>0.07480652424747676</v>
+        <v>0.4705882352941176</v>
       </c>
       <c r="F385" t="n">
         <v>0.05239997863769531</v>
@@ -35200,7 +35200,7 @@
         </is>
       </c>
       <c r="S385" s="1" t="n">
-        <v>45576</v>
+        <v>25569.04219416667</v>
       </c>
       <c r="T385" t="n">
         <v>17</v>
@@ -35241,7 +35241,7 @@
         <v>32.75</v>
       </c>
       <c r="E386" t="n">
-        <v>0.0564516129032258</v>
+        <v>0.3645833333333333</v>
       </c>
       <c r="F386" t="n">
         <v>-0.1123664215320849</v>
@@ -35291,7 +35291,7 @@
         </is>
       </c>
       <c r="S386" s="1" t="n">
-        <v>45567</v>
+        <v>25569.0421940625</v>
       </c>
       <c r="T386" t="n">
         <v>24</v>
@@ -35332,7 +35332,7 @@
         <v>30.10000038146973</v>
       </c>
       <c r="E387" t="n">
-        <v>-0.001658349508894097</v>
+        <v>0.3681818355213514</v>
       </c>
       <c r="F387" t="n">
         <v>-0.2279069941332872</v>
@@ -35382,7 +35382,7 @@
         </is>
       </c>
       <c r="S387" s="1" t="n">
-        <v>45331</v>
+        <v>25569.04219133102</v>
       </c>
       <c r="T387" t="n">
         <v>22</v>
@@ -35423,7 +35423,7 @@
         <v>20.70000076293945</v>
       </c>
       <c r="E388" t="n">
-        <v>-0.01428567795526414</v>
+        <v>-0.0372092668400256</v>
       </c>
       <c r="F388" t="n">
         <v>0.1492753641883974</v>
@@ -35473,7 +35473,7 @@
         </is>
       </c>
       <c r="S388" s="1" t="n">
-        <v>45450</v>
+        <v>25569.04219270833</v>
       </c>
       <c r="T388" t="n">
         <v>21.5</v>
@@ -35514,7 +35514,7 @@
         <v>23.40999984741211</v>
       </c>
       <c r="E389" t="n">
-        <v>-0.1081904820033482</v>
+        <v>0.3005555470784505</v>
       </c>
       <c r="F389" t="n">
         <v>-0.03887227054009172</v>
@@ -35564,7 +35564,7 @@
         </is>
       </c>
       <c r="S389" s="1" t="n">
-        <v>45548</v>
+        <v>25569.04219384259</v>
       </c>
       <c r="T389" t="n">
         <v>18</v>
@@ -35605,7 +35605,7 @@
         <v>12</v>
       </c>
       <c r="E390" t="n">
-        <v>-0.2</v>
+        <v>-0.07692307692307693</v>
       </c>
       <c r="F390" t="n">
         <v>0.1958333651224772</v>
@@ -35655,7 +35655,7 @@
         </is>
       </c>
       <c r="S390" s="1" t="n">
-        <v>45623</v>
+        <v>25569.04219471065</v>
       </c>
       <c r="T390" t="n">
         <v>13</v>
@@ -35696,7 +35696,7 @@
         <v>14.25</v>
       </c>
       <c r="E391" t="n">
-        <v>0</v>
+        <v>-0.05</v>
       </c>
       <c r="F391" t="n">
         <v>-0.3971929717482182</v>
@@ -35746,7 +35746,7 @@
         </is>
       </c>
       <c r="S391" s="1" t="n">
-        <v>45379</v>
+        <v>25569.04219188658</v>
       </c>
       <c r="T391" t="n">
         <v>15</v>
@@ -35787,7 +35787,7 @@
         <v>16.45000076293945</v>
       </c>
       <c r="E392" t="n">
-        <v>-0.01497005919633241</v>
+        <v>-0.03235289629767944</v>
       </c>
       <c r="F392" t="n">
         <v>-0.3562310236212073</v>
@@ -35837,7 +35837,7 @@
         </is>
       </c>
       <c r="S392" s="1" t="n">
-        <v>45449</v>
+        <v>25569.04219269676</v>
       </c>
       <c r="T392" t="n">
         <v>17</v>
@@ -35878,7 +35878,7 @@
         <v>16.05999946594238</v>
       </c>
       <c r="E393" t="n">
-        <v>0.07066663106282552</v>
+        <v>0.003749966621398704</v>
       </c>
       <c r="F393" t="n">
         <v>0.2272727110776461</v>
@@ -35928,7 +35928,7 @@
         </is>
       </c>
       <c r="S393" s="1" t="n">
-        <v>45491</v>
+        <v>25569.04219318287</v>
       </c>
       <c r="T393" t="n">
         <v>16</v>
@@ -35969,7 +35969,7 @@
         <v>21.39999961853027</v>
       </c>
       <c r="E394" t="n">
-        <v>-0.0893617183604139</v>
+        <v>0.1888888676961261</v>
       </c>
       <c r="F394" t="n">
         <v>0.07523367472200616</v>
@@ -36019,7 +36019,7 @@
         </is>
       </c>
       <c r="S394" s="1" t="n">
-        <v>45590</v>
+        <v>25569.0421943287</v>
       </c>
       <c r="T394" t="n">
         <v>18</v>
@@ -36060,7 +36060,7 @@
         <v>18.14999961853027</v>
       </c>
       <c r="E395" t="n">
-        <v>-0.01089922391181085</v>
+        <v>0.06764703638413352</v>
       </c>
       <c r="F395" t="n">
         <v>0.1239669447542499</v>
@@ -36110,7 +36110,7 @@
         </is>
       </c>
       <c r="S395" s="1" t="n">
-        <v>45548</v>
+        <v>25569.04219384259</v>
       </c>
       <c r="T395" t="n">
         <v>17</v>
@@ -36151,7 +36151,7 @@
         <v>316</v>
       </c>
       <c r="E396" t="n">
-        <v>-0.368</v>
+        <v>17.58823529411765</v>
       </c>
       <c r="F396" t="n">
         <v>-0.1645569620253164</v>
@@ -36201,7 +36201,7 @@
         </is>
       </c>
       <c r="S396" s="1" t="n">
-        <v>45588</v>
+        <v>25569.04219430556</v>
       </c>
       <c r="T396" t="n">
         <v>17</v>
@@ -36242,7 +36242,7 @@
         <v>26.1299991607666</v>
       </c>
       <c r="E397" t="n">
-        <v>-0.03222225330494068</v>
+        <v>0.08874996503194173</v>
       </c>
       <c r="F397" t="n">
         <v>-0.1274397256279269</v>
@@ -36292,7 +36292,7 @@
         </is>
       </c>
       <c r="S397" s="1" t="n">
-        <v>45574</v>
+        <v>25569.04219414352</v>
       </c>
       <c r="T397" t="n">
         <v>24</v>
@@ -36333,7 +36333,7 @@
         <v>22.29000091552734</v>
       </c>
       <c r="E398" t="n">
-        <v>-0.1744444105360243</v>
+        <v>0.1395705989533406</v>
       </c>
       <c r="F398" t="n">
         <v>-0.2328398528885763</v>
@@ -36381,7 +36381,7 @@
         </is>
       </c>
       <c r="S398" s="1" t="n">
-        <v>45429</v>
+        <v>25569.04219246528</v>
       </c>
       <c r="T398" t="n">
         <v>19.56</v>
@@ -36422,7 +36422,7 @@
         <v>50.43999862670898</v>
       </c>
       <c r="E399" t="n">
-        <v>0.07319146014274434</v>
+        <v>0.4835293713737934</v>
       </c>
       <c r="F399" t="n">
         <v>-0.07533702102538067</v>
@@ -36472,7 +36472,7 @@
         </is>
       </c>
       <c r="S399" s="1" t="n">
-        <v>45372</v>
+        <v>25569.04219180555</v>
       </c>
       <c r="T399" t="n">
         <v>34</v>
@@ -36513,7 +36513,7 @@
         <v>9.909999847412109</v>
       </c>
       <c r="E400" t="n">
-        <v>-0.002014144727996343</v>
+        <v>-0.009000015258789063</v>
       </c>
       <c r="F400" t="n">
         <v>0.002018209694412334</v>
@@ -36561,7 +36561,7 @@
         </is>
       </c>
       <c r="S400" s="1" t="n">
-        <v>45546</v>
+        <v>25569.04219381944</v>
       </c>
       <c r="T400" t="n">
         <v>10</v>
@@ -36602,7 +36602,7 @@
         <v>74.53819274902344</v>
       </c>
       <c r="E401" t="n">
-        <v>-0.01487806366711124</v>
+        <v>2.549437749953497</v>
       </c>
       <c r="F401" t="n">
         <v>0.002847427857279575</v>
@@ -36652,7 +36652,7 @@
         </is>
       </c>
       <c r="S401" s="1" t="n">
-        <v>45498</v>
+        <v>25569.04219326389</v>
       </c>
       <c r="T401" t="n">
         <v>21</v>
@@ -36693,7 +36693,7 @@
         <v>21.75</v>
       </c>
       <c r="E402" t="n">
-        <v>-0.03333333333333333</v>
+        <v>-0.09375</v>
       </c>
       <c r="F402" t="n">
         <v>-0.01149425287356322</v>
@@ -36741,7 +36741,7 @@
         </is>
       </c>
       <c r="S402" s="1" t="n">
-        <v>45470</v>
+        <v>25569.04219293981</v>
       </c>
       <c r="T402" t="n">
         <v>24</v>
@@ -36782,7 +36782,7 @@
         <v>48.79999923706055</v>
       </c>
       <c r="E403" t="n">
-        <v>0.08444442749023437</v>
+        <v>0.7428571156093052</v>
       </c>
       <c r="F403" t="n">
         <v>0.210245948701545</v>
@@ -36832,7 +36832,7 @@
         </is>
       </c>
       <c r="S403" s="1" t="n">
-        <v>45407</v>
+        <v>25569.04219221065</v>
       </c>
       <c r="T403" t="n">
         <v>28</v>
@@ -36873,7 +36873,7 @@
         <v>18.41255378723145</v>
       </c>
       <c r="E404" t="n">
-        <v>-0.02615385789137624</v>
+        <v>-0.03091822172466059</v>
       </c>
       <c r="F404" t="n">
         <v>0.053712438031421</v>
@@ -36923,7 +36923,7 @@
         </is>
       </c>
       <c r="S404" s="1" t="n">
-        <v>45407</v>
+        <v>25569.04219221065</v>
       </c>
       <c r="T404" t="n">
         <v>19</v>
@@ -36964,7 +36964,7 @@
         <v>12.85000038146973</v>
       </c>
       <c r="E405" t="n">
-        <v>-0.06545451771129261</v>
+        <v>-0.143333307902018</v>
       </c>
       <c r="F405" t="n">
         <v>-0.5136186914816921</v>
@@ -37014,7 +37014,7 @@
         </is>
       </c>
       <c r="S405" s="1" t="n">
-        <v>45324</v>
+        <v>25569.04219125</v>
       </c>
       <c r="T405" t="n">
         <v>15</v>
@@ -37055,7 +37055,7 @@
         <v>9.979999542236328</v>
       </c>
       <c r="E406" t="n">
-        <v>0.002007982330598095</v>
+        <v>-0.002000045776367187</v>
       </c>
       <c r="F406" t="n">
         <v>-0.001001931429475685</v>
@@ -37103,7 +37103,7 @@
         </is>
       </c>
       <c r="S406" s="1" t="n">
-        <v>45413</v>
+        <v>25569.04219228009</v>
       </c>
       <c r="T406" t="n">
         <v>10</v>
@@ -37144,7 +37144,7 @@
         <v>9.970000267028809</v>
       </c>
       <c r="E407" t="n">
-        <v>-0.001001931429475685</v>
+        <v>-0.00299997329711914</v>
       </c>
       <c r="F407" t="n">
         <v>0.004012032174693999</v>
@@ -37192,7 +37192,7 @@
         </is>
       </c>
       <c r="S407" s="1" t="n">
-        <v>45551</v>
+        <v>25569.04219387731</v>
       </c>
       <c r="T407" t="n">
         <v>10</v>
@@ -37233,7 +37233,7 @@
         <v>12.14441967010498</v>
       </c>
       <c r="E408" t="n">
-        <v>0.02879376455837599</v>
+        <v>0.01203497250874837</v>
       </c>
       <c r="F408" t="n">
         <v>0.07261746519079462</v>
@@ -37283,7 +37283,7 @@
         </is>
       </c>
       <c r="S408" s="1" t="n">
-        <v>45329</v>
+        <v>25569.04219130787</v>
       </c>
       <c r="T408" t="n">
         <v>12</v>
